--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B17" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,46 +2200,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R17" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2283,22 +2274,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B18" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,37 +2297,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R18" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,12 +2380,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5947,57 +5947,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356294</v>
+        <v>128353737</v>
       </c>
       <c r="B54" t="n">
-        <v>90892</v>
+        <v>86623</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>3762</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565290</v>
+        <v>565164</v>
       </c>
       <c r="R54" t="n">
-        <v>6683893</v>
+        <v>6683706</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6041,57 +6032,66 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356352</v>
+        <v>128356294</v>
       </c>
       <c r="B55" t="n">
-        <v>92663</v>
+        <v>90892</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565124</v>
+        <v>565290</v>
       </c>
       <c r="R55" t="n">
-        <v>6683563</v>
+        <v>6683893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6150,54 +6150,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356320</v>
+        <v>128356352</v>
       </c>
       <c r="B56" t="n">
-        <v>92679</v>
+        <v>92663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565213</v>
+        <v>565124</v>
       </c>
       <c r="R56" t="n">
-        <v>6683796</v>
+        <v>6683563</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,45 +6247,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356356</v>
+        <v>128356320</v>
       </c>
       <c r="B57" t="n">
-        <v>92663</v>
+        <v>92679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565307</v>
+        <v>565213</v>
       </c>
       <c r="R57" t="n">
-        <v>6683932</v>
+        <v>6683796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,32 +6353,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356360</v>
+        <v>128356356</v>
       </c>
       <c r="B58" t="n">
-        <v>100655</v>
+        <v>92663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565329</v>
+        <v>565307</v>
       </c>
       <c r="R58" t="n">
-        <v>6683831</v>
+        <v>6683932</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356257</v>
+        <v>128356360</v>
       </c>
       <c r="B59" t="n">
-        <v>92290</v>
+        <v>100655</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6461,43 +6461,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565243</v>
+        <v>565329</v>
       </c>
       <c r="R59" t="n">
-        <v>6683765</v>
+        <v>6683831</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6556,10 +6547,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356316</v>
+        <v>128356257</v>
       </c>
       <c r="B60" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6567,26 +6558,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6600,10 +6591,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565125</v>
+        <v>565243</v>
       </c>
       <c r="R60" t="n">
-        <v>6683662</v>
+        <v>6683765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,10 +6653,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356236</v>
+        <v>128356316</v>
       </c>
       <c r="B61" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6673,26 +6664,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6706,10 +6697,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565136</v>
+        <v>565125</v>
       </c>
       <c r="R61" t="n">
-        <v>6683697</v>
+        <v>6683662</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6768,10 +6759,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128353737</v>
+        <v>128356236</v>
       </c>
       <c r="B62" t="n">
-        <v>86623</v>
+        <v>92290</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6779,37 +6770,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565164</v>
+        <v>565136</v>
       </c>
       <c r="R62" t="n">
-        <v>6683706</v>
+        <v>6683697</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6853,22 +6853,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128353797</v>
+        <v>128356270</v>
       </c>
       <c r="B63" t="n">
-        <v>86623</v>
+        <v>92657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,37 +6876,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565197</v>
+        <v>565281</v>
       </c>
       <c r="R63" t="n">
-        <v>6683732</v>
+        <v>6683884</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6950,22 +6950,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356270</v>
+        <v>128356322</v>
       </c>
       <c r="B64" t="n">
-        <v>92657</v>
+        <v>92679</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,34 +6973,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565281</v>
+        <v>565121</v>
       </c>
       <c r="R64" t="n">
-        <v>6683884</v>
+        <v>6683569</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7059,10 +7068,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356322</v>
+        <v>128356259</v>
       </c>
       <c r="B65" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,26 +7079,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7103,10 +7112,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565121</v>
+        <v>565167</v>
       </c>
       <c r="R65" t="n">
-        <v>6683569</v>
+        <v>6683728</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,10 +7174,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356259</v>
+        <v>128353797</v>
       </c>
       <c r="B66" t="n">
-        <v>92290</v>
+        <v>86623</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7176,46 +7185,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565167</v>
+        <v>565197</v>
       </c>
       <c r="R66" t="n">
-        <v>6683728</v>
+        <v>6683732</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7259,12 +7259,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8171,48 +8171,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128354266</v>
+        <v>128356363</v>
       </c>
       <c r="B76" t="n">
-        <v>86822</v>
+        <v>100655</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565313</v>
+        <v>565298</v>
       </c>
       <c r="R76" t="n">
-        <v>6683939</v>
+        <v>6683884</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8256,22 +8256,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128353641</v>
+        <v>128356315</v>
       </c>
       <c r="B77" t="n">
-        <v>86623</v>
+        <v>92679</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8279,37 +8279,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565149</v>
+        <v>565123</v>
       </c>
       <c r="R77" t="n">
-        <v>6683686</v>
+        <v>6683582</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8353,60 +8362,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128354183</v>
+        <v>128356344</v>
       </c>
       <c r="B78" t="n">
-        <v>92290</v>
+        <v>92663</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565320</v>
+        <v>565307</v>
       </c>
       <c r="R78" t="n">
         <v>6683918</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8450,60 +8459,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356363</v>
+        <v>128354266</v>
       </c>
       <c r="B79" t="n">
-        <v>100655</v>
+        <v>86822</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R79" t="n">
-        <v>6683884</v>
+        <v>6683939</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8547,22 +8556,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356315</v>
+        <v>128353641</v>
       </c>
       <c r="B80" t="n">
-        <v>92679</v>
+        <v>86623</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8570,46 +8579,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565123</v>
+        <v>565149</v>
       </c>
       <c r="R80" t="n">
-        <v>6683582</v>
+        <v>6683686</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8653,60 +8653,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128356344</v>
+        <v>128354183</v>
       </c>
       <c r="B81" t="n">
-        <v>92663</v>
+        <v>92290</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565307</v>
+        <v>565320</v>
       </c>
       <c r="R81" t="n">
         <v>6683918</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,12 +8750,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9078,6 +9078,241 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128379692</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92666</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>565156</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6683686</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128379701</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92650</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>788</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>565183</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6683738</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>6 m långt mycel</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356237</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>92657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,46 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683884</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356335</v>
+        <v>128356237</v>
       </c>
       <c r="B6" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,34 +1083,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565323</v>
+        <v>565304</v>
       </c>
       <c r="R6" t="n">
-        <v>6683839</v>
+        <v>6683884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,7 +1178,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356324</v>
+        <v>128356335</v>
       </c>
       <c r="B7" t="n">
         <v>92679</v>
@@ -1211,26 +1206,17 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565185</v>
+        <v>565323</v>
       </c>
       <c r="R7" t="n">
-        <v>6683745</v>
+        <v>6683839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356311</v>
+        <v>128356324</v>
       </c>
       <c r="B8" t="n">
-        <v>92647</v>
+        <v>92679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565121</v>
+        <v>565185</v>
       </c>
       <c r="R8" t="n">
-        <v>6683581</v>
+        <v>6683745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,48 +1386,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128353720</v>
+        <v>128356311</v>
       </c>
       <c r="B9" t="n">
-        <v>92657</v>
+        <v>92647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565171</v>
+        <v>565121</v>
       </c>
       <c r="R9" t="n">
-        <v>6683703</v>
+        <v>6683581</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356237</v>
       </c>
       <c r="B5" t="n">
-        <v>92657</v>
+        <v>92290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565304</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683884</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1069,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356237</v>
+        <v>128356335</v>
       </c>
       <c r="B6" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,43 +1092,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565304</v>
+        <v>565323</v>
       </c>
       <c r="R6" t="n">
-        <v>6683884</v>
+        <v>6683839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1152,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1183,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356335</v>
+        <v>128356324</v>
       </c>
       <c r="B7" t="n">
         <v>92679</v>
@@ -1206,17 +1211,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565323</v>
+        <v>565185</v>
       </c>
       <c r="R7" t="n">
-        <v>6683839</v>
+        <v>6683745</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1263,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,54 +1289,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356324</v>
+        <v>128356311</v>
       </c>
       <c r="B8" t="n">
-        <v>92679</v>
+        <v>92647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565185</v>
+        <v>565121</v>
       </c>
       <c r="R8" t="n">
-        <v>6683745</v>
+        <v>6683581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,48 +1386,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356311</v>
+        <v>128353720</v>
       </c>
       <c r="B9" t="n">
-        <v>92647</v>
+        <v>92657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565121</v>
+        <v>565171</v>
       </c>
       <c r="R9" t="n">
-        <v>6683581</v>
+        <v>6683703</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B17" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,37 +2200,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R17" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2274,22 +2283,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B18" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,46 +2306,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R18" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,12 +2380,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128356270</v>
+        <v>128353797</v>
       </c>
       <c r="B63" t="n">
-        <v>92657</v>
+        <v>86623</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,37 +6876,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565281</v>
+        <v>565197</v>
       </c>
       <c r="R63" t="n">
-        <v>6683884</v>
+        <v>6683732</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6950,22 +6950,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356322</v>
+        <v>128356270</v>
       </c>
       <c r="B64" t="n">
-        <v>92679</v>
+        <v>92657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,43 +6973,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565121</v>
+        <v>565281</v>
       </c>
       <c r="R64" t="n">
-        <v>6683569</v>
+        <v>6683884</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7068,10 +7059,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356259</v>
+        <v>128356322</v>
       </c>
       <c r="B65" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,26 +7070,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7112,10 +7103,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565167</v>
+        <v>565121</v>
       </c>
       <c r="R65" t="n">
-        <v>6683728</v>
+        <v>6683569</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,10 +7165,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128353797</v>
+        <v>128356259</v>
       </c>
       <c r="B66" t="n">
-        <v>86623</v>
+        <v>92290</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7185,37 +7176,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565197</v>
+        <v>565167</v>
       </c>
       <c r="R66" t="n">
-        <v>6683732</v>
+        <v>6683728</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7259,12 +7259,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356237</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>92657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,46 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683884</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356335</v>
+        <v>128356237</v>
       </c>
       <c r="B6" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,34 +1083,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565323</v>
+        <v>565304</v>
       </c>
       <c r="R6" t="n">
-        <v>6683839</v>
+        <v>6683884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,7 +1178,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356324</v>
+        <v>128356335</v>
       </c>
       <c r="B7" t="n">
         <v>92679</v>
@@ -1211,26 +1206,17 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565185</v>
+        <v>565323</v>
       </c>
       <c r="R7" t="n">
-        <v>6683745</v>
+        <v>6683839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356311</v>
+        <v>128356324</v>
       </c>
       <c r="B8" t="n">
-        <v>92647</v>
+        <v>92679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565121</v>
+        <v>565185</v>
       </c>
       <c r="R8" t="n">
-        <v>6683581</v>
+        <v>6683745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,48 +1386,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128353720</v>
+        <v>128356311</v>
       </c>
       <c r="B9" t="n">
-        <v>92657</v>
+        <v>92647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565171</v>
+        <v>565121</v>
       </c>
       <c r="R9" t="n">
-        <v>6683703</v>
+        <v>6683581</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -5947,48 +5947,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128353737</v>
+        <v>128356294</v>
       </c>
       <c r="B54" t="n">
-        <v>86623</v>
+        <v>90892</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3762</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565164</v>
+        <v>565290</v>
       </c>
       <c r="R54" t="n">
-        <v>6683706</v>
+        <v>6683893</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6032,66 +6041,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356294</v>
+        <v>128356352</v>
       </c>
       <c r="B55" t="n">
-        <v>90892</v>
+        <v>92663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565290</v>
+        <v>565124</v>
       </c>
       <c r="R55" t="n">
-        <v>6683893</v>
+        <v>6683563</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6150,45 +6150,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356352</v>
+        <v>128356320</v>
       </c>
       <c r="B56" t="n">
-        <v>92663</v>
+        <v>92679</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565124</v>
+        <v>565213</v>
       </c>
       <c r="R56" t="n">
-        <v>6683563</v>
+        <v>6683796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6247,54 +6256,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356320</v>
+        <v>128356356</v>
       </c>
       <c r="B57" t="n">
-        <v>92679</v>
+        <v>92663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565213</v>
+        <v>565307</v>
       </c>
       <c r="R57" t="n">
-        <v>6683796</v>
+        <v>6683932</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,32 +6353,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356356</v>
+        <v>128356360</v>
       </c>
       <c r="B58" t="n">
-        <v>92663</v>
+        <v>100655</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565307</v>
+        <v>565329</v>
       </c>
       <c r="R58" t="n">
-        <v>6683932</v>
+        <v>6683831</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356360</v>
+        <v>128356257</v>
       </c>
       <c r="B59" t="n">
-        <v>100655</v>
+        <v>92290</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6461,34 +6461,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565329</v>
+        <v>565243</v>
       </c>
       <c r="R59" t="n">
-        <v>6683831</v>
+        <v>6683765</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,10 +6556,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356257</v>
+        <v>128356316</v>
       </c>
       <c r="B60" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6558,26 +6567,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6591,10 +6600,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565243</v>
+        <v>565125</v>
       </c>
       <c r="R60" t="n">
-        <v>6683765</v>
+        <v>6683662</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6653,10 +6662,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356316</v>
+        <v>128356236</v>
       </c>
       <c r="B61" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6664,26 +6673,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6697,10 +6706,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565125</v>
+        <v>565136</v>
       </c>
       <c r="R61" t="n">
-        <v>6683662</v>
+        <v>6683697</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6759,10 +6768,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128356236</v>
+        <v>128353737</v>
       </c>
       <c r="B62" t="n">
-        <v>92290</v>
+        <v>86623</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6770,46 +6779,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565136</v>
+        <v>565164</v>
       </c>
       <c r="R62" t="n">
-        <v>6683697</v>
+        <v>6683706</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6853,22 +6853,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128353797</v>
+        <v>128356270</v>
       </c>
       <c r="B63" t="n">
-        <v>86623</v>
+        <v>92657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,37 +6876,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565197</v>
+        <v>565281</v>
       </c>
       <c r="R63" t="n">
-        <v>6683732</v>
+        <v>6683884</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6950,22 +6950,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356270</v>
+        <v>128356322</v>
       </c>
       <c r="B64" t="n">
-        <v>92657</v>
+        <v>92679</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,34 +6973,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565281</v>
+        <v>565121</v>
       </c>
       <c r="R64" t="n">
-        <v>6683884</v>
+        <v>6683569</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7059,10 +7068,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356322</v>
+        <v>128356259</v>
       </c>
       <c r="B65" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,26 +7079,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7103,10 +7112,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565121</v>
+        <v>565167</v>
       </c>
       <c r="R65" t="n">
-        <v>6683569</v>
+        <v>6683728</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,10 +7174,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356259</v>
+        <v>128353797</v>
       </c>
       <c r="B66" t="n">
-        <v>92290</v>
+        <v>86623</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7176,46 +7185,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565167</v>
+        <v>565197</v>
       </c>
       <c r="R66" t="n">
-        <v>6683728</v>
+        <v>6683732</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7259,12 +7259,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356237</v>
       </c>
       <c r="B5" t="n">
-        <v>92657</v>
+        <v>92290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565304</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683884</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1069,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356237</v>
+        <v>128356335</v>
       </c>
       <c r="B6" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,43 +1092,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565304</v>
+        <v>565323</v>
       </c>
       <c r="R6" t="n">
-        <v>6683884</v>
+        <v>6683839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1152,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1183,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356335</v>
+        <v>128356324</v>
       </c>
       <c r="B7" t="n">
         <v>92679</v>
@@ -1206,17 +1211,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565323</v>
+        <v>565185</v>
       </c>
       <c r="R7" t="n">
-        <v>6683839</v>
+        <v>6683745</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1263,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,54 +1289,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356324</v>
+        <v>128356311</v>
       </c>
       <c r="B8" t="n">
-        <v>92679</v>
+        <v>92647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565185</v>
+        <v>565121</v>
       </c>
       <c r="R8" t="n">
-        <v>6683745</v>
+        <v>6683581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,48 +1386,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356311</v>
+        <v>128353720</v>
       </c>
       <c r="B9" t="n">
-        <v>92647</v>
+        <v>92657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565121</v>
+        <v>565171</v>
       </c>
       <c r="R9" t="n">
-        <v>6683581</v>
+        <v>6683703</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B17" t="n">
-        <v>92290</v>
+        <v>92679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,46 +2200,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R17" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2283,22 +2274,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B18" t="n">
-        <v>92679</v>
+        <v>92290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,37 +2297,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R18" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,12 +2380,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356348</v>
       </c>
       <c r="B2" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B3" t="n">
-        <v>100655</v>
+        <v>92684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R3" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B4" t="n">
-        <v>92679</v>
+        <v>100660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R4" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356237</v>
+        <v>128356324</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>92684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,26 +986,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565185</v>
       </c>
       <c r="R5" t="n">
-        <v>6683884</v>
+        <v>6683745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
         <v>128356335</v>
       </c>
       <c r="B6" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356324</v>
+        <v>128353720</v>
       </c>
       <c r="B7" t="n">
-        <v>92679</v>
+        <v>92662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,46 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565185</v>
+        <v>565171</v>
       </c>
       <c r="R7" t="n">
-        <v>6683745</v>
+        <v>6683703</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,57 +1268,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356311</v>
+        <v>128356237</v>
       </c>
       <c r="B8" t="n">
-        <v>92647</v>
+        <v>92295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565121</v>
+        <v>565304</v>
       </c>
       <c r="R8" t="n">
-        <v>6683581</v>
+        <v>6683884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,48 +1386,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128353720</v>
+        <v>128356311</v>
       </c>
       <c r="B9" t="n">
-        <v>92657</v>
+        <v>92652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565171</v>
+        <v>565121</v>
       </c>
       <c r="R9" t="n">
-        <v>6683703</v>
+        <v>6683581</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
         <v>128356345</v>
       </c>
       <c r="B10" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128356260</v>
       </c>
       <c r="B11" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128356235</v>
+        <v>128353570</v>
       </c>
       <c r="B12" t="n">
-        <v>92290</v>
+        <v>92684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,46 +1697,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565149</v>
+        <v>565129</v>
       </c>
       <c r="R12" t="n">
-        <v>6683718</v>
+        <v>6683660</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,57 +1771,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356353</v>
+        <v>128356325</v>
       </c>
       <c r="B13" t="n">
-        <v>92663</v>
+        <v>92684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565118</v>
+        <v>565139</v>
       </c>
       <c r="R13" t="n">
-        <v>6683561</v>
+        <v>6683679</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356325</v>
+        <v>128356235</v>
       </c>
       <c r="B14" t="n">
-        <v>92679</v>
+        <v>92295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565139</v>
+        <v>565149</v>
       </c>
       <c r="R14" t="n">
-        <v>6683679</v>
+        <v>6683718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353600</v>
+        <v>128356353</v>
       </c>
       <c r="B15" t="n">
-        <v>92647</v>
+        <v>92668</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565138</v>
+        <v>565118</v>
       </c>
       <c r="R15" t="n">
-        <v>6683661</v>
+        <v>6683561</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2080,44 +2080,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128353570</v>
+        <v>128353600</v>
       </c>
       <c r="B16" t="n">
-        <v>92679</v>
+        <v>92652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565129</v>
+        <v>565138</v>
       </c>
       <c r="R16" t="n">
-        <v>6683660</v>
+        <v>6683661</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2192,7 +2192,7 @@
         <v>128353672</v>
       </c>
       <c r="B17" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128356245</v>
       </c>
       <c r="B18" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128356319</v>
       </c>
       <c r="B19" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,45 +2498,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356349</v>
+        <v>128356321</v>
       </c>
       <c r="B20" t="n">
-        <v>92663</v>
+        <v>92684</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565147</v>
+        <v>565225</v>
       </c>
       <c r="R20" t="n">
-        <v>6683691</v>
+        <v>6683834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,54 +2604,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356321</v>
+        <v>128356342</v>
       </c>
       <c r="B21" t="n">
-        <v>92679</v>
+        <v>92668</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565225</v>
+        <v>565338</v>
       </c>
       <c r="R21" t="n">
-        <v>6683834</v>
+        <v>6683896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356342</v>
+        <v>128356338</v>
       </c>
       <c r="B22" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565338</v>
+        <v>565124</v>
       </c>
       <c r="R22" t="n">
-        <v>6683896</v>
+        <v>6683659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,6 +2772,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2798,10 +2803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356338</v>
+        <v>128356349</v>
       </c>
       <c r="B23" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,10 +2838,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565124</v>
+        <v>565147</v>
       </c>
       <c r="R23" t="n">
-        <v>6683659</v>
+        <v>6683691</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2869,11 +2874,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128356333</v>
+        <v>128356323</v>
       </c>
       <c r="B24" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565281</v>
+        <v>565127</v>
       </c>
       <c r="R24" t="n">
-        <v>6683884</v>
+        <v>6683598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128356323</v>
+        <v>128356332</v>
       </c>
       <c r="B25" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565127</v>
+        <v>565289</v>
       </c>
       <c r="R25" t="n">
-        <v>6683598</v>
+        <v>6683895</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128356332</v>
+        <v>128356333</v>
       </c>
       <c r="B26" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565289</v>
+        <v>565281</v>
       </c>
       <c r="R26" t="n">
-        <v>6683895</v>
+        <v>6683884</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>128356287</v>
       </c>
       <c r="B27" t="n">
-        <v>86623</v>
+        <v>86624</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128356346</v>
       </c>
       <c r="B28" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,54 +3412,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128356248</v>
+        <v>128356337</v>
       </c>
       <c r="B29" t="n">
-        <v>92290</v>
+        <v>92668</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565207</v>
+        <v>565149</v>
       </c>
       <c r="R29" t="n">
-        <v>6683770</v>
+        <v>6683707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,6 +3483,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,45 +3514,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128356337</v>
+        <v>128356248</v>
       </c>
       <c r="B30" t="n">
-        <v>92663</v>
+        <v>92295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565149</v>
+        <v>565207</v>
       </c>
       <c r="R30" t="n">
-        <v>6683707</v>
+        <v>6683770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,11 +3594,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128356276</v>
+        <v>128354204</v>
       </c>
       <c r="B31" t="n">
-        <v>97350</v>
+        <v>86786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,37 +3631,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565383</v>
+        <v>565325</v>
       </c>
       <c r="R31" t="n">
-        <v>6683939</v>
+        <v>6683920</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3705,22 +3705,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128356309</v>
+        <v>128353904</v>
       </c>
       <c r="B32" t="n">
-        <v>92647</v>
+        <v>92668</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,37 +3728,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565184</v>
+        <v>565224</v>
       </c>
       <c r="R32" t="n">
-        <v>6683739</v>
+        <v>6683766</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,66 +3802,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356250</v>
+        <v>128356343</v>
       </c>
       <c r="B33" t="n">
-        <v>92290</v>
+        <v>92668</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565136</v>
+        <v>565300</v>
       </c>
       <c r="R33" t="n">
-        <v>6683681</v>
+        <v>6683931</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,45 +3911,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356343</v>
+        <v>128356250</v>
       </c>
       <c r="B34" t="n">
-        <v>92663</v>
+        <v>92295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565300</v>
+        <v>565136</v>
       </c>
       <c r="R34" t="n">
-        <v>6683931</v>
+        <v>6683681</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
         <v>128356336</v>
       </c>
       <c r="B35" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4119,54 +4119,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356255</v>
+        <v>128356309</v>
       </c>
       <c r="B36" t="n">
-        <v>92290</v>
+        <v>92652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565128</v>
+        <v>565184</v>
       </c>
       <c r="R36" t="n">
-        <v>6683585</v>
+        <v>6683739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4225,48 +4216,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128353904</v>
+        <v>128356276</v>
       </c>
       <c r="B37" t="n">
-        <v>92663</v>
+        <v>97355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4368</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565224</v>
+        <v>565383</v>
       </c>
       <c r="R37" t="n">
-        <v>6683766</v>
+        <v>6683939</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4310,12 +4301,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4325,7 +4316,7 @@
         <v>128354354</v>
       </c>
       <c r="B38" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,10 +4410,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128354204</v>
+        <v>128356255</v>
       </c>
       <c r="B39" t="n">
-        <v>86785</v>
+        <v>92295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,37 +4421,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565325</v>
+        <v>565128</v>
       </c>
       <c r="R39" t="n">
-        <v>6683920</v>
+        <v>6683585</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4504,22 +4504,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356252</v>
+        <v>128356326</v>
       </c>
       <c r="B40" t="n">
-        <v>92290</v>
+        <v>92684</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,26 +4527,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565313</v>
+        <v>565306</v>
       </c>
       <c r="R40" t="n">
-        <v>6683875</v>
+        <v>6683915</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356326</v>
+        <v>128356252</v>
       </c>
       <c r="B41" t="n">
-        <v>92679</v>
+        <v>92295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,26 +4633,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565306</v>
+        <v>565313</v>
       </c>
       <c r="R41" t="n">
-        <v>6683915</v>
+        <v>6683875</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,37 +4728,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356219</v>
+        <v>128356240</v>
       </c>
       <c r="B42" t="n">
-        <v>90877</v>
+        <v>92295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>256335</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565287</v>
+        <v>565298</v>
       </c>
       <c r="R42" t="n">
-        <v>6683892</v>
+        <v>6683931</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4816,7 +4816,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4835,10 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356240</v>
+        <v>128356234</v>
       </c>
       <c r="B43" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4864,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4879,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565298</v>
+        <v>565304</v>
       </c>
       <c r="R43" t="n">
-        <v>6683931</v>
+        <v>6683798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,37 +4940,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356234</v>
+        <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>92290</v>
+        <v>90880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>256335</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4985,10 +4984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565304</v>
+        <v>565287</v>
       </c>
       <c r="R44" t="n">
-        <v>6683798</v>
+        <v>6683892</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,6 +5028,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>128356317</v>
       </c>
       <c r="B45" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5153,45 +5153,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356351</v>
+        <v>128356262</v>
       </c>
       <c r="B46" t="n">
-        <v>92663</v>
+        <v>92295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565125</v>
+        <v>565306</v>
       </c>
       <c r="R46" t="n">
-        <v>6683620</v>
+        <v>6683913</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,54 +5259,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356262</v>
+        <v>128356351</v>
       </c>
       <c r="B47" t="n">
-        <v>92290</v>
+        <v>92668</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565306</v>
+        <v>565125</v>
       </c>
       <c r="R47" t="n">
-        <v>6683913</v>
+        <v>6683620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
         <v>128356374</v>
       </c>
       <c r="B48" t="n">
-        <v>86785</v>
+        <v>86786</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5462,48 +5462,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128356350</v>
+        <v>128353745</v>
       </c>
       <c r="B49" t="n">
-        <v>92663</v>
+        <v>92684</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565128</v>
+        <v>565166</v>
       </c>
       <c r="R49" t="n">
-        <v>6683651</v>
+        <v>6683711</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5547,22 +5547,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356310</v>
+        <v>128356350</v>
       </c>
       <c r="B50" t="n">
-        <v>92647</v>
+        <v>92668</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5570,21 +5570,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565306</v>
+        <v>565128</v>
       </c>
       <c r="R50" t="n">
-        <v>6683913</v>
+        <v>6683651</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5659,7 +5659,7 @@
         <v>128356307</v>
       </c>
       <c r="B51" t="n">
-        <v>92647</v>
+        <v>92652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>128353808</v>
       </c>
       <c r="B52" t="n">
-        <v>92647</v>
+        <v>92652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5850,48 +5850,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128353745</v>
+        <v>128356310</v>
       </c>
       <c r="B53" t="n">
-        <v>92679</v>
+        <v>92652</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565166</v>
+        <v>565306</v>
       </c>
       <c r="R53" t="n">
-        <v>6683711</v>
+        <v>6683913</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,66 +5935,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356294</v>
+        <v>128356360</v>
       </c>
       <c r="B54" t="n">
-        <v>90892</v>
+        <v>100660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565290</v>
+        <v>565329</v>
       </c>
       <c r="R54" t="n">
-        <v>6683893</v>
+        <v>6683831</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6053,48 +6044,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356352</v>
+        <v>128353737</v>
       </c>
       <c r="B55" t="n">
-        <v>92663</v>
+        <v>86624</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565124</v>
+        <v>565164</v>
       </c>
       <c r="R55" t="n">
-        <v>6683563</v>
+        <v>6683706</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6138,22 +6129,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356320</v>
+        <v>128356316</v>
       </c>
       <c r="B56" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6180,7 +6171,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6194,10 +6185,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565213</v>
+        <v>565125</v>
       </c>
       <c r="R56" t="n">
-        <v>6683796</v>
+        <v>6683662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,45 +6247,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356356</v>
+        <v>128356294</v>
       </c>
       <c r="B57" t="n">
-        <v>92663</v>
+        <v>90895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565307</v>
+        <v>565290</v>
       </c>
       <c r="R57" t="n">
-        <v>6683932</v>
+        <v>6683893</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356360</v>
+        <v>128356320</v>
       </c>
       <c r="B58" t="n">
-        <v>100655</v>
+        <v>92684</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,34 +6364,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565329</v>
+        <v>565213</v>
       </c>
       <c r="R58" t="n">
-        <v>6683831</v>
+        <v>6683796</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,10 +6459,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356257</v>
+        <v>128356236</v>
       </c>
       <c r="B59" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6480,7 +6489,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6494,10 +6503,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565243</v>
+        <v>565136</v>
       </c>
       <c r="R59" t="n">
-        <v>6683765</v>
+        <v>6683697</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6556,54 +6565,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356316</v>
+        <v>128356356</v>
       </c>
       <c r="B60" t="n">
-        <v>92679</v>
+        <v>92668</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565125</v>
+        <v>565307</v>
       </c>
       <c r="R60" t="n">
-        <v>6683662</v>
+        <v>6683932</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,54 +6662,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356236</v>
+        <v>128356352</v>
       </c>
       <c r="B61" t="n">
-        <v>92290</v>
+        <v>92668</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565136</v>
+        <v>565124</v>
       </c>
       <c r="R61" t="n">
-        <v>6683697</v>
+        <v>6683563</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6768,10 +6759,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128353737</v>
+        <v>128356257</v>
       </c>
       <c r="B62" t="n">
-        <v>86623</v>
+        <v>92295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6779,37 +6770,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565164</v>
+        <v>565243</v>
       </c>
       <c r="R62" t="n">
-        <v>6683706</v>
+        <v>6683765</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6853,12 +6853,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6868,7 +6868,7 @@
         <v>128356270</v>
       </c>
       <c r="B63" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356322</v>
+        <v>128353797</v>
       </c>
       <c r="B64" t="n">
-        <v>92679</v>
+        <v>86624</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,46 +6973,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565121</v>
+        <v>565197</v>
       </c>
       <c r="R64" t="n">
-        <v>6683569</v>
+        <v>6683732</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7056,22 +7047,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356259</v>
+        <v>128356322</v>
       </c>
       <c r="B65" t="n">
-        <v>92290</v>
+        <v>92684</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,26 +7070,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7112,10 +7103,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565167</v>
+        <v>565121</v>
       </c>
       <c r="R65" t="n">
-        <v>6683728</v>
+        <v>6683569</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,10 +7165,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128353797</v>
+        <v>128356259</v>
       </c>
       <c r="B66" t="n">
-        <v>86623</v>
+        <v>92295</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7185,37 +7176,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565197</v>
+        <v>565167</v>
       </c>
       <c r="R66" t="n">
-        <v>6683732</v>
+        <v>6683728</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7259,22 +7259,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128356261</v>
+        <v>128356361</v>
       </c>
       <c r="B67" t="n">
-        <v>92290</v>
+        <v>100660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,43 +7282,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565331</v>
+        <v>565330</v>
       </c>
       <c r="R67" t="n">
-        <v>6683832</v>
+        <v>6683934</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7377,10 +7368,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128356361</v>
+        <v>128356261</v>
       </c>
       <c r="B68" t="n">
-        <v>100655</v>
+        <v>92295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7388,34 +7379,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565330</v>
+        <v>565331</v>
       </c>
       <c r="R68" t="n">
-        <v>6683934</v>
+        <v>6683832</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7477,7 +7477,7 @@
         <v>128356288</v>
       </c>
       <c r="B69" t="n">
-        <v>86623</v>
+        <v>86624</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7571,10 +7571,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356231</v>
+        <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>92290</v>
+        <v>86624</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7582,43 +7582,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565261</v>
+        <v>565257</v>
       </c>
       <c r="R70" t="n">
-        <v>6683777</v>
+        <v>6683775</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,10 +7668,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356331</v>
+        <v>128356231</v>
       </c>
       <c r="B71" t="n">
-        <v>92679</v>
+        <v>92295</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7688,26 +7679,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7721,10 +7712,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565298</v>
+        <v>565261</v>
       </c>
       <c r="R71" t="n">
-        <v>6683926</v>
+        <v>6683777</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7783,10 +7774,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356286</v>
+        <v>128356331</v>
       </c>
       <c r="B72" t="n">
-        <v>86623</v>
+        <v>92684</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7794,34 +7785,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565257</v>
+        <v>565298</v>
       </c>
       <c r="R72" t="n">
-        <v>6683775</v>
+        <v>6683926</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7880,10 +7880,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354290</v>
+        <v>128354079</v>
       </c>
       <c r="B73" t="n">
-        <v>86822</v>
+        <v>92652</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>788</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565327</v>
+        <v>565281</v>
       </c>
       <c r="R73" t="n">
-        <v>6683939</v>
+        <v>6683847</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7980,7 +7980,7 @@
         <v>128354308</v>
       </c>
       <c r="B74" t="n">
-        <v>100655</v>
+        <v>100660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8074,10 +8074,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354079</v>
+        <v>128354290</v>
       </c>
       <c r="B75" t="n">
-        <v>92647</v>
+        <v>86823</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8085,21 +8085,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>788</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565281</v>
+        <v>565327</v>
       </c>
       <c r="R75" t="n">
-        <v>6683847</v>
+        <v>6683939</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8171,10 +8171,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356363</v>
+        <v>128353641</v>
       </c>
       <c r="B76" t="n">
-        <v>100655</v>
+        <v>86624</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,37 +8182,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565298</v>
+        <v>565149</v>
       </c>
       <c r="R76" t="n">
-        <v>6683884</v>
+        <v>6683686</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8256,12 +8256,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8271,7 +8271,7 @@
         <v>128356315</v>
       </c>
       <c r="B77" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8374,10 +8374,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128356344</v>
+        <v>128354266</v>
       </c>
       <c r="B78" t="n">
-        <v>92663</v>
+        <v>86823</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8385,37 +8385,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565307</v>
+        <v>565313</v>
       </c>
       <c r="R78" t="n">
-        <v>6683918</v>
+        <v>6683939</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8459,22 +8459,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128354266</v>
+        <v>128356344</v>
       </c>
       <c r="B79" t="n">
-        <v>86822</v>
+        <v>92668</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8482,37 +8482,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565313</v>
+        <v>565307</v>
       </c>
       <c r="R79" t="n">
-        <v>6683939</v>
+        <v>6683918</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,22 +8556,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128353641</v>
+        <v>128354183</v>
       </c>
       <c r="B80" t="n">
-        <v>86623</v>
+        <v>92295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8579,34 +8579,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565149</v>
+        <v>565320</v>
       </c>
       <c r="R80" t="n">
-        <v>6683686</v>
+        <v>6683918</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8665,10 +8665,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354183</v>
+        <v>128356363</v>
       </c>
       <c r="B81" t="n">
-        <v>92290</v>
+        <v>100660</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8676,37 +8676,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565320</v>
+        <v>565298</v>
       </c>
       <c r="R81" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,12 +8750,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8765,7 +8765,7 @@
         <v>128356334</v>
       </c>
       <c r="B82" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128356330</v>
+        <v>128356318</v>
       </c>
       <c r="B83" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>565306</v>
+        <v>565133</v>
       </c>
       <c r="R83" t="n">
-        <v>6683912</v>
+        <v>6683665</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8974,10 +8974,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128356318</v>
+        <v>128356330</v>
       </c>
       <c r="B84" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>565133</v>
+        <v>565306</v>
       </c>
       <c r="R84" t="n">
-        <v>6683665</v>
+        <v>6683912</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9083,7 +9083,7 @@
         <v>128379692</v>
       </c>
       <c r="B85" t="n">
-        <v>92666</v>
+        <v>92668</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128379701</v>
       </c>
       <c r="B86" t="n">
-        <v>92650</v>
+        <v>92652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -1995,10 +1995,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128356353</v>
+        <v>128353600</v>
       </c>
       <c r="B15" t="n">
-        <v>92668</v>
+        <v>92652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565118</v>
+        <v>565138</v>
       </c>
       <c r="R15" t="n">
-        <v>6683561</v>
+        <v>6683661</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2080,22 +2080,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128353600</v>
+        <v>128356353</v>
       </c>
       <c r="B16" t="n">
-        <v>92652</v>
+        <v>92668</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,37 +2103,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565138</v>
+        <v>565118</v>
       </c>
       <c r="R16" t="n">
-        <v>6683661</v>
+        <v>6683561</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3412,45 +3412,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128356337</v>
+        <v>128356248</v>
       </c>
       <c r="B29" t="n">
-        <v>92668</v>
+        <v>92295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565149</v>
+        <v>565207</v>
       </c>
       <c r="R29" t="n">
-        <v>6683707</v>
+        <v>6683770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,11 +3492,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3514,54 +3518,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128356248</v>
+        <v>128356337</v>
       </c>
       <c r="B30" t="n">
-        <v>92295</v>
+        <v>92668</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565207</v>
+        <v>565149</v>
       </c>
       <c r="R30" t="n">
-        <v>6683770</v>
+        <v>6683707</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,6 +3589,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4516,37 +4516,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356326</v>
+        <v>128356219</v>
       </c>
       <c r="B40" t="n">
-        <v>92684</v>
+        <v>90880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>256335</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565306</v>
+        <v>565287</v>
       </c>
       <c r="R40" t="n">
-        <v>6683915</v>
+        <v>6683892</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4604,6 +4604,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4622,10 +4623,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356252</v>
+        <v>128356326</v>
       </c>
       <c r="B41" t="n">
-        <v>92295</v>
+        <v>92684</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,26 +4634,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4667,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565313</v>
+        <v>565306</v>
       </c>
       <c r="R41" t="n">
-        <v>6683875</v>
+        <v>6683915</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,7 +4729,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356240</v>
+        <v>128356252</v>
       </c>
       <c r="B42" t="n">
         <v>92295</v>
@@ -4758,7 +4759,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R42" t="n">
-        <v>6683931</v>
+        <v>6683875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4834,7 +4835,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356234</v>
+        <v>128356240</v>
       </c>
       <c r="B43" t="n">
         <v>92295</v>
@@ -4864,7 +4865,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565304</v>
+        <v>565298</v>
       </c>
       <c r="R43" t="n">
-        <v>6683798</v>
+        <v>6683931</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4940,37 +4941,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356219</v>
+        <v>128356234</v>
       </c>
       <c r="B44" t="n">
-        <v>90880</v>
+        <v>92295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256335</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4984,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565287</v>
+        <v>565304</v>
       </c>
       <c r="R44" t="n">
-        <v>6683892</v>
+        <v>6683798</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,7 +5029,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356360</v>
+        <v>128353737</v>
       </c>
       <c r="B54" t="n">
-        <v>100660</v>
+        <v>86624</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565329</v>
+        <v>565164</v>
       </c>
       <c r="R54" t="n">
-        <v>6683831</v>
+        <v>6683706</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6032,22 +6032,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128353737</v>
+        <v>128356316</v>
       </c>
       <c r="B55" t="n">
-        <v>86624</v>
+        <v>92684</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6055,37 +6055,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565164</v>
+        <v>565125</v>
       </c>
       <c r="R55" t="n">
-        <v>6683706</v>
+        <v>6683662</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6129,49 +6138,49 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356316</v>
+        <v>128356294</v>
       </c>
       <c r="B56" t="n">
-        <v>92684</v>
+        <v>90895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6185,10 +6194,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565125</v>
+        <v>565290</v>
       </c>
       <c r="R56" t="n">
-        <v>6683662</v>
+        <v>6683893</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6247,37 +6256,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356294</v>
+        <v>128356320</v>
       </c>
       <c r="B57" t="n">
-        <v>90895</v>
+        <v>92684</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6291,10 +6300,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565290</v>
+        <v>565213</v>
       </c>
       <c r="R57" t="n">
-        <v>6683893</v>
+        <v>6683796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,10 +6362,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356320</v>
+        <v>128356360</v>
       </c>
       <c r="B58" t="n">
-        <v>92684</v>
+        <v>100660</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,43 +6373,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565213</v>
+        <v>565329</v>
       </c>
       <c r="R58" t="n">
-        <v>6683796</v>
+        <v>6683831</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8374,10 +8374,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128354266</v>
+        <v>128356344</v>
       </c>
       <c r="B78" t="n">
-        <v>86823</v>
+        <v>92668</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8385,37 +8385,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565313</v>
+        <v>565307</v>
       </c>
       <c r="R78" t="n">
-        <v>6683939</v>
+        <v>6683918</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8459,60 +8459,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356344</v>
+        <v>128354183</v>
       </c>
       <c r="B79" t="n">
-        <v>92668</v>
+        <v>92295</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565307</v>
+        <v>565320</v>
       </c>
       <c r="R79" t="n">
         <v>6683918</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,22 +8556,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128354183</v>
+        <v>128356363</v>
       </c>
       <c r="B80" t="n">
-        <v>92295</v>
+        <v>100660</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8579,37 +8579,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565320</v>
+        <v>565298</v>
       </c>
       <c r="R80" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8653,60 +8653,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128356363</v>
+        <v>128354266</v>
       </c>
       <c r="B81" t="n">
-        <v>100660</v>
+        <v>86823</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R81" t="n">
-        <v>6683884</v>
+        <v>6683939</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,12 +8750,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356348</v>
       </c>
       <c r="B2" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B3" t="n">
-        <v>92684</v>
+        <v>100753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R3" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B4" t="n">
-        <v>100660</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R4" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356324</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92684</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,46 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565185</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683745</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356335</v>
+        <v>128356324</v>
       </c>
       <c r="B6" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,17 +1100,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565323</v>
+        <v>565185</v>
       </c>
       <c r="R6" t="n">
-        <v>6683839</v>
+        <v>6683745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128353720</v>
+        <v>128356335</v>
       </c>
       <c r="B7" t="n">
-        <v>92662</v>
+        <v>92776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1189,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565171</v>
+        <v>565323</v>
       </c>
       <c r="R7" t="n">
-        <v>6683703</v>
+        <v>6683839</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,66 +1268,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356237</v>
+        <v>128356311</v>
       </c>
       <c r="B8" t="n">
-        <v>92295</v>
+        <v>92744</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565304</v>
+        <v>565121</v>
       </c>
       <c r="R8" t="n">
-        <v>6683884</v>
+        <v>6683581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356311</v>
+        <v>128356237</v>
       </c>
       <c r="B9" t="n">
-        <v>92652</v>
+        <v>92387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565121</v>
+        <v>565304</v>
       </c>
       <c r="R9" t="n">
-        <v>6683581</v>
+        <v>6683884</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
         <v>128356345</v>
       </c>
       <c r="B10" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128356260</v>
       </c>
       <c r="B11" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128353570</v>
+        <v>128356235</v>
       </c>
       <c r="B12" t="n">
-        <v>92684</v>
+        <v>92387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,37 +1697,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565129</v>
+        <v>565149</v>
       </c>
       <c r="R12" t="n">
-        <v>6683660</v>
+        <v>6683718</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,66 +1780,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356325</v>
+        <v>128356353</v>
       </c>
       <c r="B13" t="n">
-        <v>92684</v>
+        <v>92760</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565139</v>
+        <v>565118</v>
       </c>
       <c r="R13" t="n">
-        <v>6683679</v>
+        <v>6683561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,64 +1882,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356235</v>
+        <v>128353600</v>
       </c>
       <c r="B14" t="n">
-        <v>92295</v>
+        <v>92744</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565149</v>
+        <v>565138</v>
       </c>
       <c r="R14" t="n">
-        <v>6683718</v>
+        <v>6683661</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1983,44 +1974,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353600</v>
+        <v>128353570</v>
       </c>
       <c r="B15" t="n">
-        <v>92652</v>
+        <v>92776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2030,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565138</v>
+        <v>565129</v>
       </c>
       <c r="R15" t="n">
-        <v>6683661</v>
+        <v>6683660</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2092,45 +2083,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356353</v>
+        <v>128356325</v>
       </c>
       <c r="B16" t="n">
-        <v>92668</v>
+        <v>92776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565118</v>
+        <v>565139</v>
       </c>
       <c r="R16" t="n">
-        <v>6683561</v>
+        <v>6683679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B17" t="n">
-        <v>92684</v>
+        <v>92387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,37 +2200,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R17" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2274,22 +2283,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B18" t="n">
-        <v>92295</v>
+        <v>92776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,46 +2306,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R18" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,66 +2380,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356319</v>
+        <v>128356342</v>
       </c>
       <c r="B19" t="n">
-        <v>92684</v>
+        <v>92760</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565206</v>
+        <v>565338</v>
       </c>
       <c r="R19" t="n">
-        <v>6683808</v>
+        <v>6683896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,54 +2489,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356321</v>
+        <v>128356338</v>
       </c>
       <c r="B20" t="n">
-        <v>92684</v>
+        <v>92760</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565225</v>
+        <v>565124</v>
       </c>
       <c r="R20" t="n">
-        <v>6683834</v>
+        <v>6683659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,6 +2560,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,10 +2591,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356342</v>
+        <v>128356349</v>
       </c>
       <c r="B21" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565338</v>
+        <v>565147</v>
       </c>
       <c r="R21" t="n">
-        <v>6683896</v>
+        <v>6683691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,45 +2688,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356338</v>
+        <v>128356319</v>
       </c>
       <c r="B22" t="n">
-        <v>92668</v>
+        <v>92776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565124</v>
+        <v>565206</v>
       </c>
       <c r="R22" t="n">
-        <v>6683659</v>
+        <v>6683808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,11 +2768,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2803,45 +2794,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356349</v>
+        <v>128356321</v>
       </c>
       <c r="B23" t="n">
-        <v>92668</v>
+        <v>92776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565147</v>
+        <v>565225</v>
       </c>
       <c r="R23" t="n">
-        <v>6683691</v>
+        <v>6683834</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,7 +2903,7 @@
         <v>128356323</v>
       </c>
       <c r="B24" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128356332</v>
       </c>
       <c r="B25" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128356333</v>
       </c>
       <c r="B26" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>128356287</v>
       </c>
       <c r="B27" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128356346</v>
       </c>
       <c r="B28" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,54 +3412,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128356248</v>
+        <v>128356337</v>
       </c>
       <c r="B29" t="n">
-        <v>92295</v>
+        <v>92760</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565207</v>
+        <v>565149</v>
       </c>
       <c r="R29" t="n">
-        <v>6683770</v>
+        <v>6683707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,6 +3483,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,45 +3514,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128356337</v>
+        <v>128356248</v>
       </c>
       <c r="B30" t="n">
-        <v>92668</v>
+        <v>92387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565149</v>
+        <v>565207</v>
       </c>
       <c r="R30" t="n">
-        <v>6683707</v>
+        <v>6683770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,11 +3594,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3623,7 +3623,7 @@
         <v>128354204</v>
       </c>
       <c r="B31" t="n">
-        <v>86786</v>
+        <v>86878</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128353904</v>
+        <v>128356309</v>
       </c>
       <c r="B32" t="n">
-        <v>92668</v>
+        <v>92744</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,37 +3728,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565224</v>
+        <v>565184</v>
       </c>
       <c r="R32" t="n">
-        <v>6683766</v>
+        <v>6683739</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,57 +3802,66 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356343</v>
+        <v>128356255</v>
       </c>
       <c r="B33" t="n">
-        <v>92668</v>
+        <v>92387</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565300</v>
+        <v>565128</v>
       </c>
       <c r="R33" t="n">
-        <v>6683931</v>
+        <v>6683585</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,54 +3920,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356250</v>
+        <v>128356343</v>
       </c>
       <c r="B34" t="n">
-        <v>92295</v>
+        <v>92760</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565136</v>
+        <v>565300</v>
       </c>
       <c r="R34" t="n">
-        <v>6683681</v>
+        <v>6683931</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,45 +4017,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356336</v>
+        <v>128356250</v>
       </c>
       <c r="B35" t="n">
-        <v>92668</v>
+        <v>92387</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565294</v>
+        <v>565136</v>
       </c>
       <c r="R35" t="n">
-        <v>6683885</v>
+        <v>6683681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4088,11 +4097,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356309</v>
+        <v>128356336</v>
       </c>
       <c r="B36" t="n">
-        <v>92652</v>
+        <v>92760</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4130,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4154,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565184</v>
+        <v>565294</v>
       </c>
       <c r="R36" t="n">
-        <v>6683739</v>
+        <v>6683885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,6 +4194,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4216,10 +4225,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356276</v>
+        <v>128354354</v>
       </c>
       <c r="B37" t="n">
-        <v>97355</v>
+        <v>92776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,37 +4236,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565383</v>
+        <v>565289</v>
       </c>
       <c r="R37" t="n">
-        <v>6683939</v>
+        <v>6683828</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4301,22 +4310,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128354354</v>
+        <v>128356276</v>
       </c>
       <c r="B38" t="n">
-        <v>92684</v>
+        <v>97448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4324,37 +4333,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565289</v>
+        <v>565383</v>
       </c>
       <c r="R38" t="n">
-        <v>6683828</v>
+        <v>6683939</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4398,69 +4407,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128356255</v>
+        <v>128353904</v>
       </c>
       <c r="B39" t="n">
-        <v>92295</v>
+        <v>92760</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565128</v>
+        <v>565224</v>
       </c>
       <c r="R39" t="n">
-        <v>6683585</v>
+        <v>6683766</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4504,49 +4504,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356219</v>
+        <v>128356252</v>
       </c>
       <c r="B40" t="n">
-        <v>90880</v>
+        <v>92387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>256335</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565287</v>
+        <v>565313</v>
       </c>
       <c r="R40" t="n">
-        <v>6683892</v>
+        <v>6683875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4604,7 +4604,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4623,10 +4622,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356326</v>
+        <v>128356240</v>
       </c>
       <c r="B41" t="n">
-        <v>92684</v>
+        <v>92387</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4634,26 +4633,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4667,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565306</v>
+        <v>565298</v>
       </c>
       <c r="R41" t="n">
-        <v>6683915</v>
+        <v>6683931</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4729,10 +4728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356252</v>
+        <v>128356234</v>
       </c>
       <c r="B42" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,7 +4758,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4773,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565313</v>
+        <v>565304</v>
       </c>
       <c r="R42" t="n">
-        <v>6683875</v>
+        <v>6683798</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,10 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356240</v>
+        <v>128356326</v>
       </c>
       <c r="B43" t="n">
-        <v>92295</v>
+        <v>92776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4846,26 +4845,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4879,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565298</v>
+        <v>565306</v>
       </c>
       <c r="R43" t="n">
-        <v>6683931</v>
+        <v>6683915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,37 +4940,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356234</v>
+        <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>92295</v>
+        <v>90972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>256335</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4985,10 +4984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565304</v>
+        <v>565287</v>
       </c>
       <c r="R44" t="n">
-        <v>6683798</v>
+        <v>6683892</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,6 +5028,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128356317</v>
+        <v>128356262</v>
       </c>
       <c r="B45" t="n">
-        <v>92684</v>
+        <v>92387</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5058,26 +5058,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565188</v>
+        <v>565306</v>
       </c>
       <c r="R45" t="n">
-        <v>6683735</v>
+        <v>6683913</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,54 +5153,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356262</v>
+        <v>128356351</v>
       </c>
       <c r="B46" t="n">
-        <v>92295</v>
+        <v>92760</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565306</v>
+        <v>565125</v>
       </c>
       <c r="R46" t="n">
-        <v>6683913</v>
+        <v>6683620</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,52 +5243,61 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356351</v>
+        <v>128356317</v>
       </c>
       <c r="B47" t="n">
-        <v>92668</v>
+        <v>92776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565125</v>
+        <v>565188</v>
       </c>
       <c r="R47" t="n">
-        <v>6683620</v>
+        <v>6683735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
         <v>128356374</v>
       </c>
       <c r="B48" t="n">
-        <v>86786</v>
+        <v>86878</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5455,55 +5455,55 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128353745</v>
+        <v>128356307</v>
       </c>
       <c r="B49" t="n">
-        <v>92684</v>
+        <v>92744</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565166</v>
+        <v>565193</v>
       </c>
       <c r="R49" t="n">
-        <v>6683711</v>
+        <v>6683755</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5547,22 +5547,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356350</v>
+        <v>128353808</v>
       </c>
       <c r="B50" t="n">
-        <v>92668</v>
+        <v>92744</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5570,37 +5570,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565128</v>
+        <v>565189</v>
       </c>
       <c r="R50" t="n">
-        <v>6683651</v>
+        <v>6683740</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5644,22 +5644,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128356307</v>
+        <v>128356310</v>
       </c>
       <c r="B51" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565193</v>
+        <v>565306</v>
       </c>
       <c r="R51" t="n">
-        <v>6683755</v>
+        <v>6683913</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5753,10 +5753,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128353808</v>
+        <v>128356350</v>
       </c>
       <c r="B52" t="n">
-        <v>92652</v>
+        <v>92760</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5764,37 +5764,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565189</v>
+        <v>565128</v>
       </c>
       <c r="R52" t="n">
-        <v>6683740</v>
+        <v>6683651</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5838,60 +5838,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Patric Engfeldt, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356310</v>
+        <v>128353745</v>
       </c>
       <c r="B53" t="n">
-        <v>92652</v>
+        <v>92776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565306</v>
+        <v>565166</v>
       </c>
       <c r="R53" t="n">
-        <v>6683913</v>
+        <v>6683711</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128353737</v>
+        <v>128356360</v>
       </c>
       <c r="B54" t="n">
-        <v>86624</v>
+        <v>100753</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565164</v>
+        <v>565329</v>
       </c>
       <c r="R54" t="n">
-        <v>6683706</v>
+        <v>6683831</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6032,22 +6032,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356316</v>
+        <v>128353737</v>
       </c>
       <c r="B55" t="n">
-        <v>92684</v>
+        <v>86716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6055,46 +6055,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565125</v>
+        <v>565164</v>
       </c>
       <c r="R55" t="n">
-        <v>6683662</v>
+        <v>6683706</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6138,49 +6129,49 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356294</v>
+        <v>128356236</v>
       </c>
       <c r="B56" t="n">
-        <v>90895</v>
+        <v>92387</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6194,10 +6185,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565290</v>
+        <v>565136</v>
       </c>
       <c r="R56" t="n">
-        <v>6683893</v>
+        <v>6683697</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,54 +6247,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356320</v>
+        <v>128356356</v>
       </c>
       <c r="B57" t="n">
-        <v>92684</v>
+        <v>92760</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565213</v>
+        <v>565307</v>
       </c>
       <c r="R57" t="n">
-        <v>6683796</v>
+        <v>6683932</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,39 +6337,39 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356360</v>
+        <v>128356352</v>
       </c>
       <c r="B58" t="n">
-        <v>100660</v>
+        <v>92760</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6397,10 +6379,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565329</v>
+        <v>565124</v>
       </c>
       <c r="R58" t="n">
-        <v>6683831</v>
+        <v>6683563</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6452,17 +6434,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356236</v>
+        <v>128356257</v>
       </c>
       <c r="B59" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6489,7 +6471,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6503,10 +6485,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565136</v>
+        <v>565243</v>
       </c>
       <c r="R59" t="n">
-        <v>6683697</v>
+        <v>6683765</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,45 +6547,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356356</v>
+        <v>128356316</v>
       </c>
       <c r="B60" t="n">
-        <v>92668</v>
+        <v>92776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565307</v>
+        <v>565125</v>
       </c>
       <c r="R60" t="n">
-        <v>6683932</v>
+        <v>6683662</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,45 +6653,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356352</v>
+        <v>128356294</v>
       </c>
       <c r="B61" t="n">
-        <v>92668</v>
+        <v>90987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565124</v>
+        <v>565290</v>
       </c>
       <c r="R61" t="n">
-        <v>6683563</v>
+        <v>6683893</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128356257</v>
+        <v>128356320</v>
       </c>
       <c r="B62" t="n">
-        <v>92295</v>
+        <v>92776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6770,26 +6770,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565243</v>
+        <v>565213</v>
       </c>
       <c r="R62" t="n">
-        <v>6683765</v>
+        <v>6683796</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128356270</v>
+        <v>128356259</v>
       </c>
       <c r="B63" t="n">
-        <v>92662</v>
+        <v>92387</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,34 +6876,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565281</v>
+        <v>565167</v>
       </c>
       <c r="R63" t="n">
-        <v>6683884</v>
+        <v>6683728</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,7 +6974,7 @@
         <v>128353797</v>
       </c>
       <c r="B64" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7059,10 +7068,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356322</v>
+        <v>128356270</v>
       </c>
       <c r="B65" t="n">
-        <v>92684</v>
+        <v>92754</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,43 +7079,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565121</v>
+        <v>565281</v>
       </c>
       <c r="R65" t="n">
-        <v>6683569</v>
+        <v>6683884</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356259</v>
+        <v>128356322</v>
       </c>
       <c r="B66" t="n">
-        <v>92295</v>
+        <v>92776</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7176,26 +7176,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565167</v>
+        <v>565121</v>
       </c>
       <c r="R66" t="n">
-        <v>6683728</v>
+        <v>6683569</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128356361</v>
+        <v>128356261</v>
       </c>
       <c r="B67" t="n">
-        <v>100660</v>
+        <v>92387</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,34 +7282,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565330</v>
+        <v>565331</v>
       </c>
       <c r="R67" t="n">
-        <v>6683934</v>
+        <v>6683832</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,10 +7377,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128356261</v>
+        <v>128356361</v>
       </c>
       <c r="B68" t="n">
-        <v>92295</v>
+        <v>100753</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7379,43 +7388,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565331</v>
+        <v>565330</v>
       </c>
       <c r="R68" t="n">
-        <v>6683832</v>
+        <v>6683934</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
         <v>128356288</v>
       </c>
       <c r="B69" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7668,57 +7668,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356231</v>
+        <v>128354079</v>
       </c>
       <c r="B71" t="n">
-        <v>92295</v>
+        <v>92744</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565261</v>
+        <v>565281</v>
       </c>
       <c r="R71" t="n">
-        <v>6683777</v>
+        <v>6683847</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7762,12 +7753,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7777,7 +7768,7 @@
         <v>128356331</v>
       </c>
       <c r="B72" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7880,10 +7871,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354079</v>
+        <v>128354290</v>
       </c>
       <c r="B73" t="n">
-        <v>92652</v>
+        <v>86915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,21 +7882,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>788</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7915,10 +7906,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565281</v>
+        <v>565327</v>
       </c>
       <c r="R73" t="n">
-        <v>6683847</v>
+        <v>6683939</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7977,10 +7968,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128354308</v>
+        <v>128356231</v>
       </c>
       <c r="B74" t="n">
-        <v>100660</v>
+        <v>92387</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7988,37 +7979,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565341</v>
+        <v>565261</v>
       </c>
       <c r="R74" t="n">
-        <v>6683943</v>
+        <v>6683777</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,44 +8062,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354290</v>
+        <v>128354308</v>
       </c>
       <c r="B75" t="n">
-        <v>86823</v>
+        <v>100753</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565327</v>
+        <v>565341</v>
       </c>
       <c r="R75" t="n">
-        <v>6683939</v>
+        <v>6683943</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8174,7 +8174,7 @@
         <v>128353641</v>
       </c>
       <c r="B76" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8268,54 +8268,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128356315</v>
+        <v>128356344</v>
       </c>
       <c r="B77" t="n">
-        <v>92684</v>
+        <v>92760</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565123</v>
+        <v>565307</v>
       </c>
       <c r="R77" t="n">
-        <v>6683582</v>
+        <v>6683918</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8374,48 +8365,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128356344</v>
+        <v>128354183</v>
       </c>
       <c r="B78" t="n">
-        <v>92668</v>
+        <v>92387</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565307</v>
+        <v>565320</v>
       </c>
       <c r="R78" t="n">
         <v>6683918</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8459,22 +8450,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128354183</v>
+        <v>128356363</v>
       </c>
       <c r="B79" t="n">
-        <v>92295</v>
+        <v>100753</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8482,37 +8473,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565320</v>
+        <v>565298</v>
       </c>
       <c r="R79" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,22 +8547,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356363</v>
+        <v>128356315</v>
       </c>
       <c r="B80" t="n">
-        <v>100660</v>
+        <v>92776</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8579,34 +8570,43 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565298</v>
+        <v>565123</v>
       </c>
       <c r="R80" t="n">
-        <v>6683884</v>
+        <v>6683582</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8668,7 +8668,7 @@
         <v>128354266</v>
       </c>
       <c r="B81" t="n">
-        <v>86823</v>
+        <v>86915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>128356334</v>
       </c>
       <c r="B82" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>128356318</v>
       </c>
       <c r="B83" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>128356330</v>
       </c>
       <c r="B84" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>128379692</v>
       </c>
       <c r="B85" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128379701</v>
       </c>
       <c r="B86" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B3" t="n">
-        <v>100753</v>
+        <v>92776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R3" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,17 +871,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R4" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356311</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565121</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683581</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356324</v>
+        <v>128353720</v>
       </c>
       <c r="B6" t="n">
-        <v>92776</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,46 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565185</v>
+        <v>565171</v>
       </c>
       <c r="R6" t="n">
-        <v>6683745</v>
+        <v>6683703</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,22 +1157,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356335</v>
+        <v>128356237</v>
       </c>
       <c r="B7" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,34 +1180,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565323</v>
+        <v>565304</v>
       </c>
       <c r="R7" t="n">
-        <v>6683839</v>
+        <v>6683884</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1249,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,45 +1275,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356311</v>
+        <v>128356324</v>
       </c>
       <c r="B8" t="n">
-        <v>92744</v>
+        <v>92776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565121</v>
+        <v>565185</v>
       </c>
       <c r="R8" t="n">
-        <v>6683581</v>
+        <v>6683745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,10 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356237</v>
+        <v>128356335</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,43 +1392,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565304</v>
+        <v>565323</v>
       </c>
       <c r="R9" t="n">
-        <v>6683884</v>
+        <v>6683839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,6 +1452,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,57 +1686,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128356235</v>
+        <v>128353600</v>
       </c>
       <c r="B12" t="n">
-        <v>92387</v>
+        <v>92744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565149</v>
+        <v>565138</v>
       </c>
       <c r="R12" t="n">
-        <v>6683718</v>
+        <v>6683661</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,57 +1771,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356353</v>
+        <v>128356235</v>
       </c>
       <c r="B13" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565118</v>
+        <v>565149</v>
       </c>
       <c r="R13" t="n">
-        <v>6683561</v>
+        <v>6683718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,17 +1882,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128353600</v>
+        <v>128356353</v>
       </c>
       <c r="B14" t="n">
-        <v>92744</v>
+        <v>92760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,37 +1900,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565138</v>
+        <v>565118</v>
       </c>
       <c r="R14" t="n">
-        <v>6683661</v>
+        <v>6683561</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,12 +1974,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B17" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,46 +2200,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R17" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2283,22 +2274,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B18" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,37 +2297,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R18" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,19 +2380,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356342</v>
+        <v>128356349</v>
       </c>
       <c r="B19" t="n">
         <v>92760</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565338</v>
+        <v>565147</v>
       </c>
       <c r="R19" t="n">
-        <v>6683896</v>
+        <v>6683691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,45 +2489,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356338</v>
+        <v>128356319</v>
       </c>
       <c r="B20" t="n">
-        <v>92760</v>
+        <v>92776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565124</v>
+        <v>565206</v>
       </c>
       <c r="R20" t="n">
-        <v>6683659</v>
+        <v>6683808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,11 +2569,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,45 +2595,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356349</v>
+        <v>128356321</v>
       </c>
       <c r="B21" t="n">
-        <v>92760</v>
+        <v>92776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565147</v>
+        <v>565225</v>
       </c>
       <c r="R21" t="n">
-        <v>6683691</v>
+        <v>6683834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,54 +2701,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356319</v>
+        <v>128356342</v>
       </c>
       <c r="B22" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565206</v>
+        <v>565338</v>
       </c>
       <c r="R22" t="n">
-        <v>6683808</v>
+        <v>6683896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2794,54 +2798,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356321</v>
+        <v>128356338</v>
       </c>
       <c r="B23" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565225</v>
+        <v>565124</v>
       </c>
       <c r="R23" t="n">
-        <v>6683834</v>
+        <v>6683659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,6 +2869,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3620,48 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128354204</v>
+        <v>128356309</v>
       </c>
       <c r="B31" t="n">
-        <v>86878</v>
+        <v>92744</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>788</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565325</v>
+        <v>565184</v>
       </c>
       <c r="R31" t="n">
-        <v>6683920</v>
+        <v>6683739</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3705,60 +3705,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128356309</v>
+        <v>128354204</v>
       </c>
       <c r="B32" t="n">
-        <v>92744</v>
+        <v>86878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>788</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565184</v>
+        <v>565325</v>
       </c>
       <c r="R32" t="n">
-        <v>6683739</v>
+        <v>6683920</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,12 +3802,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356343</v>
+        <v>128353904</v>
       </c>
       <c r="B34" t="n">
         <v>92760</v>
@@ -3951,17 +3951,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565300</v>
+        <v>565224</v>
       </c>
       <c r="R34" t="n">
-        <v>6683931</v>
+        <v>6683766</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4005,66 +4005,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356250</v>
+        <v>128356343</v>
       </c>
       <c r="B35" t="n">
-        <v>92387</v>
+        <v>92760</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565136</v>
+        <v>565300</v>
       </c>
       <c r="R35" t="n">
-        <v>6683681</v>
+        <v>6683931</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,45 +4114,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356336</v>
+        <v>128356250</v>
       </c>
       <c r="B36" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565294</v>
+        <v>565136</v>
       </c>
       <c r="R36" t="n">
-        <v>6683885</v>
+        <v>6683681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,48 +4220,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128354354</v>
+        <v>128356336</v>
       </c>
       <c r="B37" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565289</v>
+        <v>565294</v>
       </c>
       <c r="R37" t="n">
-        <v>6683828</v>
+        <v>6683885</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4296,6 +4291,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4310,12 +4310,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4419,32 +4419,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128353904</v>
+        <v>128354354</v>
       </c>
       <c r="B39" t="n">
-        <v>92760</v>
+        <v>92776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565224</v>
+        <v>565289</v>
       </c>
       <c r="R39" t="n">
-        <v>6683766</v>
+        <v>6683828</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4516,37 +4516,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356252</v>
+        <v>128356219</v>
       </c>
       <c r="B40" t="n">
-        <v>92387</v>
+        <v>90972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>256335</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565313</v>
+        <v>565287</v>
       </c>
       <c r="R40" t="n">
-        <v>6683875</v>
+        <v>6683892</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4604,6 +4604,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4622,7 +4623,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356240</v>
+        <v>128356252</v>
       </c>
       <c r="B41" t="n">
         <v>92387</v>
@@ -4652,7 +4653,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4667,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R41" t="n">
-        <v>6683931</v>
+        <v>6683875</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,7 +4729,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356234</v>
+        <v>128356240</v>
       </c>
       <c r="B42" t="n">
         <v>92387</v>
@@ -4758,7 +4759,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565304</v>
+        <v>565298</v>
       </c>
       <c r="R42" t="n">
-        <v>6683798</v>
+        <v>6683931</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4834,10 +4835,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356326</v>
+        <v>128356234</v>
       </c>
       <c r="B43" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4845,26 +4846,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565306</v>
+        <v>565304</v>
       </c>
       <c r="R43" t="n">
-        <v>6683915</v>
+        <v>6683798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4940,37 +4941,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356219</v>
+        <v>128356326</v>
       </c>
       <c r="B44" t="n">
-        <v>90972</v>
+        <v>92776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256335</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4984,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565287</v>
+        <v>565306</v>
       </c>
       <c r="R44" t="n">
-        <v>6683892</v>
+        <v>6683915</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,7 +5029,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5356,54 +5356,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128356374</v>
+        <v>128356350</v>
       </c>
       <c r="B48" t="n">
-        <v>86878</v>
+        <v>92760</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565325</v>
+        <v>565128</v>
       </c>
       <c r="R48" t="n">
-        <v>6683931</v>
+        <v>6683651</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5455,55 +5446,55 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128356307</v>
+        <v>128353745</v>
       </c>
       <c r="B49" t="n">
-        <v>92744</v>
+        <v>92776</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565193</v>
+        <v>565166</v>
       </c>
       <c r="R49" t="n">
-        <v>6683755</v>
+        <v>6683711</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5547,19 +5538,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128353808</v>
+        <v>128356307</v>
       </c>
       <c r="B50" t="n">
         <v>92744</v>
@@ -5590,17 +5581,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565189</v>
+        <v>565193</v>
       </c>
       <c r="R50" t="n">
-        <v>6683740</v>
+        <v>6683755</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5644,19 +5635,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128356310</v>
+        <v>128353808</v>
       </c>
       <c r="B51" t="n">
         <v>92744</v>
@@ -5687,17 +5678,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565306</v>
+        <v>565189</v>
       </c>
       <c r="R51" t="n">
-        <v>6683913</v>
+        <v>6683740</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5741,22 +5732,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128356350</v>
+        <v>128356310</v>
       </c>
       <c r="B52" t="n">
-        <v>92760</v>
+        <v>92744</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5764,21 +5755,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5788,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565128</v>
+        <v>565306</v>
       </c>
       <c r="R52" t="n">
-        <v>6683651</v>
+        <v>6683913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,17 +5834,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128353745</v>
+        <v>128356374</v>
       </c>
       <c r="B53" t="n">
-        <v>92776</v>
+        <v>86878</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5861,37 +5852,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565166</v>
+        <v>565325</v>
       </c>
       <c r="R53" t="n">
-        <v>6683711</v>
+        <v>6683931</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356360</v>
+        <v>128353737</v>
       </c>
       <c r="B54" t="n">
-        <v>100753</v>
+        <v>86716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565329</v>
+        <v>565164</v>
       </c>
       <c r="R54" t="n">
-        <v>6683831</v>
+        <v>6683706</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6032,22 +6032,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128353737</v>
+        <v>128356236</v>
       </c>
       <c r="B55" t="n">
-        <v>86716</v>
+        <v>92387</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6055,37 +6055,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565164</v>
+        <v>565136</v>
       </c>
       <c r="R55" t="n">
-        <v>6683706</v>
+        <v>6683697</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6129,66 +6138,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356236</v>
+        <v>128356356</v>
       </c>
       <c r="B56" t="n">
-        <v>92387</v>
+        <v>92760</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565136</v>
+        <v>565307</v>
       </c>
       <c r="R56" t="n">
-        <v>6683697</v>
+        <v>6683932</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6247,7 +6247,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356356</v>
+        <v>128356352</v>
       </c>
       <c r="B57" t="n">
         <v>92760</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565307</v>
+        <v>565124</v>
       </c>
       <c r="R57" t="n">
-        <v>6683932</v>
+        <v>6683563</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6337,52 +6337,61 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356352</v>
+        <v>128356257</v>
       </c>
       <c r="B58" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565124</v>
+        <v>565243</v>
       </c>
       <c r="R58" t="n">
-        <v>6683563</v>
+        <v>6683765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6434,17 +6443,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356257</v>
+        <v>128356316</v>
       </c>
       <c r="B59" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6452,26 +6461,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6485,10 +6494,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565243</v>
+        <v>565125</v>
       </c>
       <c r="R59" t="n">
-        <v>6683765</v>
+        <v>6683662</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,37 +6556,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356316</v>
+        <v>128356294</v>
       </c>
       <c r="B60" t="n">
-        <v>92776</v>
+        <v>90987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6591,10 +6600,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565125</v>
+        <v>565290</v>
       </c>
       <c r="R60" t="n">
-        <v>6683662</v>
+        <v>6683893</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6653,37 +6662,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356294</v>
+        <v>128356320</v>
       </c>
       <c r="B61" t="n">
-        <v>90987</v>
+        <v>92776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6697,10 +6706,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565290</v>
+        <v>565213</v>
       </c>
       <c r="R61" t="n">
-        <v>6683893</v>
+        <v>6683796</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6752,17 +6761,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128356320</v>
+        <v>128356360</v>
       </c>
       <c r="B62" t="n">
-        <v>92776</v>
+        <v>100753</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6770,43 +6779,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565213</v>
+        <v>565329</v>
       </c>
       <c r="R62" t="n">
-        <v>6683796</v>
+        <v>6683831</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128356259</v>
+        <v>128353797</v>
       </c>
       <c r="B63" t="n">
-        <v>92387</v>
+        <v>86716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,46 +6876,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565167</v>
+        <v>565197</v>
       </c>
       <c r="R63" t="n">
-        <v>6683728</v>
+        <v>6683732</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6959,22 +6950,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128353797</v>
+        <v>128356259</v>
       </c>
       <c r="B64" t="n">
-        <v>86716</v>
+        <v>92387</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6982,37 +6973,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565197</v>
+        <v>565167</v>
       </c>
       <c r="R64" t="n">
-        <v>6683732</v>
+        <v>6683728</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7056,12 +7056,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7467,55 +7467,55 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128356288</v>
+        <v>128354079</v>
       </c>
       <c r="B69" t="n">
-        <v>86716</v>
+        <v>92744</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565128</v>
+        <v>565281</v>
       </c>
       <c r="R69" t="n">
-        <v>6683644</v>
+        <v>6683847</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7559,22 +7559,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356286</v>
+        <v>128356231</v>
       </c>
       <c r="B70" t="n">
-        <v>86716</v>
+        <v>92387</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7582,34 +7582,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565257</v>
+        <v>565261</v>
       </c>
       <c r="R70" t="n">
-        <v>6683775</v>
+        <v>6683777</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7668,48 +7677,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128354079</v>
+        <v>128356331</v>
       </c>
       <c r="B71" t="n">
-        <v>92744</v>
+        <v>92776</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565281</v>
+        <v>565298</v>
       </c>
       <c r="R71" t="n">
-        <v>6683847</v>
+        <v>6683926</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7753,22 +7771,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356331</v>
+        <v>128354308</v>
       </c>
       <c r="B72" t="n">
-        <v>92776</v>
+        <v>100753</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7776,46 +7794,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565298</v>
+        <v>565341</v>
       </c>
       <c r="R72" t="n">
-        <v>6683926</v>
+        <v>6683943</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7859,12 +7868,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7968,10 +7977,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128356231</v>
+        <v>128356288</v>
       </c>
       <c r="B74" t="n">
-        <v>92387</v>
+        <v>86716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7979,43 +7988,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565261</v>
+        <v>565128</v>
       </c>
       <c r="R74" t="n">
-        <v>6683777</v>
+        <v>6683644</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8074,10 +8074,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354308</v>
+        <v>128356286</v>
       </c>
       <c r="B75" t="n">
-        <v>100753</v>
+        <v>86716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8085,37 +8085,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565341</v>
+        <v>565257</v>
       </c>
       <c r="R75" t="n">
-        <v>6683943</v>
+        <v>6683775</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8159,12 +8159,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Janolof Hermansson, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B3" t="n">
-        <v>92776</v>
+        <v>100753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R3" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R4" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356311</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92744</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565121</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683581</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128353720</v>
+        <v>128356237</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565171</v>
+        <v>565304</v>
       </c>
       <c r="R6" t="n">
-        <v>6683703</v>
+        <v>6683884</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,66 +1166,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356237</v>
+        <v>128356311</v>
       </c>
       <c r="B7" t="n">
-        <v>92387</v>
+        <v>92744</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565304</v>
+        <v>565121</v>
       </c>
       <c r="R7" t="n">
-        <v>6683884</v>
+        <v>6683581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1686,48 +1686,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128353600</v>
+        <v>128356235</v>
       </c>
       <c r="B12" t="n">
-        <v>92744</v>
+        <v>92387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565138</v>
+        <v>565149</v>
       </c>
       <c r="R12" t="n">
-        <v>6683661</v>
+        <v>6683718</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,66 +1780,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356235</v>
+        <v>128356353</v>
       </c>
       <c r="B13" t="n">
-        <v>92387</v>
+        <v>92760</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565149</v>
+        <v>565118</v>
       </c>
       <c r="R13" t="n">
-        <v>6683718</v>
+        <v>6683561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,48 +1889,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356353</v>
+        <v>128353570</v>
       </c>
       <c r="B14" t="n">
-        <v>92760</v>
+        <v>92776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565118</v>
+        <v>565129</v>
       </c>
       <c r="R14" t="n">
-        <v>6683561</v>
+        <v>6683660</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353570</v>
+        <v>128356325</v>
       </c>
       <c r="B15" t="n">
         <v>92776</v>
@@ -2014,20 +2014,29 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565129</v>
+        <v>565139</v>
       </c>
       <c r="R15" t="n">
-        <v>6683660</v>
+        <v>6683679</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,69 +2080,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356325</v>
+        <v>128353600</v>
       </c>
       <c r="B16" t="n">
-        <v>92776</v>
+        <v>92744</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565139</v>
+        <v>565138</v>
       </c>
       <c r="R16" t="n">
-        <v>6683679</v>
+        <v>6683661</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356349</v>
+        <v>128356342</v>
       </c>
       <c r="B19" t="n">
         <v>92760</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565147</v>
+        <v>565338</v>
       </c>
       <c r="R19" t="n">
-        <v>6683691</v>
+        <v>6683896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,54 +2489,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356319</v>
+        <v>128356338</v>
       </c>
       <c r="B20" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565206</v>
+        <v>565124</v>
       </c>
       <c r="R20" t="n">
-        <v>6683808</v>
+        <v>6683659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2569,6 +2560,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,54 +2591,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356321</v>
+        <v>128356349</v>
       </c>
       <c r="B21" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565225</v>
+        <v>565147</v>
       </c>
       <c r="R21" t="n">
-        <v>6683834</v>
+        <v>6683691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,45 +2688,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356342</v>
+        <v>128356319</v>
       </c>
       <c r="B22" t="n">
-        <v>92760</v>
+        <v>92776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565338</v>
+        <v>565206</v>
       </c>
       <c r="R22" t="n">
-        <v>6683896</v>
+        <v>6683808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2798,45 +2794,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356338</v>
+        <v>128356321</v>
       </c>
       <c r="B23" t="n">
-        <v>92760</v>
+        <v>92776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565124</v>
+        <v>565225</v>
       </c>
       <c r="R23" t="n">
-        <v>6683659</v>
+        <v>6683834</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2869,11 +2874,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356255</v>
+        <v>128354354</v>
       </c>
       <c r="B33" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,46 +3825,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565128</v>
+        <v>565289</v>
       </c>
       <c r="R33" t="n">
-        <v>6683585</v>
+        <v>6683828</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3908,60 +3899,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128353904</v>
+        <v>128356276</v>
       </c>
       <c r="B34" t="n">
-        <v>92760</v>
+        <v>97448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4368</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565224</v>
+        <v>565383</v>
       </c>
       <c r="R34" t="n">
-        <v>6683766</v>
+        <v>6683939</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4005,57 +3996,66 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356343</v>
+        <v>128356255</v>
       </c>
       <c r="B35" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565300</v>
+        <v>565128</v>
       </c>
       <c r="R35" t="n">
-        <v>6683931</v>
+        <v>6683585</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4114,57 +4114,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356250</v>
+        <v>128353904</v>
       </c>
       <c r="B36" t="n">
-        <v>92387</v>
+        <v>92760</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565136</v>
+        <v>565224</v>
       </c>
       <c r="R36" t="n">
-        <v>6683681</v>
+        <v>6683766</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4208,19 +4199,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356336</v>
+        <v>128356343</v>
       </c>
       <c r="B37" t="n">
         <v>92760</v>
@@ -4255,10 +4246,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565294</v>
+        <v>565300</v>
       </c>
       <c r="R37" t="n">
-        <v>6683885</v>
+        <v>6683931</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,11 +4282,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4322,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128356276</v>
+        <v>128356250</v>
       </c>
       <c r="B38" t="n">
-        <v>97448</v>
+        <v>92387</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4333,34 +4319,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565383</v>
+        <v>565136</v>
       </c>
       <c r="R38" t="n">
-        <v>6683939</v>
+        <v>6683681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4419,48 +4414,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128354354</v>
+        <v>128356336</v>
       </c>
       <c r="B39" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565289</v>
+        <v>565294</v>
       </c>
       <c r="R39" t="n">
-        <v>6683828</v>
+        <v>6683885</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4490,6 +4485,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4504,49 +4504,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356219</v>
+        <v>128356252</v>
       </c>
       <c r="B40" t="n">
-        <v>90972</v>
+        <v>92387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>256335</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565287</v>
+        <v>565313</v>
       </c>
       <c r="R40" t="n">
-        <v>6683892</v>
+        <v>6683875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4604,7 +4604,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4623,7 +4622,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356252</v>
+        <v>128356240</v>
       </c>
       <c r="B41" t="n">
         <v>92387</v>
@@ -4653,7 +4652,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4667,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565313</v>
+        <v>565298</v>
       </c>
       <c r="R41" t="n">
-        <v>6683875</v>
+        <v>6683931</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4729,7 +4728,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356240</v>
+        <v>128356234</v>
       </c>
       <c r="B42" t="n">
         <v>92387</v>
@@ -4759,7 +4758,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4773,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565298</v>
+        <v>565304</v>
       </c>
       <c r="R42" t="n">
-        <v>6683931</v>
+        <v>6683798</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,10 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356234</v>
+        <v>128356326</v>
       </c>
       <c r="B43" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4846,26 +4845,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4879,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565304</v>
+        <v>565306</v>
       </c>
       <c r="R43" t="n">
-        <v>6683798</v>
+        <v>6683915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,37 +4940,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356326</v>
+        <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>92776</v>
+        <v>90972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>256335</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4985,10 +4984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565306</v>
+        <v>565287</v>
       </c>
       <c r="R44" t="n">
-        <v>6683915</v>
+        <v>6683892</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,6 +5028,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5356,10 +5356,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128356350</v>
+        <v>128356307</v>
       </c>
       <c r="B48" t="n">
-        <v>92760</v>
+        <v>92744</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5367,21 +5367,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565128</v>
+        <v>565193</v>
       </c>
       <c r="R48" t="n">
-        <v>6683651</v>
+        <v>6683755</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,45 +5453,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128353745</v>
+        <v>128353808</v>
       </c>
       <c r="B49" t="n">
-        <v>92776</v>
+        <v>92744</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565166</v>
+        <v>565189</v>
       </c>
       <c r="R49" t="n">
-        <v>6683711</v>
+        <v>6683740</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356307</v>
+        <v>128356310</v>
       </c>
       <c r="B50" t="n">
         <v>92744</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565193</v>
+        <v>565306</v>
       </c>
       <c r="R50" t="n">
-        <v>6683755</v>
+        <v>6683913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,48 +5647,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128353808</v>
+        <v>128356374</v>
       </c>
       <c r="B51" t="n">
-        <v>92744</v>
+        <v>86878</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>788</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565189</v>
+        <v>565325</v>
       </c>
       <c r="R51" t="n">
-        <v>6683740</v>
+        <v>6683931</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5732,22 +5741,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128356310</v>
+        <v>128356350</v>
       </c>
       <c r="B52" t="n">
-        <v>92744</v>
+        <v>92760</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5755,21 +5764,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5779,10 +5788,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565306</v>
+        <v>565128</v>
       </c>
       <c r="R52" t="n">
-        <v>6683913</v>
+        <v>6683651</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,10 +5850,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356374</v>
+        <v>128353745</v>
       </c>
       <c r="B53" t="n">
-        <v>86878</v>
+        <v>92776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,46 +5861,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565325</v>
+        <v>565166</v>
       </c>
       <c r="R53" t="n">
-        <v>6683931</v>
+        <v>6683711</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128353737</v>
+        <v>128356360</v>
       </c>
       <c r="B54" t="n">
-        <v>86716</v>
+        <v>100753</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565164</v>
+        <v>565329</v>
       </c>
       <c r="R54" t="n">
-        <v>6683706</v>
+        <v>6683831</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6032,12 +6032,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356316</v>
+        <v>128353737</v>
       </c>
       <c r="B59" t="n">
-        <v>92776</v>
+        <v>86716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6461,46 +6461,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565125</v>
+        <v>565164</v>
       </c>
       <c r="R59" t="n">
-        <v>6683662</v>
+        <v>6683706</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6544,12 +6535,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6662,7 +6653,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356320</v>
+        <v>128356316</v>
       </c>
       <c r="B61" t="n">
         <v>92776</v>
@@ -6692,7 +6683,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6706,10 +6697,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565213</v>
+        <v>565125</v>
       </c>
       <c r="R61" t="n">
-        <v>6683796</v>
+        <v>6683662</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6761,17 +6752,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128356360</v>
+        <v>128356320</v>
       </c>
       <c r="B62" t="n">
-        <v>100753</v>
+        <v>92776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6779,34 +6770,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565329</v>
+        <v>565213</v>
       </c>
       <c r="R62" t="n">
-        <v>6683831</v>
+        <v>6683796</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7474,48 +7474,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128354079</v>
+        <v>128356288</v>
       </c>
       <c r="B69" t="n">
-        <v>92744</v>
+        <v>86716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565281</v>
+        <v>565128</v>
       </c>
       <c r="R69" t="n">
-        <v>6683847</v>
+        <v>6683644</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7559,22 +7559,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356231</v>
+        <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>92387</v>
+        <v>86716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7582,43 +7582,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565261</v>
+        <v>565257</v>
       </c>
       <c r="R70" t="n">
-        <v>6683777</v>
+        <v>6683775</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,10 +7668,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356331</v>
+        <v>128356231</v>
       </c>
       <c r="B71" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7688,26 +7679,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7721,10 +7712,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565298</v>
+        <v>565261</v>
       </c>
       <c r="R71" t="n">
-        <v>6683926</v>
+        <v>6683777</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7783,10 +7774,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128354308</v>
+        <v>128356331</v>
       </c>
       <c r="B72" t="n">
-        <v>100753</v>
+        <v>92776</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7794,37 +7785,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565341</v>
+        <v>565298</v>
       </c>
       <c r="R72" t="n">
-        <v>6683943</v>
+        <v>6683926</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7868,22 +7868,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354290</v>
+        <v>128354079</v>
       </c>
       <c r="B73" t="n">
-        <v>86915</v>
+        <v>92744</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>788</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565327</v>
+        <v>565281</v>
       </c>
       <c r="R73" t="n">
-        <v>6683939</v>
+        <v>6683847</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7977,10 +7977,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128356288</v>
+        <v>128354308</v>
       </c>
       <c r="B74" t="n">
-        <v>86716</v>
+        <v>100753</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7988,37 +7988,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565128</v>
+        <v>565341</v>
       </c>
       <c r="R74" t="n">
-        <v>6683644</v>
+        <v>6683943</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,60 +8062,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128356286</v>
+        <v>128354290</v>
       </c>
       <c r="B75" t="n">
-        <v>86716</v>
+        <v>86915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565257</v>
+        <v>565327</v>
       </c>
       <c r="R75" t="n">
-        <v>6683775</v>
+        <v>6683939</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8159,22 +8159,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128353641</v>
+        <v>128356315</v>
       </c>
       <c r="B76" t="n">
-        <v>86716</v>
+        <v>92776</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,37 +8182,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565149</v>
+        <v>565123</v>
       </c>
       <c r="R76" t="n">
-        <v>6683686</v>
+        <v>6683582</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8256,44 +8265,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128356344</v>
+        <v>128356363</v>
       </c>
       <c r="B77" t="n">
-        <v>92760</v>
+        <v>100753</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8303,10 +8312,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565307</v>
+        <v>565298</v>
       </c>
       <c r="R77" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8365,32 +8374,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128354183</v>
+        <v>128354266</v>
       </c>
       <c r="B78" t="n">
-        <v>92387</v>
+        <v>86915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8400,10 +8409,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565320</v>
+        <v>565313</v>
       </c>
       <c r="R78" t="n">
-        <v>6683918</v>
+        <v>6683939</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8462,10 +8471,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356363</v>
+        <v>128353641</v>
       </c>
       <c r="B79" t="n">
-        <v>100753</v>
+        <v>86716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8473,37 +8482,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565298</v>
+        <v>565149</v>
       </c>
       <c r="R79" t="n">
-        <v>6683884</v>
+        <v>6683686</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8547,66 +8556,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356315</v>
+        <v>128356344</v>
       </c>
       <c r="B80" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565123</v>
+        <v>565307</v>
       </c>
       <c r="R80" t="n">
-        <v>6683582</v>
+        <v>6683918</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8665,32 +8665,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354266</v>
+        <v>128354183</v>
       </c>
       <c r="B81" t="n">
-        <v>86915</v>
+        <v>92387</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565313</v>
+        <v>565320</v>
       </c>
       <c r="R81" t="n">
-        <v>6683939</v>
+        <v>6683918</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -1686,57 +1686,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128356235</v>
+        <v>128353600</v>
       </c>
       <c r="B12" t="n">
-        <v>92387</v>
+        <v>92744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565149</v>
+        <v>565138</v>
       </c>
       <c r="R12" t="n">
-        <v>6683718</v>
+        <v>6683661</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,57 +1771,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356353</v>
+        <v>128356235</v>
       </c>
       <c r="B13" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565118</v>
+        <v>565149</v>
       </c>
       <c r="R13" t="n">
-        <v>6683561</v>
+        <v>6683718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,48 +1889,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128353570</v>
+        <v>128356353</v>
       </c>
       <c r="B14" t="n">
-        <v>92776</v>
+        <v>92760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565129</v>
+        <v>565118</v>
       </c>
       <c r="R14" t="n">
-        <v>6683660</v>
+        <v>6683561</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128356325</v>
+        <v>128353570</v>
       </c>
       <c r="B15" t="n">
         <v>92776</v>
@@ -2014,29 +2014,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565139</v>
+        <v>565129</v>
       </c>
       <c r="R15" t="n">
-        <v>6683679</v>
+        <v>6683660</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2080,60 +2071,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128353600</v>
+        <v>128356325</v>
       </c>
       <c r="B16" t="n">
-        <v>92744</v>
+        <v>92776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565138</v>
+        <v>565139</v>
       </c>
       <c r="R16" t="n">
-        <v>6683661</v>
+        <v>6683679</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128354204</v>
+        <v>128354354</v>
       </c>
       <c r="B32" t="n">
-        <v>86878</v>
+        <v>92776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565325</v>
+        <v>565289</v>
       </c>
       <c r="R32" t="n">
-        <v>6683920</v>
+        <v>6683828</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128354354</v>
+        <v>128356276</v>
       </c>
       <c r="B33" t="n">
-        <v>92776</v>
+        <v>97448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,37 +3825,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565289</v>
+        <v>565383</v>
       </c>
       <c r="R33" t="n">
-        <v>6683828</v>
+        <v>6683939</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3899,22 +3899,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356276</v>
+        <v>128354204</v>
       </c>
       <c r="B34" t="n">
-        <v>97448</v>
+        <v>86878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,37 +3922,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565383</v>
+        <v>565325</v>
       </c>
       <c r="R34" t="n">
-        <v>6683939</v>
+        <v>6683920</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356348</v>
       </c>
       <c r="B2" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B3" t="n">
-        <v>100753</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R3" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>100768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R4" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356324</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565185</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683745</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1069,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356237</v>
+        <v>128356335</v>
       </c>
       <c r="B6" t="n">
-        <v>92387</v>
+        <v>92788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,43 +1092,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565304</v>
+        <v>565323</v>
       </c>
       <c r="R6" t="n">
-        <v>6683884</v>
+        <v>6683839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1152,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,48 +1183,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356311</v>
+        <v>128353720</v>
       </c>
       <c r="B7" t="n">
-        <v>92744</v>
+        <v>92766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565121</v>
+        <v>565171</v>
       </c>
       <c r="R7" t="n">
-        <v>6683581</v>
+        <v>6683703</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356324</v>
+        <v>128356237</v>
       </c>
       <c r="B8" t="n">
-        <v>92776</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,26 +1291,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565185</v>
+        <v>565304</v>
       </c>
       <c r="R8" t="n">
-        <v>6683745</v>
+        <v>6683884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356335</v>
+        <v>128356311</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565323</v>
+        <v>565121</v>
       </c>
       <c r="R9" t="n">
-        <v>6683839</v>
+        <v>6683581</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,11 +1457,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,7 +1486,7 @@
         <v>128356345</v>
       </c>
       <c r="B10" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128356260</v>
       </c>
       <c r="B11" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,48 +1686,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128353600</v>
+        <v>128356235</v>
       </c>
       <c r="B12" t="n">
-        <v>92744</v>
+        <v>92399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565138</v>
+        <v>565149</v>
       </c>
       <c r="R12" t="n">
-        <v>6683661</v>
+        <v>6683718</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,66 +1780,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356235</v>
+        <v>128356353</v>
       </c>
       <c r="B13" t="n">
-        <v>92387</v>
+        <v>92772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565149</v>
+        <v>565118</v>
       </c>
       <c r="R13" t="n">
-        <v>6683718</v>
+        <v>6683561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,48 +1889,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356353</v>
+        <v>128353570</v>
       </c>
       <c r="B14" t="n">
-        <v>92760</v>
+        <v>92788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565118</v>
+        <v>565129</v>
       </c>
       <c r="R14" t="n">
-        <v>6683561</v>
+        <v>6683660</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353570</v>
+        <v>128356325</v>
       </c>
       <c r="B15" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,20 +2014,29 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565129</v>
+        <v>565139</v>
       </c>
       <c r="R15" t="n">
-        <v>6683660</v>
+        <v>6683679</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,69 +2080,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356325</v>
+        <v>128353600</v>
       </c>
       <c r="B16" t="n">
-        <v>92776</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565139</v>
+        <v>565138</v>
       </c>
       <c r="R16" t="n">
-        <v>6683679</v>
+        <v>6683661</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
         <v>128353672</v>
       </c>
       <c r="B17" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128356245</v>
       </c>
       <c r="B18" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128356342</v>
       </c>
       <c r="B19" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>128356338</v>
       </c>
       <c r="B20" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>128356349</v>
       </c>
       <c r="B21" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>128356319</v>
       </c>
       <c r="B22" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>128356321</v>
       </c>
       <c r="B23" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128356323</v>
       </c>
       <c r="B24" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128356332</v>
       </c>
       <c r="B25" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128356333</v>
       </c>
       <c r="B26" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>128356287</v>
       </c>
       <c r="B27" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128356346</v>
       </c>
       <c r="B28" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128356337</v>
       </c>
       <c r="B29" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>128356248</v>
       </c>
       <c r="B30" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,48 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128356309</v>
+        <v>128354204</v>
       </c>
       <c r="B31" t="n">
-        <v>92744</v>
+        <v>86888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>788</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565184</v>
+        <v>565325</v>
       </c>
       <c r="R31" t="n">
-        <v>6683739</v>
+        <v>6683920</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3705,12 +3705,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
         <v>128354354</v>
       </c>
       <c r="B32" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128356276</v>
       </c>
       <c r="B33" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3911,48 +3911,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128354204</v>
+        <v>128356309</v>
       </c>
       <c r="B34" t="n">
-        <v>86878</v>
+        <v>92756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>788</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565325</v>
+        <v>565184</v>
       </c>
       <c r="R34" t="n">
-        <v>6683920</v>
+        <v>6683739</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
         <v>128356255</v>
       </c>
       <c r="B35" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128353904</v>
       </c>
       <c r="B36" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>128356343</v>
       </c>
       <c r="B37" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>128356250</v>
       </c>
       <c r="B38" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>128356336</v>
       </c>
       <c r="B39" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356252</v>
+        <v>128356326</v>
       </c>
       <c r="B40" t="n">
-        <v>92387</v>
+        <v>92788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,26 +4527,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565313</v>
+        <v>565306</v>
       </c>
       <c r="R40" t="n">
-        <v>6683875</v>
+        <v>6683915</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356240</v>
+        <v>128356252</v>
       </c>
       <c r="B41" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R41" t="n">
-        <v>6683931</v>
+        <v>6683875</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356234</v>
+        <v>128356240</v>
       </c>
       <c r="B42" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565304</v>
+        <v>565298</v>
       </c>
       <c r="R42" t="n">
-        <v>6683798</v>
+        <v>6683931</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356326</v>
+        <v>128356234</v>
       </c>
       <c r="B43" t="n">
-        <v>92776</v>
+        <v>92399</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4845,26 +4845,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565306</v>
+        <v>565304</v>
       </c>
       <c r="R43" t="n">
-        <v>6683915</v>
+        <v>6683798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
         <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>90972</v>
+        <v>90984</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128356262</v>
+        <v>128356317</v>
       </c>
       <c r="B45" t="n">
-        <v>92387</v>
+        <v>92788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5058,26 +5058,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565306</v>
+        <v>565188</v>
       </c>
       <c r="R45" t="n">
-        <v>6683913</v>
+        <v>6683735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,45 +5153,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356351</v>
+        <v>128356262</v>
       </c>
       <c r="B46" t="n">
-        <v>92760</v>
+        <v>92399</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565125</v>
+        <v>565306</v>
       </c>
       <c r="R46" t="n">
-        <v>6683620</v>
+        <v>6683913</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,54 +5259,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356317</v>
+        <v>128356351</v>
       </c>
       <c r="B47" t="n">
-        <v>92776</v>
+        <v>92772</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565188</v>
+        <v>565125</v>
       </c>
       <c r="R47" t="n">
-        <v>6683735</v>
+        <v>6683620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5356,45 +5356,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128356307</v>
+        <v>128356374</v>
       </c>
       <c r="B48" t="n">
-        <v>92744</v>
+        <v>86888</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>788</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565193</v>
+        <v>565325</v>
       </c>
       <c r="R48" t="n">
-        <v>6683755</v>
+        <v>6683931</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,45 +5462,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128353808</v>
+        <v>128353745</v>
       </c>
       <c r="B49" t="n">
-        <v>92744</v>
+        <v>92788</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565189</v>
+        <v>565166</v>
       </c>
       <c r="R49" t="n">
-        <v>6683740</v>
+        <v>6683711</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5550,10 +5559,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356310</v>
+        <v>128356307</v>
       </c>
       <c r="B50" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,10 +5594,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565306</v>
+        <v>565193</v>
       </c>
       <c r="R50" t="n">
-        <v>6683913</v>
+        <v>6683755</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,57 +5656,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128356374</v>
+        <v>128353808</v>
       </c>
       <c r="B51" t="n">
-        <v>86878</v>
+        <v>92756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>788</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565325</v>
+        <v>565189</v>
       </c>
       <c r="R51" t="n">
-        <v>6683931</v>
+        <v>6683740</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5741,22 +5741,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128356350</v>
+        <v>128356310</v>
       </c>
       <c r="B52" t="n">
-        <v>92760</v>
+        <v>92756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5764,21 +5764,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565128</v>
+        <v>565306</v>
       </c>
       <c r="R52" t="n">
-        <v>6683651</v>
+        <v>6683913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5850,48 +5850,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128353745</v>
+        <v>128356350</v>
       </c>
       <c r="B53" t="n">
-        <v>92776</v>
+        <v>92772</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565166</v>
+        <v>565128</v>
       </c>
       <c r="R53" t="n">
-        <v>6683711</v>
+        <v>6683651</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356360</v>
+        <v>128356316</v>
       </c>
       <c r="B54" t="n">
-        <v>100753</v>
+        <v>92788</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,34 +5958,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565329</v>
+        <v>565125</v>
       </c>
       <c r="R54" t="n">
-        <v>6683831</v>
+        <v>6683662</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6044,37 +6053,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356236</v>
+        <v>128356294</v>
       </c>
       <c r="B55" t="n">
-        <v>92387</v>
+        <v>90999</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6088,10 +6097,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565136</v>
+        <v>565290</v>
       </c>
       <c r="R55" t="n">
-        <v>6683697</v>
+        <v>6683893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6150,45 +6159,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356356</v>
+        <v>128356320</v>
       </c>
       <c r="B56" t="n">
-        <v>92760</v>
+        <v>92788</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565307</v>
+        <v>565213</v>
       </c>
       <c r="R56" t="n">
-        <v>6683932</v>
+        <v>6683796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6247,45 +6265,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356352</v>
+        <v>128356236</v>
       </c>
       <c r="B57" t="n">
-        <v>92760</v>
+        <v>92399</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565124</v>
+        <v>565136</v>
       </c>
       <c r="R57" t="n">
-        <v>6683563</v>
+        <v>6683697</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6344,54 +6371,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356257</v>
+        <v>128356356</v>
       </c>
       <c r="B58" t="n">
-        <v>92387</v>
+        <v>92772</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565243</v>
+        <v>565307</v>
       </c>
       <c r="R58" t="n">
-        <v>6683765</v>
+        <v>6683932</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,48 +6468,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128353737</v>
+        <v>128356352</v>
       </c>
       <c r="B59" t="n">
-        <v>86716</v>
+        <v>92772</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565164</v>
+        <v>565124</v>
       </c>
       <c r="R59" t="n">
-        <v>6683706</v>
+        <v>6683563</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6535,69 +6553,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356294</v>
+        <v>128353737</v>
       </c>
       <c r="B60" t="n">
-        <v>90987</v>
+        <v>86727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>3762</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565290</v>
+        <v>565164</v>
       </c>
       <c r="R60" t="n">
-        <v>6683893</v>
+        <v>6683706</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6641,22 +6650,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356316</v>
+        <v>128356257</v>
       </c>
       <c r="B61" t="n">
-        <v>92776</v>
+        <v>92399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6664,26 +6673,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6697,10 +6706,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565125</v>
+        <v>565243</v>
       </c>
       <c r="R61" t="n">
-        <v>6683662</v>
+        <v>6683765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6759,10 +6768,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128356320</v>
+        <v>128356360</v>
       </c>
       <c r="B62" t="n">
-        <v>92776</v>
+        <v>100768</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6770,43 +6779,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565213</v>
+        <v>565329</v>
       </c>
       <c r="R62" t="n">
-        <v>6683796</v>
+        <v>6683831</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6868,7 +6868,7 @@
         <v>128353797</v>
       </c>
       <c r="B63" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356259</v>
+        <v>128356322</v>
       </c>
       <c r="B64" t="n">
-        <v>92387</v>
+        <v>92788</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,26 +6973,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565167</v>
+        <v>565121</v>
       </c>
       <c r="R64" t="n">
-        <v>6683728</v>
+        <v>6683569</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356270</v>
+        <v>128356259</v>
       </c>
       <c r="B65" t="n">
-        <v>92754</v>
+        <v>92399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,34 +7079,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565281</v>
+        <v>565167</v>
       </c>
       <c r="R65" t="n">
-        <v>6683884</v>
+        <v>6683728</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,10 +7174,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356322</v>
+        <v>128356270</v>
       </c>
       <c r="B66" t="n">
-        <v>92776</v>
+        <v>92766</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7176,43 +7185,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565121</v>
+        <v>565281</v>
       </c>
       <c r="R66" t="n">
-        <v>6683569</v>
+        <v>6683884</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
         <v>128356261</v>
       </c>
       <c r="B67" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>128356361</v>
       </c>
       <c r="B68" t="n">
-        <v>100753</v>
+        <v>100768</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7474,48 +7474,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128356288</v>
+        <v>128354290</v>
       </c>
       <c r="B69" t="n">
-        <v>86716</v>
+        <v>86925</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565128</v>
+        <v>565327</v>
       </c>
       <c r="R69" t="n">
-        <v>6683644</v>
+        <v>6683939</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7559,12 +7559,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
         <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356231</v>
+        <v>128356331</v>
       </c>
       <c r="B71" t="n">
-        <v>92387</v>
+        <v>92788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7679,26 +7679,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565261</v>
+        <v>565298</v>
       </c>
       <c r="R71" t="n">
-        <v>6683777</v>
+        <v>6683926</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7774,57 +7774,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356331</v>
+        <v>128354079</v>
       </c>
       <c r="B72" t="n">
-        <v>92776</v>
+        <v>92756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565298</v>
+        <v>565281</v>
       </c>
       <c r="R72" t="n">
-        <v>6683926</v>
+        <v>6683847</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7868,60 +7859,69 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354079</v>
+        <v>128356231</v>
       </c>
       <c r="B73" t="n">
-        <v>92744</v>
+        <v>92399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565281</v>
+        <v>565261</v>
       </c>
       <c r="R73" t="n">
-        <v>6683847</v>
+        <v>6683777</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7965,22 +7965,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128354308</v>
+        <v>128356288</v>
       </c>
       <c r="B74" t="n">
-        <v>100753</v>
+        <v>86727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7988,37 +7988,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565341</v>
+        <v>565128</v>
       </c>
       <c r="R74" t="n">
-        <v>6683943</v>
+        <v>6683644</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,44 +8062,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354290</v>
+        <v>128354308</v>
       </c>
       <c r="B75" t="n">
-        <v>86915</v>
+        <v>100768</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565327</v>
+        <v>565341</v>
       </c>
       <c r="R75" t="n">
-        <v>6683939</v>
+        <v>6683943</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8171,10 +8171,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356315</v>
+        <v>128353641</v>
       </c>
       <c r="B76" t="n">
-        <v>92776</v>
+        <v>86727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,46 +8182,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565123</v>
+        <v>565149</v>
       </c>
       <c r="R76" t="n">
-        <v>6683582</v>
+        <v>6683686</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8265,22 +8256,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128356363</v>
+        <v>128354183</v>
       </c>
       <c r="B77" t="n">
-        <v>100753</v>
+        <v>92399</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8288,37 +8279,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565298</v>
+        <v>565320</v>
       </c>
       <c r="R77" t="n">
-        <v>6683884</v>
+        <v>6683918</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8362,60 +8353,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128354266</v>
+        <v>128356363</v>
       </c>
       <c r="B78" t="n">
-        <v>86915</v>
+        <v>100768</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565313</v>
+        <v>565298</v>
       </c>
       <c r="R78" t="n">
-        <v>6683939</v>
+        <v>6683884</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8459,22 +8450,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128353641</v>
+        <v>128356315</v>
       </c>
       <c r="B79" t="n">
-        <v>86716</v>
+        <v>92788</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8482,37 +8473,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565149</v>
+        <v>565123</v>
       </c>
       <c r="R79" t="n">
-        <v>6683686</v>
+        <v>6683582</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,12 +8556,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8571,7 +8571,7 @@
         <v>128356344</v>
       </c>
       <c r="B80" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,32 +8665,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354183</v>
+        <v>128354266</v>
       </c>
       <c r="B81" t="n">
-        <v>92387</v>
+        <v>86925</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565320</v>
+        <v>565313</v>
       </c>
       <c r="R81" t="n">
-        <v>6683918</v>
+        <v>6683939</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8765,7 +8765,7 @@
         <v>128356334</v>
       </c>
       <c r="B82" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>128356318</v>
       </c>
       <c r="B83" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>128356330</v>
       </c>
       <c r="B84" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>128379692</v>
       </c>
       <c r="B85" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128379701</v>
       </c>
       <c r="B86" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356324</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,46 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565185</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683745</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356335</v>
+        <v>128356237</v>
       </c>
       <c r="B6" t="n">
-        <v>92788</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,34 +1083,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565323</v>
+        <v>565304</v>
       </c>
       <c r="R6" t="n">
-        <v>6683839</v>
+        <v>6683884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128353720</v>
+        <v>128356324</v>
       </c>
       <c r="B7" t="n">
-        <v>92766</v>
+        <v>92788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1189,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565171</v>
+        <v>565185</v>
       </c>
       <c r="R7" t="n">
-        <v>6683703</v>
+        <v>6683745</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,22 +1272,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356237</v>
+        <v>128356335</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,43 +1295,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565304</v>
+        <v>565323</v>
       </c>
       <c r="R8" t="n">
-        <v>6683884</v>
+        <v>6683839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B17" t="n">
-        <v>92788</v>
+        <v>92399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,37 +2200,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R17" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2274,22 +2283,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B18" t="n">
-        <v>92399</v>
+        <v>92788</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,46 +2306,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R18" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,57 +2380,66 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356342</v>
+        <v>128356319</v>
       </c>
       <c r="B19" t="n">
-        <v>92772</v>
+        <v>92788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565338</v>
+        <v>565206</v>
       </c>
       <c r="R19" t="n">
-        <v>6683896</v>
+        <v>6683808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,45 +2498,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356338</v>
+        <v>128356321</v>
       </c>
       <c r="B20" t="n">
-        <v>92772</v>
+        <v>92788</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565124</v>
+        <v>565225</v>
       </c>
       <c r="R20" t="n">
-        <v>6683659</v>
+        <v>6683834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,11 +2578,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,7 +2604,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356349</v>
+        <v>128356342</v>
       </c>
       <c r="B21" t="n">
         <v>92772</v>
@@ -2626,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565147</v>
+        <v>565338</v>
       </c>
       <c r="R21" t="n">
-        <v>6683691</v>
+        <v>6683896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,54 +2701,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356319</v>
+        <v>128356338</v>
       </c>
       <c r="B22" t="n">
-        <v>92788</v>
+        <v>92772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565206</v>
+        <v>565124</v>
       </c>
       <c r="R22" t="n">
-        <v>6683808</v>
+        <v>6683659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,6 +2772,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2794,54 +2803,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356321</v>
+        <v>128356349</v>
       </c>
       <c r="B23" t="n">
-        <v>92788</v>
+        <v>92772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565225</v>
+        <v>565147</v>
       </c>
       <c r="R23" t="n">
-        <v>6683834</v>
+        <v>6683691</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128354354</v>
+        <v>128356255</v>
       </c>
       <c r="B32" t="n">
-        <v>92788</v>
+        <v>92399</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,37 +3728,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565289</v>
+        <v>565128</v>
       </c>
       <c r="R32" t="n">
-        <v>6683828</v>
+        <v>6683585</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,60 +3811,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356276</v>
+        <v>128353904</v>
       </c>
       <c r="B33" t="n">
-        <v>97460</v>
+        <v>92772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>4368</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565383</v>
+        <v>565224</v>
       </c>
       <c r="R33" t="n">
-        <v>6683939</v>
+        <v>6683766</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3899,22 +3908,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356309</v>
+        <v>128356343</v>
       </c>
       <c r="B34" t="n">
-        <v>92756</v>
+        <v>92772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,21 +3931,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3946,10 +3955,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565184</v>
+        <v>565300</v>
       </c>
       <c r="R34" t="n">
-        <v>6683739</v>
+        <v>6683931</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4008,7 +4017,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356255</v>
+        <v>128356250</v>
       </c>
       <c r="B35" t="n">
         <v>92399</v>
@@ -4038,7 +4047,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4052,10 +4061,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565128</v>
+        <v>565136</v>
       </c>
       <c r="R35" t="n">
-        <v>6683585</v>
+        <v>6683681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4114,7 +4123,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128353904</v>
+        <v>128356336</v>
       </c>
       <c r="B36" t="n">
         <v>92772</v>
@@ -4145,17 +4154,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565224</v>
+        <v>565294</v>
       </c>
       <c r="R36" t="n">
-        <v>6683766</v>
+        <v>6683885</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4185,6 +4194,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4199,44 +4213,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356343</v>
+        <v>128356276</v>
       </c>
       <c r="B37" t="n">
-        <v>92772</v>
+        <v>97460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4368</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4246,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565300</v>
+        <v>565383</v>
       </c>
       <c r="R37" t="n">
-        <v>6683931</v>
+        <v>6683939</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4308,10 +4322,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128356250</v>
+        <v>128354354</v>
       </c>
       <c r="B38" t="n">
-        <v>92399</v>
+        <v>92788</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,46 +4333,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565136</v>
+        <v>565289</v>
       </c>
       <c r="R38" t="n">
-        <v>6683681</v>
+        <v>6683828</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4402,22 +4407,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128356336</v>
+        <v>128356309</v>
       </c>
       <c r="B39" t="n">
-        <v>92772</v>
+        <v>92756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4425,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565294</v>
+        <v>565184</v>
       </c>
       <c r="R39" t="n">
-        <v>6683885</v>
+        <v>6683739</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4485,11 +4490,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5462,48 +5462,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128353745</v>
+        <v>128356307</v>
       </c>
       <c r="B49" t="n">
-        <v>92788</v>
+        <v>92756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565166</v>
+        <v>565193</v>
       </c>
       <c r="R49" t="n">
-        <v>6683711</v>
+        <v>6683755</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5547,19 +5547,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356307</v>
+        <v>128353808</v>
       </c>
       <c r="B50" t="n">
         <v>92756</v>
@@ -5590,17 +5590,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565193</v>
+        <v>565189</v>
       </c>
       <c r="R50" t="n">
-        <v>6683755</v>
+        <v>6683740</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5644,19 +5644,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128353808</v>
+        <v>128356310</v>
       </c>
       <c r="B51" t="n">
         <v>92756</v>
@@ -5687,17 +5687,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565189</v>
+        <v>565306</v>
       </c>
       <c r="R51" t="n">
-        <v>6683740</v>
+        <v>6683913</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5741,60 +5741,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128356310</v>
+        <v>128353745</v>
       </c>
       <c r="B52" t="n">
-        <v>92756</v>
+        <v>92788</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565306</v>
+        <v>565166</v>
       </c>
       <c r="R52" t="n">
-        <v>6683913</v>
+        <v>6683711</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5838,12 +5838,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7474,48 +7474,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128354290</v>
+        <v>128356331</v>
       </c>
       <c r="B69" t="n">
-        <v>86925</v>
+        <v>92788</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565327</v>
+        <v>565298</v>
       </c>
       <c r="R69" t="n">
-        <v>6683939</v>
+        <v>6683926</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7559,22 +7568,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356286</v>
+        <v>128354308</v>
       </c>
       <c r="B70" t="n">
-        <v>86727</v>
+        <v>100768</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7582,37 +7591,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565257</v>
+        <v>565341</v>
       </c>
       <c r="R70" t="n">
-        <v>6683775</v>
+        <v>6683943</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7656,69 +7665,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356331</v>
+        <v>128354290</v>
       </c>
       <c r="B71" t="n">
-        <v>92788</v>
+        <v>86925</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565298</v>
+        <v>565327</v>
       </c>
       <c r="R71" t="n">
-        <v>6683926</v>
+        <v>6683939</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7762,60 +7762,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128354079</v>
+        <v>128356286</v>
       </c>
       <c r="B72" t="n">
-        <v>92756</v>
+        <v>86727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565281</v>
+        <v>565257</v>
       </c>
       <c r="R72" t="n">
-        <v>6683847</v>
+        <v>6683775</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7859,69 +7859,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128356231</v>
+        <v>128354079</v>
       </c>
       <c r="B73" t="n">
-        <v>92399</v>
+        <v>92756</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565261</v>
+        <v>565281</v>
       </c>
       <c r="R73" t="n">
-        <v>6683777</v>
+        <v>6683847</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7965,22 +7956,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128356288</v>
+        <v>128356231</v>
       </c>
       <c r="B74" t="n">
-        <v>86727</v>
+        <v>92399</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7988,34 +7979,43 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565128</v>
+        <v>565261</v>
       </c>
       <c r="R74" t="n">
-        <v>6683644</v>
+        <v>6683777</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8074,10 +8074,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354308</v>
+        <v>128356288</v>
       </c>
       <c r="B75" t="n">
-        <v>100768</v>
+        <v>86727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8085,37 +8085,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565341</v>
+        <v>565128</v>
       </c>
       <c r="R75" t="n">
-        <v>6683943</v>
+        <v>6683644</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8159,22 +8159,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128353641</v>
+        <v>128356315</v>
       </c>
       <c r="B76" t="n">
-        <v>86727</v>
+        <v>92788</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,37 +8182,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565149</v>
+        <v>565123</v>
       </c>
       <c r="R76" t="n">
-        <v>6683686</v>
+        <v>6683582</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8256,22 +8265,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128354183</v>
+        <v>128353641</v>
       </c>
       <c r="B77" t="n">
-        <v>92399</v>
+        <v>86727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8279,34 +8288,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565320</v>
+        <v>565149</v>
       </c>
       <c r="R77" t="n">
-        <v>6683918</v>
+        <v>6683686</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8365,32 +8374,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128356363</v>
+        <v>128356344</v>
       </c>
       <c r="B78" t="n">
-        <v>100768</v>
+        <v>92772</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8400,10 +8409,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565298</v>
+        <v>565307</v>
       </c>
       <c r="R78" t="n">
-        <v>6683884</v>
+        <v>6683918</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8462,10 +8471,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356315</v>
+        <v>128354183</v>
       </c>
       <c r="B79" t="n">
-        <v>92788</v>
+        <v>92399</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8473,46 +8482,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565123</v>
+        <v>565320</v>
       </c>
       <c r="R79" t="n">
-        <v>6683582</v>
+        <v>6683918</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,22 +8556,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356344</v>
+        <v>128354266</v>
       </c>
       <c r="B80" t="n">
-        <v>92772</v>
+        <v>86925</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8579,37 +8579,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4368</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565307</v>
+        <v>565313</v>
       </c>
       <c r="R80" t="n">
-        <v>6683918</v>
+        <v>6683939</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8653,60 +8653,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354266</v>
+        <v>128356363</v>
       </c>
       <c r="B81" t="n">
-        <v>86925</v>
+        <v>100768</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565313</v>
+        <v>565298</v>
       </c>
       <c r="R81" t="n">
-        <v>6683939</v>
+        <v>6683884</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,12 +8750,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356348</v>
       </c>
       <c r="B2" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128356327</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128356362</v>
       </c>
       <c r="B4" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356311</v>
       </c>
       <c r="B5" t="n">
-        <v>92766</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565121</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683581</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356237</v>
+        <v>128353720</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,46 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565304</v>
+        <v>565171</v>
       </c>
       <c r="R6" t="n">
-        <v>6683884</v>
+        <v>6683703</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,22 +1157,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356324</v>
+        <v>128356237</v>
       </c>
       <c r="B7" t="n">
-        <v>92788</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,26 +1180,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1222,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565185</v>
+        <v>565304</v>
       </c>
       <c r="R7" t="n">
-        <v>6683745</v>
+        <v>6683884</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1278,7 @@
         <v>128356335</v>
       </c>
       <c r="B8" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356311</v>
+        <v>128356324</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565121</v>
+        <v>565185</v>
       </c>
       <c r="R9" t="n">
-        <v>6683581</v>
+        <v>6683745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
         <v>128356345</v>
       </c>
       <c r="B10" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128356260</v>
       </c>
       <c r="B11" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128356235</v>
       </c>
       <c r="B12" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128356353</v>
       </c>
       <c r="B13" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128353570</v>
+        <v>128353600</v>
       </c>
       <c r="B14" t="n">
-        <v>92788</v>
+        <v>92758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565129</v>
+        <v>565138</v>
       </c>
       <c r="R14" t="n">
-        <v>6683660</v>
+        <v>6683661</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128356325</v>
+        <v>128353570</v>
       </c>
       <c r="B15" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,29 +2014,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565139</v>
+        <v>565129</v>
       </c>
       <c r="R15" t="n">
-        <v>6683679</v>
+        <v>6683660</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2080,60 +2071,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128353600</v>
+        <v>128356325</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565138</v>
+        <v>565139</v>
       </c>
       <c r="R16" t="n">
-        <v>6683661</v>
+        <v>6683679</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
         <v>128356245</v>
       </c>
       <c r="B17" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128353672</v>
       </c>
       <c r="B18" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356319</v>
+        <v>128356321</v>
       </c>
       <c r="B19" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565206</v>
+        <v>565225</v>
       </c>
       <c r="R19" t="n">
-        <v>6683808</v>
+        <v>6683834</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356321</v>
+        <v>128356319</v>
       </c>
       <c r="B20" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565225</v>
+        <v>565206</v>
       </c>
       <c r="R20" t="n">
-        <v>6683834</v>
+        <v>6683808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,7 +2607,7 @@
         <v>128356342</v>
       </c>
       <c r="B21" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>128356338</v>
       </c>
       <c r="B22" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>128356349</v>
       </c>
       <c r="B23" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128356323</v>
+        <v>128356333</v>
       </c>
       <c r="B24" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565127</v>
+        <v>565281</v>
       </c>
       <c r="R24" t="n">
-        <v>6683598</v>
+        <v>6683884</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>128356332</v>
       </c>
       <c r="B25" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128356333</v>
+        <v>128356323</v>
       </c>
       <c r="B26" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565281</v>
+        <v>565127</v>
       </c>
       <c r="R26" t="n">
-        <v>6683884</v>
+        <v>6683598</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128356287</v>
+        <v>128356346</v>
       </c>
       <c r="B27" t="n">
-        <v>86727</v>
+        <v>92774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565133</v>
+        <v>565165</v>
       </c>
       <c r="R27" t="n">
-        <v>6683665</v>
+        <v>6683730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128356346</v>
+        <v>128356287</v>
       </c>
       <c r="B28" t="n">
-        <v>92772</v>
+        <v>86729</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565165</v>
+        <v>565133</v>
       </c>
       <c r="R28" t="n">
-        <v>6683730</v>
+        <v>6683665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>128356337</v>
       </c>
       <c r="B29" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>128356248</v>
       </c>
       <c r="B30" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128354204</v>
       </c>
       <c r="B31" t="n">
-        <v>86888</v>
+        <v>86890</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3717,57 +3717,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128356255</v>
+        <v>128353904</v>
       </c>
       <c r="B32" t="n">
-        <v>92399</v>
+        <v>92774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565128</v>
+        <v>565224</v>
       </c>
       <c r="R32" t="n">
-        <v>6683585</v>
+        <v>6683766</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3811,22 +3802,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128353904</v>
+        <v>128356343</v>
       </c>
       <c r="B33" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3854,17 +3845,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565224</v>
+        <v>565300</v>
       </c>
       <c r="R33" t="n">
-        <v>6683766</v>
+        <v>6683931</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3908,22 +3899,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356343</v>
+        <v>128356336</v>
       </c>
       <c r="B34" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3955,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565300</v>
+        <v>565294</v>
       </c>
       <c r="R34" t="n">
-        <v>6683931</v>
+        <v>6683885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3991,6 +3982,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,54 +4013,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356250</v>
+        <v>128356309</v>
       </c>
       <c r="B35" t="n">
-        <v>92399</v>
+        <v>92758</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565136</v>
+        <v>565184</v>
       </c>
       <c r="R35" t="n">
-        <v>6683681</v>
+        <v>6683739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,32 +4110,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356336</v>
+        <v>128356276</v>
       </c>
       <c r="B36" t="n">
-        <v>92772</v>
+        <v>97462</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4145,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565294</v>
+        <v>565383</v>
       </c>
       <c r="R36" t="n">
-        <v>6683885</v>
+        <v>6683939</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,11 +4181,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,10 +4207,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356276</v>
+        <v>128356250</v>
       </c>
       <c r="B37" t="n">
-        <v>97460</v>
+        <v>92401</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4236,34 +4218,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565383</v>
+        <v>565136</v>
       </c>
       <c r="R37" t="n">
-        <v>6683939</v>
+        <v>6683681</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,10 +4313,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128354354</v>
+        <v>128356255</v>
       </c>
       <c r="B38" t="n">
-        <v>92788</v>
+        <v>92401</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4333,37 +4324,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565289</v>
+        <v>565128</v>
       </c>
       <c r="R38" t="n">
-        <v>6683828</v>
+        <v>6683585</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4407,60 +4407,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128356309</v>
+        <v>128354354</v>
       </c>
       <c r="B39" t="n">
-        <v>92756</v>
+        <v>92790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565184</v>
+        <v>565289</v>
       </c>
       <c r="R39" t="n">
-        <v>6683739</v>
+        <v>6683828</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4504,12 +4504,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
         <v>128356326</v>
       </c>
       <c r="B40" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356252</v>
+        <v>128356234</v>
       </c>
       <c r="B41" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565313</v>
+        <v>565304</v>
       </c>
       <c r="R41" t="n">
-        <v>6683875</v>
+        <v>6683798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4731,7 +4731,7 @@
         <v>128356240</v>
       </c>
       <c r="B42" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356234</v>
+        <v>128356252</v>
       </c>
       <c r="B43" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565304</v>
+        <v>565313</v>
       </c>
       <c r="R43" t="n">
-        <v>6683798</v>
+        <v>6683875</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
         <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>90984</v>
+        <v>90986</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128356317</v>
+        <v>128356262</v>
       </c>
       <c r="B45" t="n">
-        <v>92788</v>
+        <v>92401</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5058,26 +5058,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565188</v>
+        <v>565306</v>
       </c>
       <c r="R45" t="n">
-        <v>6683735</v>
+        <v>6683913</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,54 +5153,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356262</v>
+        <v>128356351</v>
       </c>
       <c r="B46" t="n">
-        <v>92399</v>
+        <v>92774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565306</v>
+        <v>565125</v>
       </c>
       <c r="R46" t="n">
-        <v>6683913</v>
+        <v>6683620</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5259,45 +5250,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356351</v>
+        <v>128356317</v>
       </c>
       <c r="B47" t="n">
-        <v>92772</v>
+        <v>92790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565125</v>
+        <v>565188</v>
       </c>
       <c r="R47" t="n">
-        <v>6683620</v>
+        <v>6683735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
         <v>128356374</v>
       </c>
       <c r="B48" t="n">
-        <v>86888</v>
+        <v>86890</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128356307</v>
+        <v>128356350</v>
       </c>
       <c r="B49" t="n">
-        <v>92756</v>
+        <v>92774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565193</v>
+        <v>565128</v>
       </c>
       <c r="R49" t="n">
-        <v>6683755</v>
+        <v>6683651</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5559,10 +5559,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128353808</v>
+        <v>128356307</v>
       </c>
       <c r="B50" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5590,17 +5590,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565189</v>
+        <v>565193</v>
       </c>
       <c r="R50" t="n">
-        <v>6683740</v>
+        <v>6683755</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5644,22 +5644,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128356310</v>
+        <v>128353808</v>
       </c>
       <c r="B51" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,17 +5687,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565306</v>
+        <v>565189</v>
       </c>
       <c r="R51" t="n">
-        <v>6683913</v>
+        <v>6683740</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5741,60 +5741,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128353745</v>
+        <v>128356310</v>
       </c>
       <c r="B52" t="n">
-        <v>92788</v>
+        <v>92758</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565166</v>
+        <v>565306</v>
       </c>
       <c r="R52" t="n">
-        <v>6683711</v>
+        <v>6683913</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5838,60 +5838,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356350</v>
+        <v>128353745</v>
       </c>
       <c r="B53" t="n">
-        <v>92772</v>
+        <v>92790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565128</v>
+        <v>565166</v>
       </c>
       <c r="R53" t="n">
-        <v>6683651</v>
+        <v>6683711</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,66 +5935,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356316</v>
+        <v>128356356</v>
       </c>
       <c r="B54" t="n">
-        <v>92788</v>
+        <v>92774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565125</v>
+        <v>565307</v>
       </c>
       <c r="R54" t="n">
-        <v>6683662</v>
+        <v>6683932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6053,54 +6044,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356294</v>
+        <v>128356352</v>
       </c>
       <c r="B55" t="n">
-        <v>90999</v>
+        <v>92774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565290</v>
+        <v>565124</v>
       </c>
       <c r="R55" t="n">
-        <v>6683893</v>
+        <v>6683563</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,10 +6141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356320</v>
+        <v>128353737</v>
       </c>
       <c r="B56" t="n">
-        <v>92788</v>
+        <v>86729</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,46 +6152,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565213</v>
+        <v>565164</v>
       </c>
       <c r="R56" t="n">
-        <v>6683796</v>
+        <v>6683706</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6253,22 +6226,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356236</v>
+        <v>128356257</v>
       </c>
       <c r="B57" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,7 +6268,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6309,10 +6282,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565136</v>
+        <v>565243</v>
       </c>
       <c r="R57" t="n">
-        <v>6683697</v>
+        <v>6683765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,45 +6344,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356356</v>
+        <v>128356316</v>
       </c>
       <c r="B58" t="n">
-        <v>92772</v>
+        <v>92790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565307</v>
+        <v>565125</v>
       </c>
       <c r="R58" t="n">
-        <v>6683932</v>
+        <v>6683662</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6468,45 +6450,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356352</v>
+        <v>128356294</v>
       </c>
       <c r="B59" t="n">
-        <v>92772</v>
+        <v>91001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565124</v>
+        <v>565290</v>
       </c>
       <c r="R59" t="n">
-        <v>6683563</v>
+        <v>6683893</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,10 +6556,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128353737</v>
+        <v>128356320</v>
       </c>
       <c r="B60" t="n">
-        <v>86727</v>
+        <v>92790</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6576,37 +6567,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565164</v>
+        <v>565213</v>
       </c>
       <c r="R60" t="n">
-        <v>6683706</v>
+        <v>6683796</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6650,22 +6650,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356257</v>
+        <v>128356236</v>
       </c>
       <c r="B61" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565243</v>
+        <v>565136</v>
       </c>
       <c r="R61" t="n">
-        <v>6683765</v>
+        <v>6683697</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6771,7 +6771,7 @@
         <v>128356360</v>
       </c>
       <c r="B62" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128353797</v>
+        <v>128356322</v>
       </c>
       <c r="B63" t="n">
-        <v>86727</v>
+        <v>92790</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,37 +6876,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565197</v>
+        <v>565121</v>
       </c>
       <c r="R63" t="n">
-        <v>6683732</v>
+        <v>6683569</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6950,22 +6959,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356322</v>
+        <v>128353797</v>
       </c>
       <c r="B64" t="n">
-        <v>92788</v>
+        <v>86729</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,46 +6982,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565121</v>
+        <v>565197</v>
       </c>
       <c r="R64" t="n">
-        <v>6683569</v>
+        <v>6683732</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7056,22 +7056,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356259</v>
+        <v>128356270</v>
       </c>
       <c r="B65" t="n">
-        <v>92399</v>
+        <v>92768</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,43 +7079,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565167</v>
+        <v>565281</v>
       </c>
       <c r="R65" t="n">
-        <v>6683728</v>
+        <v>6683884</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,10 +7165,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356270</v>
+        <v>128356259</v>
       </c>
       <c r="B66" t="n">
-        <v>92766</v>
+        <v>92401</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7185,34 +7176,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565281</v>
+        <v>565167</v>
       </c>
       <c r="R66" t="n">
-        <v>6683884</v>
+        <v>6683728</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
         <v>128356261</v>
       </c>
       <c r="B67" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>128356361</v>
       </c>
       <c r="B68" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128356331</v>
+        <v>128356288</v>
       </c>
       <c r="B69" t="n">
-        <v>92788</v>
+        <v>86729</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7485,43 +7485,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565298</v>
+        <v>565128</v>
       </c>
       <c r="R69" t="n">
-        <v>6683926</v>
+        <v>6683644</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7580,10 +7571,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128354308</v>
+        <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>100768</v>
+        <v>86729</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7591,37 +7582,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565341</v>
+        <v>565257</v>
       </c>
       <c r="R70" t="n">
-        <v>6683943</v>
+        <v>6683775</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7665,60 +7656,69 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128354290</v>
+        <v>128356331</v>
       </c>
       <c r="B71" t="n">
-        <v>86925</v>
+        <v>92790</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565327</v>
+        <v>565298</v>
       </c>
       <c r="R71" t="n">
-        <v>6683939</v>
+        <v>6683926</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7762,22 +7762,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356286</v>
+        <v>128356231</v>
       </c>
       <c r="B72" t="n">
-        <v>86727</v>
+        <v>92401</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7785,34 +7785,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565257</v>
+        <v>565261</v>
       </c>
       <c r="R72" t="n">
-        <v>6683775</v>
+        <v>6683777</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7871,32 +7880,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354079</v>
+        <v>128354308</v>
       </c>
       <c r="B73" t="n">
-        <v>92756</v>
+        <v>100773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7906,10 +7915,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565281</v>
+        <v>565341</v>
       </c>
       <c r="R73" t="n">
-        <v>6683847</v>
+        <v>6683943</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7968,57 +7977,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128356231</v>
+        <v>128354290</v>
       </c>
       <c r="B74" t="n">
-        <v>92399</v>
+        <v>86927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565261</v>
+        <v>565327</v>
       </c>
       <c r="R74" t="n">
-        <v>6683777</v>
+        <v>6683939</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,60 +8062,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128356288</v>
+        <v>128354079</v>
       </c>
       <c r="B75" t="n">
-        <v>86727</v>
+        <v>92758</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565128</v>
+        <v>565281</v>
       </c>
       <c r="R75" t="n">
-        <v>6683644</v>
+        <v>6683847</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8159,22 +8159,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356315</v>
+        <v>128353641</v>
       </c>
       <c r="B76" t="n">
-        <v>92788</v>
+        <v>86729</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,46 +8182,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565123</v>
+        <v>565149</v>
       </c>
       <c r="R76" t="n">
-        <v>6683582</v>
+        <v>6683686</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8265,60 +8256,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128353641</v>
+        <v>128356344</v>
       </c>
       <c r="B77" t="n">
-        <v>86727</v>
+        <v>92774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565149</v>
+        <v>565307</v>
       </c>
       <c r="R77" t="n">
-        <v>6683686</v>
+        <v>6683918</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8362,57 +8353,66 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128356344</v>
+        <v>128356315</v>
       </c>
       <c r="B78" t="n">
-        <v>92772</v>
+        <v>92790</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565307</v>
+        <v>565123</v>
       </c>
       <c r="R78" t="n">
-        <v>6683918</v>
+        <v>6683582</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8474,7 +8474,7 @@
         <v>128354183</v>
       </c>
       <c r="B79" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8568,48 +8568,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128354266</v>
+        <v>128356363</v>
       </c>
       <c r="B80" t="n">
-        <v>86925</v>
+        <v>100773</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565313</v>
+        <v>565298</v>
       </c>
       <c r="R80" t="n">
-        <v>6683939</v>
+        <v>6683884</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8653,60 +8653,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128356363</v>
+        <v>128354266</v>
       </c>
       <c r="B81" t="n">
-        <v>100768</v>
+        <v>86927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R81" t="n">
-        <v>6683884</v>
+        <v>6683939</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,22 +8750,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128356334</v>
+        <v>128356330</v>
       </c>
       <c r="B82" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>565315</v>
+        <v>565306</v>
       </c>
       <c r="R82" t="n">
-        <v>6683935</v>
+        <v>6683912</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128356318</v>
+        <v>128356334</v>
       </c>
       <c r="B83" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>565133</v>
+        <v>565315</v>
       </c>
       <c r="R83" t="n">
-        <v>6683665</v>
+        <v>6683935</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8974,10 +8974,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128356330</v>
+        <v>128356318</v>
       </c>
       <c r="B84" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>565306</v>
+        <v>565133</v>
       </c>
       <c r="R84" t="n">
-        <v>6683912</v>
+        <v>6683665</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9083,7 +9083,7 @@
         <v>128379692</v>
       </c>
       <c r="B85" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128379701</v>
       </c>
       <c r="B86" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>128356362</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356311</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92758</v>
+        <v>92768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565121</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683581</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128353720</v>
+        <v>128356324</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565171</v>
+        <v>565185</v>
       </c>
       <c r="R6" t="n">
-        <v>6683703</v>
+        <v>6683745</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,66 +1166,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356237</v>
+        <v>128356311</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565304</v>
+        <v>565121</v>
       </c>
       <c r="R7" t="n">
-        <v>6683884</v>
+        <v>6683581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356335</v>
+        <v>128356237</v>
       </c>
       <c r="B8" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,34 +1286,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565323</v>
+        <v>565304</v>
       </c>
       <c r="R8" t="n">
-        <v>6683839</v>
+        <v>6683884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,11 +1355,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1381,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356324</v>
+        <v>128356335</v>
       </c>
       <c r="B9" t="n">
         <v>92790</v>
@@ -1405,26 +1409,17 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565185</v>
+        <v>565323</v>
       </c>
       <c r="R9" t="n">
-        <v>6683745</v>
+        <v>6683839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,6 +1452,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,54 +1686,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128356235</v>
+        <v>128356353</v>
       </c>
       <c r="B12" t="n">
-        <v>92401</v>
+        <v>92774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565149</v>
+        <v>565118</v>
       </c>
       <c r="R12" t="n">
-        <v>6683718</v>
+        <v>6683561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,48 +1783,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356353</v>
+        <v>128353570</v>
       </c>
       <c r="B13" t="n">
-        <v>92774</v>
+        <v>92790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565118</v>
+        <v>565129</v>
       </c>
       <c r="R13" t="n">
-        <v>6683561</v>
+        <v>6683660</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,60 +1868,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128353600</v>
+        <v>128356325</v>
       </c>
       <c r="B14" t="n">
-        <v>92758</v>
+        <v>92790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565138</v>
+        <v>565139</v>
       </c>
       <c r="R14" t="n">
-        <v>6683661</v>
+        <v>6683679</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353570</v>
+        <v>128356235</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,37 +1997,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565129</v>
+        <v>565149</v>
       </c>
       <c r="R15" t="n">
-        <v>6683660</v>
+        <v>6683718</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,69 +2080,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356325</v>
+        <v>128353600</v>
       </c>
       <c r="B16" t="n">
-        <v>92790</v>
+        <v>92758</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565139</v>
+        <v>565138</v>
       </c>
       <c r="R16" t="n">
-        <v>6683679</v>
+        <v>6683661</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3620,48 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128354204</v>
+        <v>128356309</v>
       </c>
       <c r="B31" t="n">
-        <v>86890</v>
+        <v>92758</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>788</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565325</v>
+        <v>565184</v>
       </c>
       <c r="R31" t="n">
-        <v>6683920</v>
+        <v>6683739</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3705,44 +3705,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128353904</v>
+        <v>128354204</v>
       </c>
       <c r="B32" t="n">
-        <v>92774</v>
+        <v>86890</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565224</v>
+        <v>565325</v>
       </c>
       <c r="R32" t="n">
-        <v>6683766</v>
+        <v>6683920</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356343</v>
+        <v>128353904</v>
       </c>
       <c r="B33" t="n">
         <v>92774</v>
@@ -3845,17 +3845,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565300</v>
+        <v>565224</v>
       </c>
       <c r="R33" t="n">
-        <v>6683931</v>
+        <v>6683766</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3899,19 +3899,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356336</v>
+        <v>128356343</v>
       </c>
       <c r="B34" t="n">
         <v>92774</v>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565294</v>
+        <v>565300</v>
       </c>
       <c r="R34" t="n">
-        <v>6683885</v>
+        <v>6683931</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,11 +3982,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4013,10 +4008,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356309</v>
+        <v>128356336</v>
       </c>
       <c r="B35" t="n">
-        <v>92758</v>
+        <v>92774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4019,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565184</v>
+        <v>565294</v>
       </c>
       <c r="R35" t="n">
-        <v>6683739</v>
+        <v>6683885</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4084,6 +4079,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4110,10 +4110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356276</v>
+        <v>128356250</v>
       </c>
       <c r="B36" t="n">
-        <v>97462</v>
+        <v>92401</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4121,34 +4121,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565383</v>
+        <v>565136</v>
       </c>
       <c r="R36" t="n">
-        <v>6683939</v>
+        <v>6683681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,7 +4216,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356250</v>
+        <v>128356255</v>
       </c>
       <c r="B37" t="n">
         <v>92401</v>
@@ -4237,7 +4246,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4251,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565136</v>
+        <v>565128</v>
       </c>
       <c r="R37" t="n">
-        <v>6683681</v>
+        <v>6683585</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4313,10 +4322,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128356255</v>
+        <v>128354354</v>
       </c>
       <c r="B38" t="n">
-        <v>92401</v>
+        <v>92790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4324,46 +4333,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565128</v>
+        <v>565289</v>
       </c>
       <c r="R38" t="n">
-        <v>6683585</v>
+        <v>6683828</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4407,22 +4407,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128354354</v>
+        <v>128356276</v>
       </c>
       <c r="B39" t="n">
-        <v>92790</v>
+        <v>97462</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,37 +4430,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565289</v>
+        <v>565383</v>
       </c>
       <c r="R39" t="n">
-        <v>6683828</v>
+        <v>6683939</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4504,12 +4504,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5047,54 +5047,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128356262</v>
+        <v>128356351</v>
       </c>
       <c r="B45" t="n">
-        <v>92401</v>
+        <v>92774</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565306</v>
+        <v>565125</v>
       </c>
       <c r="R45" t="n">
-        <v>6683913</v>
+        <v>6683620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,45 +5144,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356351</v>
+        <v>128356262</v>
       </c>
       <c r="B46" t="n">
-        <v>92774</v>
+        <v>92401</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565125</v>
+        <v>565306</v>
       </c>
       <c r="R46" t="n">
-        <v>6683620</v>
+        <v>6683913</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5947,7 +5947,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356356</v>
+        <v>128356352</v>
       </c>
       <c r="B54" t="n">
         <v>92774</v>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565307</v>
+        <v>565124</v>
       </c>
       <c r="R54" t="n">
-        <v>6683932</v>
+        <v>6683563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6044,48 +6044,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356352</v>
+        <v>128353737</v>
       </c>
       <c r="B55" t="n">
-        <v>92774</v>
+        <v>86729</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565124</v>
+        <v>565164</v>
       </c>
       <c r="R55" t="n">
-        <v>6683563</v>
+        <v>6683706</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6129,22 +6129,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128353737</v>
+        <v>128356257</v>
       </c>
       <c r="B56" t="n">
-        <v>86729</v>
+        <v>92401</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6152,37 +6152,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565164</v>
+        <v>565243</v>
       </c>
       <c r="R56" t="n">
-        <v>6683706</v>
+        <v>6683765</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6226,22 +6235,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356257</v>
+        <v>128356316</v>
       </c>
       <c r="B57" t="n">
-        <v>92401</v>
+        <v>92790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6249,26 +6258,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6282,10 +6291,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565243</v>
+        <v>565125</v>
       </c>
       <c r="R57" t="n">
-        <v>6683765</v>
+        <v>6683662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6344,37 +6353,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356316</v>
+        <v>128356294</v>
       </c>
       <c r="B58" t="n">
-        <v>92790</v>
+        <v>91001</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6388,10 +6397,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565125</v>
+        <v>565290</v>
       </c>
       <c r="R58" t="n">
-        <v>6683662</v>
+        <v>6683893</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,37 +6459,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356294</v>
+        <v>128356320</v>
       </c>
       <c r="B59" t="n">
-        <v>91001</v>
+        <v>92790</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6494,10 +6503,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565290</v>
+        <v>565213</v>
       </c>
       <c r="R59" t="n">
-        <v>6683893</v>
+        <v>6683796</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6556,10 +6565,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356320</v>
+        <v>128356236</v>
       </c>
       <c r="B60" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6567,26 +6576,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6600,10 +6609,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565213</v>
+        <v>565136</v>
       </c>
       <c r="R60" t="n">
-        <v>6683796</v>
+        <v>6683697</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,54 +6671,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356236</v>
+        <v>128356356</v>
       </c>
       <c r="B61" t="n">
-        <v>92401</v>
+        <v>92774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565136</v>
+        <v>565307</v>
       </c>
       <c r="R61" t="n">
-        <v>6683697</v>
+        <v>6683932</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6771,7 +6771,7 @@
         <v>128356360</v>
       </c>
       <c r="B62" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128356322</v>
+        <v>128353797</v>
       </c>
       <c r="B63" t="n">
-        <v>92790</v>
+        <v>86729</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,46 +6876,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565121</v>
+        <v>565197</v>
       </c>
       <c r="R63" t="n">
-        <v>6683569</v>
+        <v>6683732</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6959,22 +6950,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128353797</v>
+        <v>128356270</v>
       </c>
       <c r="B64" t="n">
-        <v>86729</v>
+        <v>92768</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6982,37 +6973,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565197</v>
+        <v>565281</v>
       </c>
       <c r="R64" t="n">
-        <v>6683732</v>
+        <v>6683884</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7056,22 +7047,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356270</v>
+        <v>128356322</v>
       </c>
       <c r="B65" t="n">
-        <v>92768</v>
+        <v>92790</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,34 +7070,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565281</v>
+        <v>565121</v>
       </c>
       <c r="R65" t="n">
-        <v>6683884</v>
+        <v>6683569</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128356261</v>
+        <v>128356361</v>
       </c>
       <c r="B67" t="n">
-        <v>92401</v>
+        <v>100779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,43 +7282,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565331</v>
+        <v>565330</v>
       </c>
       <c r="R67" t="n">
-        <v>6683832</v>
+        <v>6683934</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7377,10 +7368,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128356361</v>
+        <v>128356261</v>
       </c>
       <c r="B68" t="n">
-        <v>100773</v>
+        <v>92401</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7388,34 +7379,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565330</v>
+        <v>565331</v>
       </c>
       <c r="R68" t="n">
-        <v>6683934</v>
+        <v>6683832</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,48 +7474,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128356288</v>
+        <v>128354290</v>
       </c>
       <c r="B69" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565128</v>
+        <v>565327</v>
       </c>
       <c r="R69" t="n">
-        <v>6683644</v>
+        <v>6683939</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7559,60 +7559,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356286</v>
+        <v>128354079</v>
       </c>
       <c r="B70" t="n">
-        <v>86729</v>
+        <v>92758</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565257</v>
+        <v>565281</v>
       </c>
       <c r="R70" t="n">
-        <v>6683775</v>
+        <v>6683847</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7656,22 +7656,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356331</v>
+        <v>128356288</v>
       </c>
       <c r="B71" t="n">
-        <v>92790</v>
+        <v>86729</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7679,43 +7679,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565298</v>
+        <v>565128</v>
       </c>
       <c r="R71" t="n">
-        <v>6683926</v>
+        <v>6683644</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7774,10 +7765,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356231</v>
+        <v>128356286</v>
       </c>
       <c r="B72" t="n">
-        <v>92401</v>
+        <v>86729</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7785,43 +7776,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565261</v>
+        <v>565257</v>
       </c>
       <c r="R72" t="n">
-        <v>6683777</v>
+        <v>6683775</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7880,10 +7862,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354308</v>
+        <v>128356331</v>
       </c>
       <c r="B73" t="n">
-        <v>100773</v>
+        <v>92790</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,37 +7873,46 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565341</v>
+        <v>565298</v>
       </c>
       <c r="R73" t="n">
-        <v>6683943</v>
+        <v>6683926</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7965,60 +7956,69 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128354290</v>
+        <v>128356231</v>
       </c>
       <c r="B74" t="n">
-        <v>86927</v>
+        <v>92401</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565327</v>
+        <v>565261</v>
       </c>
       <c r="R74" t="n">
-        <v>6683939</v>
+        <v>6683777</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,44 +8062,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354079</v>
+        <v>128354308</v>
       </c>
       <c r="B75" t="n">
-        <v>92758</v>
+        <v>100779</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565281</v>
+        <v>565341</v>
       </c>
       <c r="R75" t="n">
-        <v>6683847</v>
+        <v>6683943</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8171,10 +8171,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128353641</v>
+        <v>128356363</v>
       </c>
       <c r="B76" t="n">
-        <v>86729</v>
+        <v>100779</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,37 +8182,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565149</v>
+        <v>565298</v>
       </c>
       <c r="R76" t="n">
-        <v>6683686</v>
+        <v>6683884</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8256,22 +8256,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128356344</v>
+        <v>128354266</v>
       </c>
       <c r="B77" t="n">
-        <v>92774</v>
+        <v>86927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8279,37 +8279,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565307</v>
+        <v>565313</v>
       </c>
       <c r="R77" t="n">
-        <v>6683918</v>
+        <v>6683939</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8353,22 +8353,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128356315</v>
+        <v>128353641</v>
       </c>
       <c r="B78" t="n">
-        <v>92790</v>
+        <v>86729</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8376,46 +8376,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565123</v>
+        <v>565149</v>
       </c>
       <c r="R78" t="n">
-        <v>6683582</v>
+        <v>6683686</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8459,60 +8450,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128354183</v>
+        <v>128356344</v>
       </c>
       <c r="B79" t="n">
-        <v>92401</v>
+        <v>92774</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565320</v>
+        <v>565307</v>
       </c>
       <c r="R79" t="n">
         <v>6683918</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,22 +8547,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356363</v>
+        <v>128356315</v>
       </c>
       <c r="B80" t="n">
-        <v>100773</v>
+        <v>92790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8579,34 +8570,43 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565298</v>
+        <v>565123</v>
       </c>
       <c r="R80" t="n">
-        <v>6683884</v>
+        <v>6683582</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8665,32 +8665,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354266</v>
+        <v>128354183</v>
       </c>
       <c r="B81" t="n">
-        <v>86927</v>
+        <v>92401</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565313</v>
+        <v>565320</v>
       </c>
       <c r="R81" t="n">
-        <v>6683939</v>
+        <v>6683918</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R3" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>92790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R4" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356311</v>
       </c>
       <c r="B5" t="n">
-        <v>92768</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565121</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683581</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356324</v>
+        <v>128356237</v>
       </c>
       <c r="B6" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,26 +1083,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565185</v>
+        <v>565304</v>
       </c>
       <c r="R6" t="n">
-        <v>6683745</v>
+        <v>6683884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,32 +1178,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356311</v>
+        <v>128356335</v>
       </c>
       <c r="B7" t="n">
-        <v>92758</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565121</v>
+        <v>565323</v>
       </c>
       <c r="R7" t="n">
-        <v>6683581</v>
+        <v>6683839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356237</v>
+        <v>128353720</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,46 +1291,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565304</v>
+        <v>565171</v>
       </c>
       <c r="R8" t="n">
-        <v>6683884</v>
+        <v>6683703</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,19 +1365,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356335</v>
+        <v>128356324</v>
       </c>
       <c r="B9" t="n">
         <v>92790</v>
@@ -1409,17 +1405,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565323</v>
+        <v>565185</v>
       </c>
       <c r="R9" t="n">
-        <v>6683839</v>
+        <v>6683745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,11 +1457,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1783,32 +1783,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128353570</v>
+        <v>128353600</v>
       </c>
       <c r="B13" t="n">
-        <v>92790</v>
+        <v>92758</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565129</v>
+        <v>565138</v>
       </c>
       <c r="R13" t="n">
-        <v>6683660</v>
+        <v>6683661</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356325</v>
+        <v>128353570</v>
       </c>
       <c r="B14" t="n">
         <v>92790</v>
@@ -1908,29 +1908,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565139</v>
+        <v>565129</v>
       </c>
       <c r="R14" t="n">
-        <v>6683679</v>
+        <v>6683660</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,22 +1965,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128356235</v>
+        <v>128356325</v>
       </c>
       <c r="B15" t="n">
-        <v>92401</v>
+        <v>92790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,26 +1988,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2030,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565149</v>
+        <v>565139</v>
       </c>
       <c r="R15" t="n">
-        <v>6683718</v>
+        <v>6683679</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,48 +2083,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128353600</v>
+        <v>128356235</v>
       </c>
       <c r="B16" t="n">
-        <v>92758</v>
+        <v>92401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565138</v>
+        <v>565149</v>
       </c>
       <c r="R16" t="n">
-        <v>6683661</v>
+        <v>6683718</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,12 +2177,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2392,54 +2392,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356321</v>
+        <v>128356342</v>
       </c>
       <c r="B19" t="n">
-        <v>92790</v>
+        <v>92774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565225</v>
+        <v>565338</v>
       </c>
       <c r="R19" t="n">
-        <v>6683834</v>
+        <v>6683896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,54 +2489,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356319</v>
+        <v>128356338</v>
       </c>
       <c r="B20" t="n">
-        <v>92790</v>
+        <v>92774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565206</v>
+        <v>565124</v>
       </c>
       <c r="R20" t="n">
-        <v>6683808</v>
+        <v>6683659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,6 +2560,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,7 +2591,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356342</v>
+        <v>128356349</v>
       </c>
       <c r="B21" t="n">
         <v>92774</v>
@@ -2639,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565338</v>
+        <v>565147</v>
       </c>
       <c r="R21" t="n">
-        <v>6683896</v>
+        <v>6683691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,45 +2688,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356338</v>
+        <v>128356321</v>
       </c>
       <c r="B22" t="n">
-        <v>92774</v>
+        <v>92790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565124</v>
+        <v>565225</v>
       </c>
       <c r="R22" t="n">
-        <v>6683659</v>
+        <v>6683834</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,11 +2768,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2803,45 +2794,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356349</v>
+        <v>128356319</v>
       </c>
       <c r="B23" t="n">
-        <v>92774</v>
+        <v>92790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565147</v>
+        <v>565206</v>
       </c>
       <c r="R23" t="n">
-        <v>6683691</v>
+        <v>6683808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -5947,7 +5947,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356352</v>
+        <v>128356356</v>
       </c>
       <c r="B54" t="n">
         <v>92774</v>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565124</v>
+        <v>565307</v>
       </c>
       <c r="R54" t="n">
-        <v>6683563</v>
+        <v>6683932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6044,48 +6044,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128353737</v>
+        <v>128356352</v>
       </c>
       <c r="B55" t="n">
-        <v>86729</v>
+        <v>92774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565164</v>
+        <v>565124</v>
       </c>
       <c r="R55" t="n">
-        <v>6683706</v>
+        <v>6683563</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6129,22 +6129,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356257</v>
+        <v>128353737</v>
       </c>
       <c r="B56" t="n">
-        <v>92401</v>
+        <v>86729</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6152,46 +6152,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565243</v>
+        <v>565164</v>
       </c>
       <c r="R56" t="n">
-        <v>6683765</v>
+        <v>6683706</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6235,22 +6226,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356316</v>
+        <v>128356257</v>
       </c>
       <c r="B57" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6258,26 +6249,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6291,10 +6282,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565125</v>
+        <v>565243</v>
       </c>
       <c r="R57" t="n">
-        <v>6683662</v>
+        <v>6683765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,37 +6344,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356294</v>
+        <v>128356316</v>
       </c>
       <c r="B58" t="n">
-        <v>91001</v>
+        <v>92790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6397,10 +6388,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565290</v>
+        <v>565125</v>
       </c>
       <c r="R58" t="n">
-        <v>6683893</v>
+        <v>6683662</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6459,37 +6450,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356320</v>
+        <v>128356294</v>
       </c>
       <c r="B59" t="n">
-        <v>92790</v>
+        <v>91001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6503,10 +6494,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565213</v>
+        <v>565290</v>
       </c>
       <c r="R59" t="n">
-        <v>6683796</v>
+        <v>6683893</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,10 +6556,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356236</v>
+        <v>128356320</v>
       </c>
       <c r="B60" t="n">
-        <v>92401</v>
+        <v>92790</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6576,26 +6567,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6609,10 +6600,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565136</v>
+        <v>565213</v>
       </c>
       <c r="R60" t="n">
-        <v>6683697</v>
+        <v>6683796</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6671,45 +6662,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356356</v>
+        <v>128356236</v>
       </c>
       <c r="B61" t="n">
-        <v>92774</v>
+        <v>92401</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565307</v>
+        <v>565136</v>
       </c>
       <c r="R61" t="n">
-        <v>6683932</v>
+        <v>6683697</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356348</v>
       </c>
       <c r="B2" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R3" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B4" t="n">
-        <v>92790</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R4" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
         <v>128356311</v>
       </c>
       <c r="B5" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128356237</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356335</v>
+        <v>128353720</v>
       </c>
       <c r="B7" t="n">
-        <v>92790</v>
+        <v>92769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565323</v>
+        <v>565171</v>
       </c>
       <c r="R7" t="n">
-        <v>6683839</v>
+        <v>6683703</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1249,11 +1249,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,22 +1263,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128353720</v>
+        <v>128356324</v>
       </c>
       <c r="B8" t="n">
-        <v>92768</v>
+        <v>92791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,37 +1286,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565171</v>
+        <v>565185</v>
       </c>
       <c r="R8" t="n">
-        <v>6683703</v>
+        <v>6683745</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1365,22 +1369,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356324</v>
+        <v>128356335</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,26 +1409,17 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565185</v>
+        <v>565323</v>
       </c>
       <c r="R9" t="n">
-        <v>6683745</v>
+        <v>6683839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,6 +1452,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,45 +1483,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128356345</v>
+        <v>128356260</v>
       </c>
       <c r="B10" t="n">
-        <v>92774</v>
+        <v>92402</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565282</v>
+        <v>565139</v>
       </c>
       <c r="R10" t="n">
-        <v>6683847</v>
+        <v>6683696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,54 +1589,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128356260</v>
+        <v>128356345</v>
       </c>
       <c r="B11" t="n">
-        <v>92401</v>
+        <v>92775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565139</v>
+        <v>565282</v>
       </c>
       <c r="R11" t="n">
-        <v>6683696</v>
+        <v>6683847</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128356353</v>
+        <v>128353600</v>
       </c>
       <c r="B12" t="n">
-        <v>92774</v>
+        <v>92759</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,37 +1697,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565118</v>
+        <v>565138</v>
       </c>
       <c r="R12" t="n">
-        <v>6683561</v>
+        <v>6683661</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,60 +1771,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128353600</v>
+        <v>128356235</v>
       </c>
       <c r="B13" t="n">
-        <v>92758</v>
+        <v>92402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565138</v>
+        <v>565149</v>
       </c>
       <c r="R13" t="n">
-        <v>6683661</v>
+        <v>6683718</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1868,60 +1877,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128353570</v>
+        <v>128356353</v>
       </c>
       <c r="B14" t="n">
-        <v>92790</v>
+        <v>92775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565129</v>
+        <v>565118</v>
       </c>
       <c r="R14" t="n">
-        <v>6683660</v>
+        <v>6683561</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128356325</v>
+        <v>128353570</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,29 +2014,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565139</v>
+        <v>565129</v>
       </c>
       <c r="R15" t="n">
-        <v>6683679</v>
+        <v>6683660</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,22 +2071,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356235</v>
+        <v>128356325</v>
       </c>
       <c r="B16" t="n">
-        <v>92401</v>
+        <v>92791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,26 +2094,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565149</v>
+        <v>565139</v>
       </c>
       <c r="R16" t="n">
-        <v>6683718</v>
+        <v>6683679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,7 +2192,7 @@
         <v>128356245</v>
       </c>
       <c r="B17" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128353672</v>
       </c>
       <c r="B18" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128356342</v>
       </c>
       <c r="B19" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>128356338</v>
       </c>
       <c r="B20" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>128356349</v>
       </c>
       <c r="B21" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356321</v>
+        <v>128356319</v>
       </c>
       <c r="B22" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565225</v>
+        <v>565206</v>
       </c>
       <c r="R22" t="n">
-        <v>6683834</v>
+        <v>6683808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356319</v>
+        <v>128356321</v>
       </c>
       <c r="B23" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565206</v>
+        <v>565225</v>
       </c>
       <c r="R23" t="n">
-        <v>6683808</v>
+        <v>6683834</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128356333</v>
+        <v>128356323</v>
       </c>
       <c r="B24" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565281</v>
+        <v>565127</v>
       </c>
       <c r="R24" t="n">
-        <v>6683884</v>
+        <v>6683598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>128356332</v>
       </c>
       <c r="B25" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128356323</v>
+        <v>128356333</v>
       </c>
       <c r="B26" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565127</v>
+        <v>565281</v>
       </c>
       <c r="R26" t="n">
-        <v>6683598</v>
+        <v>6683884</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128356346</v>
+        <v>128356287</v>
       </c>
       <c r="B27" t="n">
-        <v>92774</v>
+        <v>86729</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565165</v>
+        <v>565133</v>
       </c>
       <c r="R27" t="n">
-        <v>6683730</v>
+        <v>6683665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128356287</v>
+        <v>128356346</v>
       </c>
       <c r="B28" t="n">
-        <v>86729</v>
+        <v>92775</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565133</v>
+        <v>565165</v>
       </c>
       <c r="R28" t="n">
-        <v>6683665</v>
+        <v>6683730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>128356337</v>
       </c>
       <c r="B29" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>128356248</v>
       </c>
       <c r="B30" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128356309</v>
+        <v>128353904</v>
       </c>
       <c r="B31" t="n">
-        <v>92758</v>
+        <v>92775</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,37 +3631,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565184</v>
+        <v>565224</v>
       </c>
       <c r="R31" t="n">
-        <v>6683739</v>
+        <v>6683766</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3705,60 +3705,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128354204</v>
+        <v>128356343</v>
       </c>
       <c r="B32" t="n">
-        <v>86890</v>
+        <v>92775</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565325</v>
+        <v>565300</v>
       </c>
       <c r="R32" t="n">
-        <v>6683920</v>
+        <v>6683931</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,22 +3802,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128353904</v>
+        <v>128356336</v>
       </c>
       <c r="B33" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3845,17 +3845,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565224</v>
+        <v>565294</v>
       </c>
       <c r="R33" t="n">
-        <v>6683766</v>
+        <v>6683885</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3885,6 +3885,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3899,22 +3904,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356343</v>
+        <v>128356309</v>
       </c>
       <c r="B34" t="n">
-        <v>92774</v>
+        <v>92759</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,21 +3927,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565300</v>
+        <v>565184</v>
       </c>
       <c r="R34" t="n">
-        <v>6683931</v>
+        <v>6683739</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4008,48 +4013,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356336</v>
+        <v>128354204</v>
       </c>
       <c r="B35" t="n">
-        <v>92774</v>
+        <v>86890</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4368</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565294</v>
+        <v>565325</v>
       </c>
       <c r="R35" t="n">
-        <v>6683885</v>
+        <v>6683920</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4079,11 +4084,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4098,22 +4098,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356250</v>
+        <v>128356255</v>
       </c>
       <c r="B36" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565136</v>
+        <v>565128</v>
       </c>
       <c r="R36" t="n">
-        <v>6683681</v>
+        <v>6683585</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,10 +4216,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356255</v>
+        <v>128356250</v>
       </c>
       <c r="B37" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565128</v>
+        <v>565136</v>
       </c>
       <c r="R37" t="n">
-        <v>6683585</v>
+        <v>6683681</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4325,7 +4325,7 @@
         <v>128354354</v>
       </c>
       <c r="B38" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128356276</v>
       </c>
       <c r="B39" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356326</v>
+        <v>128356252</v>
       </c>
       <c r="B40" t="n">
-        <v>92790</v>
+        <v>92402</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,26 +4527,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565306</v>
+        <v>565313</v>
       </c>
       <c r="R40" t="n">
-        <v>6683915</v>
+        <v>6683875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356234</v>
+        <v>128356240</v>
       </c>
       <c r="B41" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565304</v>
+        <v>565298</v>
       </c>
       <c r="R41" t="n">
-        <v>6683798</v>
+        <v>6683931</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356240</v>
+        <v>128356234</v>
       </c>
       <c r="B42" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565298</v>
+        <v>565304</v>
       </c>
       <c r="R42" t="n">
-        <v>6683931</v>
+        <v>6683798</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356252</v>
+        <v>128356326</v>
       </c>
       <c r="B43" t="n">
-        <v>92401</v>
+        <v>92791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4845,26 +4845,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565313</v>
+        <v>565306</v>
       </c>
       <c r="R43" t="n">
-        <v>6683875</v>
+        <v>6683915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
         <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>90986</v>
+        <v>90987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>128356351</v>
       </c>
       <c r="B45" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356262</v>
+        <v>128356317</v>
       </c>
       <c r="B46" t="n">
-        <v>92401</v>
+        <v>92791</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5155,26 +5155,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565306</v>
+        <v>565188</v>
       </c>
       <c r="R46" t="n">
-        <v>6683913</v>
+        <v>6683735</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356317</v>
+        <v>128356262</v>
       </c>
       <c r="B47" t="n">
-        <v>92790</v>
+        <v>92402</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,26 +5261,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565188</v>
+        <v>565306</v>
       </c>
       <c r="R47" t="n">
-        <v>6683735</v>
+        <v>6683913</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5462,48 +5462,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128356350</v>
+        <v>128353745</v>
       </c>
       <c r="B49" t="n">
-        <v>92774</v>
+        <v>92791</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565128</v>
+        <v>565166</v>
       </c>
       <c r="R49" t="n">
-        <v>6683651</v>
+        <v>6683711</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5547,22 +5547,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356307</v>
+        <v>128353808</v>
       </c>
       <c r="B50" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5590,17 +5590,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565193</v>
+        <v>565189</v>
       </c>
       <c r="R50" t="n">
-        <v>6683755</v>
+        <v>6683740</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5644,22 +5644,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128353808</v>
+        <v>128356307</v>
       </c>
       <c r="B51" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,17 +5687,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565189</v>
+        <v>565193</v>
       </c>
       <c r="R51" t="n">
-        <v>6683740</v>
+        <v>6683755</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5741,12 +5741,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
         <v>128356310</v>
       </c>
       <c r="B52" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5850,48 +5850,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128353745</v>
+        <v>128356350</v>
       </c>
       <c r="B53" t="n">
-        <v>92790</v>
+        <v>92775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565166</v>
+        <v>565128</v>
       </c>
       <c r="R53" t="n">
-        <v>6683711</v>
+        <v>6683651</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,57 +5935,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356356</v>
+        <v>128356316</v>
       </c>
       <c r="B54" t="n">
-        <v>92774</v>
+        <v>92791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565307</v>
+        <v>565125</v>
       </c>
       <c r="R54" t="n">
-        <v>6683932</v>
+        <v>6683662</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6044,45 +6053,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356352</v>
+        <v>128356294</v>
       </c>
       <c r="B55" t="n">
-        <v>92774</v>
+        <v>91002</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565124</v>
+        <v>565290</v>
       </c>
       <c r="R55" t="n">
-        <v>6683563</v>
+        <v>6683893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6141,10 +6159,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128353737</v>
+        <v>128356320</v>
       </c>
       <c r="B56" t="n">
-        <v>86729</v>
+        <v>92791</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6152,37 +6170,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565164</v>
+        <v>565213</v>
       </c>
       <c r="R56" t="n">
-        <v>6683706</v>
+        <v>6683796</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6226,22 +6253,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356257</v>
+        <v>128353737</v>
       </c>
       <c r="B57" t="n">
-        <v>92401</v>
+        <v>86729</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6249,46 +6276,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565243</v>
+        <v>565164</v>
       </c>
       <c r="R57" t="n">
-        <v>6683765</v>
+        <v>6683706</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6332,22 +6350,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356316</v>
+        <v>128356236</v>
       </c>
       <c r="B58" t="n">
-        <v>92790</v>
+        <v>92402</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6355,26 +6373,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6388,10 +6406,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565125</v>
+        <v>565136</v>
       </c>
       <c r="R58" t="n">
-        <v>6683662</v>
+        <v>6683697</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,37 +6468,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356294</v>
+        <v>128356257</v>
       </c>
       <c r="B59" t="n">
-        <v>91001</v>
+        <v>92402</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6494,10 +6512,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565290</v>
+        <v>565243</v>
       </c>
       <c r="R59" t="n">
-        <v>6683893</v>
+        <v>6683765</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6556,54 +6574,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356320</v>
+        <v>128356356</v>
       </c>
       <c r="B60" t="n">
-        <v>92790</v>
+        <v>92775</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565213</v>
+        <v>565307</v>
       </c>
       <c r="R60" t="n">
-        <v>6683796</v>
+        <v>6683932</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,54 +6671,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356236</v>
+        <v>128356352</v>
       </c>
       <c r="B61" t="n">
-        <v>92401</v>
+        <v>92775</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565136</v>
+        <v>565124</v>
       </c>
       <c r="R61" t="n">
-        <v>6683697</v>
+        <v>6683563</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6771,7 +6771,7 @@
         <v>128356360</v>
       </c>
       <c r="B62" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356270</v>
+        <v>128356322</v>
       </c>
       <c r="B64" t="n">
-        <v>92768</v>
+        <v>92791</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,34 +6973,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565281</v>
+        <v>565121</v>
       </c>
       <c r="R64" t="n">
-        <v>6683884</v>
+        <v>6683569</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7059,10 +7068,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356322</v>
+        <v>128356259</v>
       </c>
       <c r="B65" t="n">
-        <v>92790</v>
+        <v>92402</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,26 +7079,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7103,10 +7112,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565121</v>
+        <v>565167</v>
       </c>
       <c r="R65" t="n">
-        <v>6683569</v>
+        <v>6683728</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,10 +7174,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356259</v>
+        <v>128356270</v>
       </c>
       <c r="B66" t="n">
-        <v>92401</v>
+        <v>92769</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7176,43 +7185,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565167</v>
+        <v>565281</v>
       </c>
       <c r="R66" t="n">
-        <v>6683728</v>
+        <v>6683884</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128356361</v>
+        <v>128356261</v>
       </c>
       <c r="B67" t="n">
-        <v>100779</v>
+        <v>92402</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,34 +7282,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565330</v>
+        <v>565331</v>
       </c>
       <c r="R67" t="n">
-        <v>6683934</v>
+        <v>6683832</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,10 +7377,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128356261</v>
+        <v>128356361</v>
       </c>
       <c r="B68" t="n">
-        <v>92401</v>
+        <v>100780</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7379,43 +7388,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565331</v>
+        <v>565330</v>
       </c>
       <c r="R68" t="n">
-        <v>6683832</v>
+        <v>6683934</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128354290</v>
+        <v>128354079</v>
       </c>
       <c r="B69" t="n">
-        <v>86927</v>
+        <v>92759</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>788</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565327</v>
+        <v>565281</v>
       </c>
       <c r="R69" t="n">
-        <v>6683939</v>
+        <v>6683847</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7571,48 +7571,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128354079</v>
+        <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>92758</v>
+        <v>86729</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565281</v>
+        <v>565257</v>
       </c>
       <c r="R70" t="n">
-        <v>6683847</v>
+        <v>6683775</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7656,12 +7656,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356286</v>
+        <v>128356231</v>
       </c>
       <c r="B72" t="n">
-        <v>86729</v>
+        <v>92402</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7776,34 +7776,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565257</v>
+        <v>565261</v>
       </c>
       <c r="R72" t="n">
-        <v>6683775</v>
+        <v>6683777</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,7 +7874,7 @@
         <v>128356331</v>
       </c>
       <c r="B73" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7968,10 +7977,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128356231</v>
+        <v>128354308</v>
       </c>
       <c r="B74" t="n">
-        <v>92401</v>
+        <v>100780</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7979,46 +7988,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565261</v>
+        <v>565341</v>
       </c>
       <c r="R74" t="n">
-        <v>6683777</v>
+        <v>6683943</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,44 +8062,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354308</v>
+        <v>128354290</v>
       </c>
       <c r="B75" t="n">
-        <v>100779</v>
+        <v>86927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565341</v>
+        <v>565327</v>
       </c>
       <c r="R75" t="n">
-        <v>6683943</v>
+        <v>6683939</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356363</v>
+        <v>128356344</v>
       </c>
       <c r="B76" t="n">
-        <v>100779</v>
+        <v>92775</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565298</v>
+        <v>565307</v>
       </c>
       <c r="R76" t="n">
-        <v>6683884</v>
+        <v>6683918</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8268,45 +8268,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128354266</v>
+        <v>128353641</v>
       </c>
       <c r="B77" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565313</v>
+        <v>565149</v>
       </c>
       <c r="R77" t="n">
-        <v>6683939</v>
+        <v>6683686</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128353641</v>
+        <v>128354183</v>
       </c>
       <c r="B78" t="n">
-        <v>86729</v>
+        <v>92402</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8376,34 +8376,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565149</v>
+        <v>565320</v>
       </c>
       <c r="R78" t="n">
-        <v>6683686</v>
+        <v>6683918</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8462,45 +8462,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356344</v>
+        <v>128356315</v>
       </c>
       <c r="B79" t="n">
-        <v>92774</v>
+        <v>92791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565307</v>
+        <v>565123</v>
       </c>
       <c r="R79" t="n">
-        <v>6683918</v>
+        <v>6683582</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8559,10 +8568,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356315</v>
+        <v>128356363</v>
       </c>
       <c r="B80" t="n">
-        <v>92790</v>
+        <v>100780</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8570,43 +8579,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565123</v>
+        <v>565298</v>
       </c>
       <c r="R80" t="n">
-        <v>6683582</v>
+        <v>6683884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8665,32 +8665,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354183</v>
+        <v>128354266</v>
       </c>
       <c r="B81" t="n">
-        <v>92401</v>
+        <v>86927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565320</v>
+        <v>565313</v>
       </c>
       <c r="R81" t="n">
-        <v>6683918</v>
+        <v>6683939</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8762,10 +8762,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128356330</v>
+        <v>128356334</v>
       </c>
       <c r="B82" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>565306</v>
+        <v>565315</v>
       </c>
       <c r="R82" t="n">
-        <v>6683912</v>
+        <v>6683935</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8868,10 +8868,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128356334</v>
+        <v>128356318</v>
       </c>
       <c r="B83" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>565315</v>
+        <v>565133</v>
       </c>
       <c r="R83" t="n">
-        <v>6683935</v>
+        <v>6683665</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8974,10 +8974,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128356318</v>
+        <v>128356330</v>
       </c>
       <c r="B84" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>565133</v>
+        <v>565306</v>
       </c>
       <c r="R84" t="n">
-        <v>6683665</v>
+        <v>6683912</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9083,7 +9083,7 @@
         <v>128379692</v>
       </c>
       <c r="B85" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128379701</v>
       </c>
       <c r="B86" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356327</v>
+        <v>128356362</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565292</v>
+        <v>565302</v>
       </c>
       <c r="R3" t="n">
-        <v>6683907</v>
+        <v>6683928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356362</v>
+        <v>128356327</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>92791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565302</v>
+        <v>565292</v>
       </c>
       <c r="R4" t="n">
-        <v>6683928</v>
+        <v>6683907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356311</v>
+        <v>128353720</v>
       </c>
       <c r="B5" t="n">
-        <v>92759</v>
+        <v>92769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565121</v>
+        <v>565171</v>
       </c>
       <c r="R5" t="n">
-        <v>6683581</v>
+        <v>6683703</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,66 +1060,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356237</v>
+        <v>128356311</v>
       </c>
       <c r="B6" t="n">
-        <v>92402</v>
+        <v>92759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565304</v>
+        <v>565121</v>
       </c>
       <c r="R6" t="n">
-        <v>6683884</v>
+        <v>6683581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128353720</v>
+        <v>128356237</v>
       </c>
       <c r="B7" t="n">
-        <v>92769</v>
+        <v>92402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,37 +1180,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565171</v>
+        <v>565304</v>
       </c>
       <c r="R7" t="n">
-        <v>6683703</v>
+        <v>6683884</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,12 +1263,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128356287</v>
+        <v>128356346</v>
       </c>
       <c r="B27" t="n">
-        <v>86729</v>
+        <v>92775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565133</v>
+        <v>565165</v>
       </c>
       <c r="R27" t="n">
-        <v>6683665</v>
+        <v>6683730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128356346</v>
+        <v>128356287</v>
       </c>
       <c r="B28" t="n">
-        <v>92775</v>
+        <v>86729</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565165</v>
+        <v>565133</v>
       </c>
       <c r="R28" t="n">
-        <v>6683730</v>
+        <v>6683665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3620,32 +3620,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128353904</v>
+        <v>128354204</v>
       </c>
       <c r="B31" t="n">
-        <v>92775</v>
+        <v>86890</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565224</v>
+        <v>565325</v>
       </c>
       <c r="R31" t="n">
-        <v>6683766</v>
+        <v>6683920</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3717,48 +3717,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128356343</v>
+        <v>128354354</v>
       </c>
       <c r="B32" t="n">
-        <v>92775</v>
+        <v>92791</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565300</v>
+        <v>565289</v>
       </c>
       <c r="R32" t="n">
-        <v>6683931</v>
+        <v>6683828</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,22 +3802,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356336</v>
+        <v>128356309</v>
       </c>
       <c r="B33" t="n">
-        <v>92775</v>
+        <v>92759</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565294</v>
+        <v>565184</v>
       </c>
       <c r="R33" t="n">
-        <v>6683885</v>
+        <v>6683739</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,45 +3911,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356309</v>
+        <v>128356255</v>
       </c>
       <c r="B34" t="n">
-        <v>92759</v>
+        <v>92402</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565184</v>
+        <v>565128</v>
       </c>
       <c r="R34" t="n">
-        <v>6683739</v>
+        <v>6683585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4013,10 +4017,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128354204</v>
+        <v>128356250</v>
       </c>
       <c r="B35" t="n">
-        <v>86890</v>
+        <v>92402</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,37 +4028,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565325</v>
+        <v>565136</v>
       </c>
       <c r="R35" t="n">
-        <v>6683920</v>
+        <v>6683681</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4098,69 +4111,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356255</v>
+        <v>128353904</v>
       </c>
       <c r="B36" t="n">
-        <v>92402</v>
+        <v>92775</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565128</v>
+        <v>565224</v>
       </c>
       <c r="R36" t="n">
-        <v>6683585</v>
+        <v>6683766</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4204,66 +4208,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356250</v>
+        <v>128356343</v>
       </c>
       <c r="B37" t="n">
-        <v>92402</v>
+        <v>92775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565136</v>
+        <v>565300</v>
       </c>
       <c r="R37" t="n">
-        <v>6683681</v>
+        <v>6683931</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,48 +4317,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128354354</v>
+        <v>128356336</v>
       </c>
       <c r="B38" t="n">
-        <v>92791</v>
+        <v>92775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565289</v>
+        <v>565294</v>
       </c>
       <c r="R38" t="n">
-        <v>6683828</v>
+        <v>6683885</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4393,6 +4388,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4407,12 +4407,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4834,37 +4834,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356326</v>
+        <v>128356219</v>
       </c>
       <c r="B43" t="n">
-        <v>92791</v>
+        <v>90987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>256335</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565306</v>
+        <v>565287</v>
       </c>
       <c r="R43" t="n">
-        <v>6683915</v>
+        <v>6683892</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,6 +4922,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4940,37 +4941,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356219</v>
+        <v>128356326</v>
       </c>
       <c r="B44" t="n">
-        <v>90987</v>
+        <v>92791</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256335</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4984,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565287</v>
+        <v>565306</v>
       </c>
       <c r="R44" t="n">
-        <v>6683892</v>
+        <v>6683915</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,7 +5029,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5356,54 +5356,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128356374</v>
+        <v>128356350</v>
       </c>
       <c r="B48" t="n">
-        <v>86890</v>
+        <v>92775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565325</v>
+        <v>565128</v>
       </c>
       <c r="R48" t="n">
-        <v>6683931</v>
+        <v>6683651</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5850,45 +5841,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356350</v>
+        <v>128356374</v>
       </c>
       <c r="B53" t="n">
-        <v>92775</v>
+        <v>86890</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4368</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565128</v>
+        <v>565325</v>
       </c>
       <c r="R53" t="n">
-        <v>6683651</v>
+        <v>6683931</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356316</v>
+        <v>128353737</v>
       </c>
       <c r="B54" t="n">
-        <v>92791</v>
+        <v>86729</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,46 +5958,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565125</v>
+        <v>565164</v>
       </c>
       <c r="R54" t="n">
-        <v>6683662</v>
+        <v>6683706</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6041,49 +6032,49 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356294</v>
+        <v>128356236</v>
       </c>
       <c r="B55" t="n">
-        <v>91002</v>
+        <v>92402</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6097,10 +6088,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565290</v>
+        <v>565136</v>
       </c>
       <c r="R55" t="n">
-        <v>6683893</v>
+        <v>6683697</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,10 +6150,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356320</v>
+        <v>128356257</v>
       </c>
       <c r="B56" t="n">
-        <v>92791</v>
+        <v>92402</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,26 +6161,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6203,10 +6194,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565213</v>
+        <v>565243</v>
       </c>
       <c r="R56" t="n">
-        <v>6683796</v>
+        <v>6683765</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6265,48 +6256,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128353737</v>
+        <v>128356356</v>
       </c>
       <c r="B57" t="n">
-        <v>86729</v>
+        <v>92775</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565164</v>
+        <v>565307</v>
       </c>
       <c r="R57" t="n">
-        <v>6683706</v>
+        <v>6683932</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6350,66 +6341,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356236</v>
+        <v>128356352</v>
       </c>
       <c r="B58" t="n">
-        <v>92402</v>
+        <v>92775</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565136</v>
+        <v>565124</v>
       </c>
       <c r="R58" t="n">
-        <v>6683697</v>
+        <v>6683563</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6468,10 +6450,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356257</v>
+        <v>128356316</v>
       </c>
       <c r="B59" t="n">
-        <v>92402</v>
+        <v>92791</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6479,26 +6461,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6512,10 +6494,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565243</v>
+        <v>565125</v>
       </c>
       <c r="R59" t="n">
-        <v>6683765</v>
+        <v>6683662</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6574,45 +6556,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356356</v>
+        <v>128356294</v>
       </c>
       <c r="B60" t="n">
-        <v>92775</v>
+        <v>91002</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565307</v>
+        <v>565290</v>
       </c>
       <c r="R60" t="n">
-        <v>6683932</v>
+        <v>6683893</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6671,45 +6662,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356352</v>
+        <v>128356320</v>
       </c>
       <c r="B61" t="n">
-        <v>92775</v>
+        <v>92791</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565124</v>
+        <v>565213</v>
       </c>
       <c r="R61" t="n">
-        <v>6683563</v>
+        <v>6683796</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356322</v>
+        <v>128356270</v>
       </c>
       <c r="B64" t="n">
-        <v>92791</v>
+        <v>92769</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,43 +6973,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565121</v>
+        <v>565281</v>
       </c>
       <c r="R64" t="n">
-        <v>6683569</v>
+        <v>6683884</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7068,10 +7059,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356259</v>
+        <v>128356322</v>
       </c>
       <c r="B65" t="n">
-        <v>92402</v>
+        <v>92791</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,26 +7070,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7112,10 +7103,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565167</v>
+        <v>565121</v>
       </c>
       <c r="R65" t="n">
-        <v>6683728</v>
+        <v>6683569</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,10 +7165,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356270</v>
+        <v>128356259</v>
       </c>
       <c r="B66" t="n">
-        <v>92769</v>
+        <v>92402</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7185,34 +7176,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565281</v>
+        <v>565167</v>
       </c>
       <c r="R66" t="n">
-        <v>6683884</v>
+        <v>6683728</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128354079</v>
+        <v>128354308</v>
       </c>
       <c r="B69" t="n">
-        <v>92759</v>
+        <v>100780</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565281</v>
+        <v>565341</v>
       </c>
       <c r="R69" t="n">
-        <v>6683847</v>
+        <v>6683943</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7571,48 +7571,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356286</v>
+        <v>128354290</v>
       </c>
       <c r="B70" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565257</v>
+        <v>565327</v>
       </c>
       <c r="R70" t="n">
-        <v>6683775</v>
+        <v>6683939</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7656,19 +7656,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356288</v>
+        <v>128356286</v>
       </c>
       <c r="B71" t="n">
         <v>86729</v>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565128</v>
+        <v>565257</v>
       </c>
       <c r="R71" t="n">
-        <v>6683644</v>
+        <v>6683775</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356231</v>
+        <v>128356288</v>
       </c>
       <c r="B72" t="n">
-        <v>92402</v>
+        <v>86729</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7776,43 +7776,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565261</v>
+        <v>565128</v>
       </c>
       <c r="R72" t="n">
-        <v>6683777</v>
+        <v>6683644</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7871,10 +7862,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128356331</v>
+        <v>128356231</v>
       </c>
       <c r="B73" t="n">
-        <v>92791</v>
+        <v>92402</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,26 +7873,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7915,10 +7906,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565298</v>
+        <v>565261</v>
       </c>
       <c r="R73" t="n">
-        <v>6683926</v>
+        <v>6683777</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7977,32 +7968,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128354308</v>
+        <v>128354079</v>
       </c>
       <c r="B74" t="n">
-        <v>100780</v>
+        <v>92759</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8012,10 +8003,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565341</v>
+        <v>565281</v>
       </c>
       <c r="R74" t="n">
-        <v>6683943</v>
+        <v>6683847</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8074,48 +8065,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128354290</v>
+        <v>128356331</v>
       </c>
       <c r="B75" t="n">
-        <v>86927</v>
+        <v>92791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565327</v>
+        <v>565298</v>
       </c>
       <c r="R75" t="n">
-        <v>6683939</v>
+        <v>6683926</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8159,44 +8159,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356344</v>
+        <v>128356363</v>
       </c>
       <c r="B76" t="n">
-        <v>92775</v>
+        <v>100780</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565307</v>
+        <v>565298</v>
       </c>
       <c r="R76" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8268,45 +8268,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128353641</v>
+        <v>128354266</v>
       </c>
       <c r="B77" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565149</v>
+        <v>565313</v>
       </c>
       <c r="R77" t="n">
-        <v>6683686</v>
+        <v>6683939</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8365,48 +8365,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128354183</v>
+        <v>128356344</v>
       </c>
       <c r="B78" t="n">
-        <v>92402</v>
+        <v>92775</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565320</v>
+        <v>565307</v>
       </c>
       <c r="R78" t="n">
         <v>6683918</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8450,22 +8450,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356315</v>
+        <v>128353641</v>
       </c>
       <c r="B79" t="n">
-        <v>92791</v>
+        <v>86729</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8473,46 +8473,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565123</v>
+        <v>565149</v>
       </c>
       <c r="R79" t="n">
-        <v>6683582</v>
+        <v>6683686</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8556,22 +8547,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128356363</v>
+        <v>128354183</v>
       </c>
       <c r="B80" t="n">
-        <v>100780</v>
+        <v>92402</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8579,37 +8570,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565298</v>
+        <v>565320</v>
       </c>
       <c r="R80" t="n">
-        <v>6683884</v>
+        <v>6683918</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8653,60 +8644,69 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354266</v>
+        <v>128356315</v>
       </c>
       <c r="B81" t="n">
-        <v>86927</v>
+        <v>92791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565313</v>
+        <v>565123</v>
       </c>
       <c r="R81" t="n">
-        <v>6683939</v>
+        <v>6683582</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,12 +8750,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356348</v>
       </c>
       <c r="B2" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128356362</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128356327</v>
       </c>
       <c r="B4" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128353720</v>
+        <v>128356324</v>
       </c>
       <c r="B5" t="n">
-        <v>92769</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565171</v>
+        <v>565185</v>
       </c>
       <c r="R5" t="n">
-        <v>6683703</v>
+        <v>6683745</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,44 +1069,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356311</v>
+        <v>128356335</v>
       </c>
       <c r="B6" t="n">
-        <v>92759</v>
+        <v>92818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565121</v>
+        <v>565323</v>
       </c>
       <c r="R6" t="n">
-        <v>6683581</v>
+        <v>6683839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1152,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,54 +1183,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356237</v>
+        <v>128356311</v>
       </c>
       <c r="B7" t="n">
-        <v>92402</v>
+        <v>92786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565304</v>
+        <v>565121</v>
       </c>
       <c r="R7" t="n">
-        <v>6683884</v>
+        <v>6683581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356324</v>
+        <v>128356237</v>
       </c>
       <c r="B8" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,26 +1291,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565185</v>
+        <v>565304</v>
       </c>
       <c r="R8" t="n">
-        <v>6683745</v>
+        <v>6683884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356335</v>
+        <v>128353720</v>
       </c>
       <c r="B9" t="n">
-        <v>92791</v>
+        <v>92796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,37 +1397,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565323</v>
+        <v>565171</v>
       </c>
       <c r="R9" t="n">
-        <v>6683839</v>
+        <v>6683703</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,11 +1457,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,12 +1471,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
         <v>128356260</v>
       </c>
       <c r="B10" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128356345</v>
       </c>
       <c r="B11" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,32 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128353600</v>
+        <v>128353570</v>
       </c>
       <c r="B12" t="n">
-        <v>92759</v>
+        <v>92818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565138</v>
+        <v>565129</v>
       </c>
       <c r="R12" t="n">
-        <v>6683661</v>
+        <v>6683660</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356235</v>
+        <v>128356325</v>
       </c>
       <c r="B13" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1794,26 +1794,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565149</v>
+        <v>565139</v>
       </c>
       <c r="R13" t="n">
-        <v>6683718</v>
+        <v>6683679</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,45 +1889,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356353</v>
+        <v>128356235</v>
       </c>
       <c r="B14" t="n">
-        <v>92775</v>
+        <v>92429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565118</v>
+        <v>565149</v>
       </c>
       <c r="R14" t="n">
-        <v>6683561</v>
+        <v>6683718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,32 +1995,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353570</v>
+        <v>128353600</v>
       </c>
       <c r="B15" t="n">
-        <v>92791</v>
+        <v>92786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565129</v>
+        <v>565138</v>
       </c>
       <c r="R15" t="n">
-        <v>6683660</v>
+        <v>6683661</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2083,54 +2092,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356325</v>
+        <v>128356353</v>
       </c>
       <c r="B16" t="n">
-        <v>92791</v>
+        <v>92802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565139</v>
+        <v>565118</v>
       </c>
       <c r="R16" t="n">
-        <v>6683679</v>
+        <v>6683561</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128356245</v>
+        <v>128353672</v>
       </c>
       <c r="B17" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,46 +2200,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565330</v>
+        <v>565163</v>
       </c>
       <c r="R17" t="n">
-        <v>6683935</v>
+        <v>6683698</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2283,22 +2274,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128353672</v>
+        <v>128356245</v>
       </c>
       <c r="B18" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,37 +2297,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565163</v>
+        <v>565330</v>
       </c>
       <c r="R18" t="n">
-        <v>6683698</v>
+        <v>6683935</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2380,12 +2380,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>128356342</v>
       </c>
       <c r="B19" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356338</v>
+        <v>128356349</v>
       </c>
       <c r="B20" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565124</v>
+        <v>565147</v>
       </c>
       <c r="R20" t="n">
-        <v>6683659</v>
+        <v>6683691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,11 +2560,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,10 +2586,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356349</v>
+        <v>128356338</v>
       </c>
       <c r="B21" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565147</v>
+        <v>565124</v>
       </c>
       <c r="R21" t="n">
-        <v>6683691</v>
+        <v>6683659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2662,6 +2657,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2691,7 +2691,7 @@
         <v>128356319</v>
       </c>
       <c r="B22" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>128356321</v>
       </c>
       <c r="B23" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128356323</v>
+        <v>128356332</v>
       </c>
       <c r="B24" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565127</v>
+        <v>565289</v>
       </c>
       <c r="R24" t="n">
-        <v>6683598</v>
+        <v>6683895</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128356332</v>
+        <v>128356323</v>
       </c>
       <c r="B25" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565289</v>
+        <v>565127</v>
       </c>
       <c r="R25" t="n">
-        <v>6683895</v>
+        <v>6683598</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
         <v>128356333</v>
       </c>
       <c r="B26" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>128356346</v>
       </c>
       <c r="B27" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128356287</v>
       </c>
       <c r="B28" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,45 +3412,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128356337</v>
+        <v>128356248</v>
       </c>
       <c r="B29" t="n">
-        <v>92775</v>
+        <v>92429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565149</v>
+        <v>565207</v>
       </c>
       <c r="R29" t="n">
-        <v>6683707</v>
+        <v>6683770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,11 +3492,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3514,54 +3518,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128356248</v>
+        <v>128356337</v>
       </c>
       <c r="B30" t="n">
-        <v>92402</v>
+        <v>92802</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565207</v>
+        <v>565149</v>
       </c>
       <c r="R30" t="n">
-        <v>6683770</v>
+        <v>6683707</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,6 +3589,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128354204</v>
+        <v>128354354</v>
       </c>
       <c r="B31" t="n">
-        <v>86890</v>
+        <v>92818</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,21 +3631,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565325</v>
+        <v>565289</v>
       </c>
       <c r="R31" t="n">
-        <v>6683920</v>
+        <v>6683828</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128354354</v>
+        <v>128356276</v>
       </c>
       <c r="B32" t="n">
-        <v>92791</v>
+        <v>97490</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,37 +3728,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565289</v>
+        <v>565383</v>
       </c>
       <c r="R32" t="n">
-        <v>6683828</v>
+        <v>6683939</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,12 +3802,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3817,7 +3817,7 @@
         <v>128356309</v>
       </c>
       <c r="B33" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3911,57 +3911,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356255</v>
+        <v>128353904</v>
       </c>
       <c r="B34" t="n">
-        <v>92402</v>
+        <v>92802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565128</v>
+        <v>565224</v>
       </c>
       <c r="R34" t="n">
-        <v>6683585</v>
+        <v>6683766</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4005,66 +3996,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356250</v>
+        <v>128356336</v>
       </c>
       <c r="B35" t="n">
-        <v>92402</v>
+        <v>92802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565136</v>
+        <v>565294</v>
       </c>
       <c r="R35" t="n">
-        <v>6683681</v>
+        <v>6683885</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,6 +4079,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,48 +4110,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128353904</v>
+        <v>128356250</v>
       </c>
       <c r="B36" t="n">
-        <v>92775</v>
+        <v>92429</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565224</v>
+        <v>565136</v>
       </c>
       <c r="R36" t="n">
-        <v>6683766</v>
+        <v>6683681</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4208,57 +4204,66 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356343</v>
+        <v>128356255</v>
       </c>
       <c r="B37" t="n">
-        <v>92775</v>
+        <v>92429</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565300</v>
+        <v>565128</v>
       </c>
       <c r="R37" t="n">
-        <v>6683931</v>
+        <v>6683585</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,10 +4322,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128356336</v>
+        <v>128356343</v>
       </c>
       <c r="B38" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,10 +4357,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565294</v>
+        <v>565300</v>
       </c>
       <c r="R38" t="n">
-        <v>6683885</v>
+        <v>6683931</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,11 +4393,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128356276</v>
+        <v>128354204</v>
       </c>
       <c r="B39" t="n">
-        <v>97463</v>
+        <v>86917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,37 +4430,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565383</v>
+        <v>565325</v>
       </c>
       <c r="R39" t="n">
-        <v>6683939</v>
+        <v>6683920</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4504,22 +4504,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356252</v>
+        <v>128356234</v>
       </c>
       <c r="B40" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565313</v>
+        <v>565304</v>
       </c>
       <c r="R40" t="n">
-        <v>6683875</v>
+        <v>6683798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4625,7 +4625,7 @@
         <v>128356240</v>
       </c>
       <c r="B41" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356234</v>
+        <v>128356252</v>
       </c>
       <c r="B42" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565304</v>
+        <v>565313</v>
       </c>
       <c r="R42" t="n">
-        <v>6683798</v>
+        <v>6683875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4837,7 +4837,7 @@
         <v>128356219</v>
       </c>
       <c r="B43" t="n">
-        <v>90987</v>
+        <v>91014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>128356326</v>
       </c>
       <c r="B44" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>128356351</v>
       </c>
       <c r="B45" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356317</v>
+        <v>128356262</v>
       </c>
       <c r="B46" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5155,26 +5155,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565188</v>
+        <v>565306</v>
       </c>
       <c r="R46" t="n">
-        <v>6683735</v>
+        <v>6683913</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356262</v>
+        <v>128356317</v>
       </c>
       <c r="B47" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,26 +5261,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565306</v>
+        <v>565188</v>
       </c>
       <c r="R47" t="n">
-        <v>6683913</v>
+        <v>6683735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5356,10 +5356,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128356350</v>
+        <v>128356307</v>
       </c>
       <c r="B48" t="n">
-        <v>92775</v>
+        <v>92786</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5367,21 +5367,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565128</v>
+        <v>565193</v>
       </c>
       <c r="R48" t="n">
-        <v>6683651</v>
+        <v>6683755</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,45 +5453,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128353745</v>
+        <v>128353808</v>
       </c>
       <c r="B49" t="n">
-        <v>92791</v>
+        <v>92786</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565166</v>
+        <v>565189</v>
       </c>
       <c r="R49" t="n">
-        <v>6683711</v>
+        <v>6683740</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128353808</v>
+        <v>128356310</v>
       </c>
       <c r="B50" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5581,17 +5581,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565189</v>
+        <v>565306</v>
       </c>
       <c r="R50" t="n">
-        <v>6683740</v>
+        <v>6683913</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5635,60 +5635,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128356307</v>
+        <v>128353745</v>
       </c>
       <c r="B51" t="n">
-        <v>92759</v>
+        <v>92818</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565193</v>
+        <v>565166</v>
       </c>
       <c r="R51" t="n">
-        <v>6683755</v>
+        <v>6683711</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5732,57 +5732,66 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128356310</v>
+        <v>128356374</v>
       </c>
       <c r="B52" t="n">
-        <v>92759</v>
+        <v>86917</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>788</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565306</v>
+        <v>565325</v>
       </c>
       <c r="R52" t="n">
-        <v>6683913</v>
+        <v>6683931</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,54 +5850,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356374</v>
+        <v>128356350</v>
       </c>
       <c r="B53" t="n">
-        <v>86890</v>
+        <v>92802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3674</v>
+        <v>4368</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565325</v>
+        <v>565128</v>
       </c>
       <c r="R53" t="n">
-        <v>6683931</v>
+        <v>6683651</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5947,48 +5947,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128353737</v>
+        <v>128356294</v>
       </c>
       <c r="B54" t="n">
-        <v>86729</v>
+        <v>91029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3762</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565164</v>
+        <v>565290</v>
       </c>
       <c r="R54" t="n">
-        <v>6683706</v>
+        <v>6683893</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6032,22 +6041,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356236</v>
+        <v>128356320</v>
       </c>
       <c r="B55" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6055,26 +6064,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6088,10 +6097,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565136</v>
+        <v>565213</v>
       </c>
       <c r="R55" t="n">
-        <v>6683697</v>
+        <v>6683796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6150,10 +6159,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356257</v>
+        <v>128356316</v>
       </c>
       <c r="B56" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6161,26 +6170,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6194,10 +6203,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565243</v>
+        <v>565125</v>
       </c>
       <c r="R56" t="n">
-        <v>6683765</v>
+        <v>6683662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,48 +6265,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356356</v>
+        <v>128353737</v>
       </c>
       <c r="B57" t="n">
-        <v>92775</v>
+        <v>86756</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565307</v>
+        <v>565164</v>
       </c>
       <c r="R57" t="n">
-        <v>6683932</v>
+        <v>6683706</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6341,57 +6350,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356352</v>
+        <v>128356257</v>
       </c>
       <c r="B58" t="n">
-        <v>92775</v>
+        <v>92429</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565124</v>
+        <v>565243</v>
       </c>
       <c r="R58" t="n">
-        <v>6683563</v>
+        <v>6683765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6450,10 +6468,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356316</v>
+        <v>128356236</v>
       </c>
       <c r="B59" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6461,26 +6479,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6494,10 +6512,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565125</v>
+        <v>565136</v>
       </c>
       <c r="R59" t="n">
-        <v>6683662</v>
+        <v>6683697</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6556,54 +6574,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356294</v>
+        <v>128356352</v>
       </c>
       <c r="B60" t="n">
-        <v>91002</v>
+        <v>92802</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565290</v>
+        <v>565124</v>
       </c>
       <c r="R60" t="n">
-        <v>6683893</v>
+        <v>6683563</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,54 +6671,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356320</v>
+        <v>128356356</v>
       </c>
       <c r="B61" t="n">
-        <v>92791</v>
+        <v>92802</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565213</v>
+        <v>565307</v>
       </c>
       <c r="R61" t="n">
-        <v>6683796</v>
+        <v>6683932</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6771,7 +6771,7 @@
         <v>128356360</v>
       </c>
       <c r="B62" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128353797</v>
+        <v>128356322</v>
       </c>
       <c r="B63" t="n">
-        <v>86729</v>
+        <v>92818</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,37 +6876,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565197</v>
+        <v>565121</v>
       </c>
       <c r="R63" t="n">
-        <v>6683732</v>
+        <v>6683569</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6950,22 +6959,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128356270</v>
+        <v>128353797</v>
       </c>
       <c r="B64" t="n">
-        <v>92769</v>
+        <v>86756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6973,37 +6982,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565281</v>
+        <v>565197</v>
       </c>
       <c r="R64" t="n">
-        <v>6683884</v>
+        <v>6683732</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7047,22 +7056,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356322</v>
+        <v>128356270</v>
       </c>
       <c r="B65" t="n">
-        <v>92791</v>
+        <v>92796</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,43 +7079,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565121</v>
+        <v>565281</v>
       </c>
       <c r="R65" t="n">
-        <v>6683569</v>
+        <v>6683884</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7168,7 +7168,7 @@
         <v>128356259</v>
       </c>
       <c r="B66" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>128356261</v>
       </c>
       <c r="B67" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>128356361</v>
       </c>
       <c r="B68" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128354308</v>
+        <v>128356331</v>
       </c>
       <c r="B69" t="n">
-        <v>100780</v>
+        <v>92818</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7485,37 +7485,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565341</v>
+        <v>565298</v>
       </c>
       <c r="R69" t="n">
-        <v>6683943</v>
+        <v>6683926</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7559,60 +7568,69 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128354290</v>
+        <v>128356231</v>
       </c>
       <c r="B70" t="n">
-        <v>86927</v>
+        <v>92429</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565327</v>
+        <v>565261</v>
       </c>
       <c r="R70" t="n">
-        <v>6683939</v>
+        <v>6683777</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7656,22 +7674,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128356286</v>
+        <v>128354308</v>
       </c>
       <c r="B71" t="n">
-        <v>86729</v>
+        <v>100807</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7679,37 +7697,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565257</v>
+        <v>565341</v>
       </c>
       <c r="R71" t="n">
-        <v>6683775</v>
+        <v>6683943</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7753,12 +7771,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7768,7 +7786,7 @@
         <v>128356288</v>
       </c>
       <c r="B72" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7862,10 +7880,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128356231</v>
+        <v>128356286</v>
       </c>
       <c r="B73" t="n">
-        <v>92402</v>
+        <v>86756</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7873,43 +7891,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565261</v>
+        <v>565257</v>
       </c>
       <c r="R73" t="n">
-        <v>6683777</v>
+        <v>6683775</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7971,7 +7980,7 @@
         <v>128354079</v>
       </c>
       <c r="B74" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8065,57 +8074,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128356331</v>
+        <v>128354290</v>
       </c>
       <c r="B75" t="n">
-        <v>92791</v>
+        <v>86954</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565298</v>
+        <v>565327</v>
       </c>
       <c r="R75" t="n">
-        <v>6683926</v>
+        <v>6683939</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8159,22 +8159,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356363</v>
+        <v>128353641</v>
       </c>
       <c r="B76" t="n">
-        <v>100780</v>
+        <v>86756</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8182,37 +8182,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565298</v>
+        <v>565149</v>
       </c>
       <c r="R76" t="n">
-        <v>6683884</v>
+        <v>6683686</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8256,12 +8256,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8271,7 +8271,7 @@
         <v>128354266</v>
       </c>
       <c r="B77" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8365,45 +8365,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128356344</v>
+        <v>128356315</v>
       </c>
       <c r="B78" t="n">
-        <v>92775</v>
+        <v>92818</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565307</v>
+        <v>565123</v>
       </c>
       <c r="R78" t="n">
-        <v>6683918</v>
+        <v>6683582</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8462,48 +8471,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128353641</v>
+        <v>128356344</v>
       </c>
       <c r="B79" t="n">
-        <v>86729</v>
+        <v>92802</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565149</v>
+        <v>565307</v>
       </c>
       <c r="R79" t="n">
-        <v>6683686</v>
+        <v>6683918</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8547,12 +8556,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8562,7 +8571,7 @@
         <v>128354183</v>
       </c>
       <c r="B80" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8656,10 +8665,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128356315</v>
+        <v>128356363</v>
       </c>
       <c r="B81" t="n">
-        <v>92791</v>
+        <v>100807</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8667,43 +8676,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565123</v>
+        <v>565298</v>
       </c>
       <c r="R81" t="n">
-        <v>6683582</v>
+        <v>6683884</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8765,7 +8765,7 @@
         <v>128356334</v>
       </c>
       <c r="B82" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>128356318</v>
       </c>
       <c r="B83" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>128356330</v>
       </c>
       <c r="B84" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>128379692</v>
       </c>
       <c r="B85" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128379701</v>
       </c>
       <c r="B86" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -975,54 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356324</v>
+        <v>128356311</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565185</v>
+        <v>565121</v>
       </c>
       <c r="R5" t="n">
-        <v>6683745</v>
+        <v>6683581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356335</v>
+        <v>128356324</v>
       </c>
       <c r="B6" t="n">
         <v>92818</v>
@@ -1109,17 +1100,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565323</v>
+        <v>565185</v>
       </c>
       <c r="R6" t="n">
-        <v>6683839</v>
+        <v>6683745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,32 +1178,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356311</v>
+        <v>128356335</v>
       </c>
       <c r="B7" t="n">
-        <v>92786</v>
+        <v>92818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565121</v>
+        <v>565323</v>
       </c>
       <c r="R7" t="n">
-        <v>6683581</v>
+        <v>6683839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1483,54 +1483,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128356260</v>
+        <v>128356345</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565139</v>
+        <v>565282</v>
       </c>
       <c r="R10" t="n">
-        <v>6683696</v>
+        <v>6683847</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,45 +1580,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128356345</v>
+        <v>128356260</v>
       </c>
       <c r="B11" t="n">
-        <v>92802</v>
+        <v>92429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565282</v>
+        <v>565139</v>
       </c>
       <c r="R11" t="n">
-        <v>6683847</v>
+        <v>6683696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,32 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128353570</v>
+        <v>128353600</v>
       </c>
       <c r="B12" t="n">
-        <v>92818</v>
+        <v>92786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565129</v>
+        <v>565138</v>
       </c>
       <c r="R12" t="n">
-        <v>6683660</v>
+        <v>6683661</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1783,54 +1783,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356325</v>
+        <v>128356353</v>
       </c>
       <c r="B13" t="n">
-        <v>92818</v>
+        <v>92802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565139</v>
+        <v>565118</v>
       </c>
       <c r="R13" t="n">
-        <v>6683679</v>
+        <v>6683561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,10 +1880,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356235</v>
+        <v>128353570</v>
       </c>
       <c r="B14" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,46 +1891,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565149</v>
+        <v>565129</v>
       </c>
       <c r="R14" t="n">
-        <v>6683718</v>
+        <v>6683660</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1983,60 +1965,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128353600</v>
+        <v>128356325</v>
       </c>
       <c r="B15" t="n">
-        <v>92786</v>
+        <v>92818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565138</v>
+        <v>565139</v>
       </c>
       <c r="R15" t="n">
-        <v>6683661</v>
+        <v>6683679</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2080,57 +2071,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356353</v>
+        <v>128356235</v>
       </c>
       <c r="B16" t="n">
-        <v>92802</v>
+        <v>92429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565118</v>
+        <v>565149</v>
       </c>
       <c r="R16" t="n">
-        <v>6683561</v>
+        <v>6683718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356349</v>
+        <v>128356338</v>
       </c>
       <c r="B20" t="n">
         <v>92802</v>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565147</v>
+        <v>565124</v>
       </c>
       <c r="R20" t="n">
-        <v>6683691</v>
+        <v>6683659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,6 +2560,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,7 +2591,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356338</v>
+        <v>128356349</v>
       </c>
       <c r="B21" t="n">
         <v>92802</v>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565124</v>
+        <v>565147</v>
       </c>
       <c r="R21" t="n">
-        <v>6683659</v>
+        <v>6683691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,11 +2662,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,7 +2900,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128356332</v>
+        <v>128356323</v>
       </c>
       <c r="B24" t="n">
         <v>92818</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565289</v>
+        <v>565127</v>
       </c>
       <c r="R24" t="n">
-        <v>6683895</v>
+        <v>6683598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128356323</v>
+        <v>128356332</v>
       </c>
       <c r="B25" t="n">
         <v>92818</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565127</v>
+        <v>565289</v>
       </c>
       <c r="R25" t="n">
-        <v>6683598</v>
+        <v>6683895</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,54 +3412,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128356248</v>
+        <v>128356337</v>
       </c>
       <c r="B29" t="n">
-        <v>92429</v>
+        <v>92802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565207</v>
+        <v>565149</v>
       </c>
       <c r="R29" t="n">
-        <v>6683770</v>
+        <v>6683707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,6 +3483,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,45 +3514,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128356337</v>
+        <v>128356248</v>
       </c>
       <c r="B30" t="n">
-        <v>92802</v>
+        <v>92429</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565149</v>
+        <v>565207</v>
       </c>
       <c r="R30" t="n">
-        <v>6683707</v>
+        <v>6683770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,11 +3594,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128354354</v>
+        <v>128356276</v>
       </c>
       <c r="B31" t="n">
-        <v>92818</v>
+        <v>97490</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,37 +3631,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565289</v>
+        <v>565383</v>
       </c>
       <c r="R31" t="n">
-        <v>6683828</v>
+        <v>6683939</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3705,44 +3705,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128356276</v>
+        <v>128356309</v>
       </c>
       <c r="B32" t="n">
-        <v>97490</v>
+        <v>92786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>788</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565383</v>
+        <v>565184</v>
       </c>
       <c r="R32" t="n">
-        <v>6683939</v>
+        <v>6683739</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,48 +3814,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128356309</v>
+        <v>128354204</v>
       </c>
       <c r="B33" t="n">
-        <v>92786</v>
+        <v>86917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>788</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565184</v>
+        <v>565325</v>
       </c>
       <c r="R33" t="n">
-        <v>6683739</v>
+        <v>6683920</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3899,12 +3899,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128356336</v>
+        <v>128356343</v>
       </c>
       <c r="B35" t="n">
         <v>92802</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565294</v>
+        <v>565300</v>
       </c>
       <c r="R35" t="n">
-        <v>6683885</v>
+        <v>6683931</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,11 +4079,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4110,54 +4105,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356250</v>
+        <v>128356336</v>
       </c>
       <c r="B36" t="n">
-        <v>92429</v>
+        <v>92802</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565136</v>
+        <v>565294</v>
       </c>
       <c r="R36" t="n">
-        <v>6683681</v>
+        <v>6683885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,6 +4176,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4216,10 +4207,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356255</v>
+        <v>128354354</v>
       </c>
       <c r="B37" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,46 +4218,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565128</v>
+        <v>565289</v>
       </c>
       <c r="R37" t="n">
-        <v>6683585</v>
+        <v>6683828</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4310,57 +4292,66 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128356343</v>
+        <v>128356255</v>
       </c>
       <c r="B38" t="n">
-        <v>92802</v>
+        <v>92429</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565300</v>
+        <v>565128</v>
       </c>
       <c r="R38" t="n">
-        <v>6683931</v>
+        <v>6683585</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4419,10 +4410,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128354204</v>
+        <v>128356250</v>
       </c>
       <c r="B39" t="n">
-        <v>86917</v>
+        <v>92429</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,37 +4421,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565325</v>
+        <v>565136</v>
       </c>
       <c r="R39" t="n">
-        <v>6683920</v>
+        <v>6683681</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4504,22 +4504,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356234</v>
+        <v>128356326</v>
       </c>
       <c r="B40" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,26 +4527,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565304</v>
+        <v>565306</v>
       </c>
       <c r="R40" t="n">
-        <v>6683798</v>
+        <v>6683915</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356240</v>
+        <v>128356252</v>
       </c>
       <c r="B41" t="n">
         <v>92429</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R41" t="n">
-        <v>6683931</v>
+        <v>6683875</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356252</v>
+        <v>128356240</v>
       </c>
       <c r="B42" t="n">
         <v>92429</v>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565313</v>
+        <v>565298</v>
       </c>
       <c r="R42" t="n">
-        <v>6683875</v>
+        <v>6683931</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4834,37 +4834,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356219</v>
+        <v>128356234</v>
       </c>
       <c r="B43" t="n">
-        <v>91014</v>
+        <v>92429</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>256335</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565287</v>
+        <v>565304</v>
       </c>
       <c r="R43" t="n">
-        <v>6683892</v>
+        <v>6683798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4941,37 +4940,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356326</v>
+        <v>128356219</v>
       </c>
       <c r="B44" t="n">
-        <v>92818</v>
+        <v>91014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>256335</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4985,10 +4984,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565306</v>
+        <v>565287</v>
       </c>
       <c r="R44" t="n">
-        <v>6683915</v>
+        <v>6683892</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,6 +5028,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356262</v>
+        <v>128356317</v>
       </c>
       <c r="B46" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5155,26 +5155,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565306</v>
+        <v>565188</v>
       </c>
       <c r="R46" t="n">
-        <v>6683913</v>
+        <v>6683735</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356317</v>
+        <v>128356262</v>
       </c>
       <c r="B47" t="n">
-        <v>92818</v>
+        <v>92429</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,26 +5261,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565188</v>
+        <v>565306</v>
       </c>
       <c r="R47" t="n">
-        <v>6683735</v>
+        <v>6683913</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128353745</v>
+        <v>128356374</v>
       </c>
       <c r="B51" t="n">
-        <v>92818</v>
+        <v>86917</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,37 +5658,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565166</v>
+        <v>565325</v>
       </c>
       <c r="R51" t="n">
-        <v>6683711</v>
+        <v>6683931</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5732,66 +5741,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128356374</v>
+        <v>128356350</v>
       </c>
       <c r="B52" t="n">
-        <v>86917</v>
+        <v>92802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>4368</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565325</v>
+        <v>565128</v>
       </c>
       <c r="R52" t="n">
-        <v>6683931</v>
+        <v>6683651</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5850,48 +5850,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356350</v>
+        <v>128353745</v>
       </c>
       <c r="B53" t="n">
-        <v>92802</v>
+        <v>92818</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565128</v>
+        <v>565166</v>
       </c>
       <c r="R53" t="n">
-        <v>6683651</v>
+        <v>6683711</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5935,66 +5935,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356294</v>
+        <v>128356356</v>
       </c>
       <c r="B54" t="n">
-        <v>91029</v>
+        <v>92802</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565290</v>
+        <v>565307</v>
       </c>
       <c r="R54" t="n">
-        <v>6683893</v>
+        <v>6683932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6053,54 +6044,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356320</v>
+        <v>128356352</v>
       </c>
       <c r="B55" t="n">
-        <v>92818</v>
+        <v>92802</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565213</v>
+        <v>565124</v>
       </c>
       <c r="R55" t="n">
-        <v>6683796</v>
+        <v>6683563</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,10 +6141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356316</v>
+        <v>128353737</v>
       </c>
       <c r="B56" t="n">
-        <v>92818</v>
+        <v>86756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,46 +6152,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565125</v>
+        <v>565164</v>
       </c>
       <c r="R56" t="n">
-        <v>6683662</v>
+        <v>6683706</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6253,22 +6226,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128353737</v>
+        <v>128356316</v>
       </c>
       <c r="B57" t="n">
-        <v>86756</v>
+        <v>92818</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6276,37 +6249,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565164</v>
+        <v>565125</v>
       </c>
       <c r="R57" t="n">
-        <v>6683706</v>
+        <v>6683662</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6350,22 +6332,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356257</v>
+        <v>128356320</v>
       </c>
       <c r="B58" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6373,26 +6355,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6406,10 +6388,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565243</v>
+        <v>565213</v>
       </c>
       <c r="R58" t="n">
-        <v>6683765</v>
+        <v>6683796</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6574,45 +6556,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128356352</v>
+        <v>128356294</v>
       </c>
       <c r="B60" t="n">
-        <v>92802</v>
+        <v>91029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565124</v>
+        <v>565290</v>
       </c>
       <c r="R60" t="n">
-        <v>6683563</v>
+        <v>6683893</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6671,45 +6662,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356356</v>
+        <v>128356257</v>
       </c>
       <c r="B61" t="n">
-        <v>92802</v>
+        <v>92429</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565307</v>
+        <v>565243</v>
       </c>
       <c r="R61" t="n">
-        <v>6683932</v>
+        <v>6683765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128356322</v>
+        <v>128353797</v>
       </c>
       <c r="B63" t="n">
-        <v>92818</v>
+        <v>86756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6876,46 +6876,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565121</v>
+        <v>565197</v>
       </c>
       <c r="R63" t="n">
-        <v>6683569</v>
+        <v>6683732</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6959,22 +6950,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128353797</v>
+        <v>128356270</v>
       </c>
       <c r="B64" t="n">
-        <v>86756</v>
+        <v>92796</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6982,37 +6973,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565197</v>
+        <v>565281</v>
       </c>
       <c r="R64" t="n">
-        <v>6683732</v>
+        <v>6683884</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7056,22 +7047,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356270</v>
+        <v>128356322</v>
       </c>
       <c r="B65" t="n">
-        <v>92796</v>
+        <v>92818</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7079,34 +7070,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565281</v>
+        <v>565121</v>
       </c>
       <c r="R65" t="n">
-        <v>6683884</v>
+        <v>6683569</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128356261</v>
+        <v>128356361</v>
       </c>
       <c r="B67" t="n">
-        <v>92429</v>
+        <v>100807</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,43 +7282,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565331</v>
+        <v>565330</v>
       </c>
       <c r="R67" t="n">
-        <v>6683832</v>
+        <v>6683934</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7377,10 +7368,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128356361</v>
+        <v>128356261</v>
       </c>
       <c r="B68" t="n">
-        <v>100807</v>
+        <v>92429</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7388,34 +7379,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565330</v>
+        <v>565331</v>
       </c>
       <c r="R68" t="n">
-        <v>6683934</v>
+        <v>6683832</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128356331</v>
+        <v>128356288</v>
       </c>
       <c r="B69" t="n">
-        <v>92818</v>
+        <v>86756</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7485,43 +7485,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565298</v>
+        <v>565128</v>
       </c>
       <c r="R69" t="n">
-        <v>6683926</v>
+        <v>6683644</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7580,10 +7571,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356231</v>
+        <v>128356286</v>
       </c>
       <c r="B70" t="n">
-        <v>92429</v>
+        <v>86756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7591,43 +7582,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565261</v>
+        <v>565257</v>
       </c>
       <c r="R70" t="n">
-        <v>6683777</v>
+        <v>6683775</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,48 +7765,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128356288</v>
+        <v>128354079</v>
       </c>
       <c r="B72" t="n">
-        <v>86756</v>
+        <v>92786</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565128</v>
+        <v>565281</v>
       </c>
       <c r="R72" t="n">
-        <v>6683644</v>
+        <v>6683847</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7868,22 +7850,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128356286</v>
+        <v>128356331</v>
       </c>
       <c r="B73" t="n">
-        <v>86756</v>
+        <v>92818</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,34 +7873,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565257</v>
+        <v>565298</v>
       </c>
       <c r="R73" t="n">
-        <v>6683775</v>
+        <v>6683926</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7977,48 +7968,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128354079</v>
+        <v>128356231</v>
       </c>
       <c r="B74" t="n">
-        <v>92786</v>
+        <v>92429</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565281</v>
+        <v>565261</v>
       </c>
       <c r="R74" t="n">
-        <v>6683847</v>
+        <v>6683777</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8062,12 +8062,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128354266</v>
+        <v>128356344</v>
       </c>
       <c r="B77" t="n">
-        <v>86954</v>
+        <v>92802</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8279,37 +8279,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565313</v>
+        <v>565307</v>
       </c>
       <c r="R77" t="n">
-        <v>6683939</v>
+        <v>6683918</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8353,12 +8353,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8471,32 +8471,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356344</v>
+        <v>128356363</v>
       </c>
       <c r="B79" t="n">
-        <v>92802</v>
+        <v>100807</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565307</v>
+        <v>565298</v>
       </c>
       <c r="R79" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8665,48 +8665,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128356363</v>
+        <v>128354266</v>
       </c>
       <c r="B81" t="n">
-        <v>100807</v>
+        <v>86954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565298</v>
+        <v>565313</v>
       </c>
       <c r="R81" t="n">
-        <v>6683884</v>
+        <v>6683939</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8750,12 +8750,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128356348</v>
+        <v>128353600</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565149</v>
+        <v>565138</v>
       </c>
       <c r="R2" t="n">
-        <v>6683699</v>
+        <v>6683661</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,69 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128356327</v>
+        <v>128353808</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565292</v>
+        <v>565189</v>
       </c>
       <c r="R3" t="n">
-        <v>6683907</v>
+        <v>6683740</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,60 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356362</v>
+        <v>128354079</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>93199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565302</v>
+        <v>565281</v>
       </c>
       <c r="R4" t="n">
-        <v>6683928</v>
+        <v>6683847</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356335</v>
+        <v>128356307</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>93199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565323</v>
+        <v>565193</v>
       </c>
       <c r="R5" t="n">
-        <v>6683839</v>
+        <v>6683755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356324</v>
+        <v>128356309</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>93199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565185</v>
+        <v>565184</v>
       </c>
       <c r="R6" t="n">
-        <v>6683745</v>
+        <v>6683739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128353720</v>
+        <v>128356310</v>
       </c>
       <c r="B7" t="n">
-        <v>92810</v>
+        <v>93199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565171</v>
+        <v>565306</v>
       </c>
       <c r="R7" t="n">
-        <v>6683703</v>
+        <v>6683913</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,66 +1245,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356237</v>
+        <v>128356311</v>
       </c>
       <c r="B8" t="n">
-        <v>92443</v>
+        <v>93199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565304</v>
+        <v>565121</v>
       </c>
       <c r="R8" t="n">
-        <v>6683884</v>
+        <v>6683581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356311</v>
+        <v>128379701</v>
       </c>
       <c r="B9" t="n">
-        <v>92800</v>
+        <v>93199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1415,19 +1383,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565121</v>
+        <v>565183</v>
       </c>
       <c r="R9" t="n">
-        <v>6683581</v>
+        <v>6683738</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,34 +1430,50 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6 m långt mycel</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128356345</v>
+        <v>120161061</v>
       </c>
       <c r="B10" t="n">
-        <v>92816</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,37 +1481,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565282</v>
+        <v>565172</v>
       </c>
       <c r="R10" t="n">
-        <v>6683847</v>
+        <v>6683606</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,12 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,22 +1555,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128356260</v>
+        <v>128354204</v>
       </c>
       <c r="B11" t="n">
-        <v>92443</v>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,46 +1578,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565139</v>
+        <v>565325</v>
       </c>
       <c r="R11" t="n">
-        <v>6683696</v>
+        <v>6683920</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,22 +1652,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128353570</v>
+        <v>128356374</v>
       </c>
       <c r="B12" t="n">
-        <v>92834</v>
+        <v>87309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,37 +1675,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565129</v>
+        <v>565325</v>
       </c>
       <c r="R12" t="n">
-        <v>6683660</v>
+        <v>6683931</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,22 +1758,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128356325</v>
+        <v>128353641</v>
       </c>
       <c r="B13" t="n">
-        <v>92834</v>
+        <v>87146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1794,46 +1781,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565139</v>
+        <v>565149</v>
       </c>
       <c r="R13" t="n">
-        <v>6683679</v>
+        <v>6683686</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,44 +1855,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128353600</v>
+        <v>128353737</v>
       </c>
       <c r="B14" t="n">
-        <v>92800</v>
+        <v>87146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565138</v>
+        <v>565164</v>
       </c>
       <c r="R14" t="n">
-        <v>6683661</v>
+        <v>6683706</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1986,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128356235</v>
+        <v>128353797</v>
       </c>
       <c r="B15" t="n">
-        <v>92443</v>
+        <v>87146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,46 +1975,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565149</v>
+        <v>565197</v>
       </c>
       <c r="R15" t="n">
-        <v>6683718</v>
+        <v>6683732</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2080,44 +2049,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356353</v>
+        <v>128356285</v>
       </c>
       <c r="B16" t="n">
-        <v>92816</v>
+        <v>87146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565118</v>
+        <v>565102</v>
       </c>
       <c r="R16" t="n">
-        <v>6683561</v>
+        <v>6683543</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128353672</v>
+        <v>128356286</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>87146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,37 +2169,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565163</v>
+        <v>565257</v>
       </c>
       <c r="R17" t="n">
-        <v>6683698</v>
+        <v>6683775</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2274,22 +2243,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128356245</v>
+        <v>128356287</v>
       </c>
       <c r="B18" t="n">
-        <v>92443</v>
+        <v>87146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,43 +2266,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565330</v>
+        <v>565133</v>
       </c>
       <c r="R18" t="n">
-        <v>6683935</v>
+        <v>6683665</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,32 +2352,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128356342</v>
+        <v>128356288</v>
       </c>
       <c r="B19" t="n">
-        <v>92816</v>
+        <v>87146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4368</v>
+        <v>3762</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2427,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565338</v>
+        <v>565128</v>
       </c>
       <c r="R19" t="n">
-        <v>6683896</v>
+        <v>6683644</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,10 +2449,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128356338</v>
+        <v>128353720</v>
       </c>
       <c r="B20" t="n">
-        <v>92816</v>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2500,37 +2460,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565124</v>
+        <v>565171</v>
       </c>
       <c r="R20" t="n">
-        <v>6683659</v>
+        <v>6683703</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2560,11 +2520,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2579,22 +2534,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128356349</v>
+        <v>128356270</v>
       </c>
       <c r="B21" t="n">
-        <v>92816</v>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,21 +2557,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565147</v>
+        <v>565281</v>
       </c>
       <c r="R21" t="n">
-        <v>6683691</v>
+        <v>6683884</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,57 +2643,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128356321</v>
+        <v>128353904</v>
       </c>
       <c r="B22" t="n">
-        <v>92834</v>
+        <v>93215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565225</v>
+        <v>565224</v>
       </c>
       <c r="R22" t="n">
-        <v>6683834</v>
+        <v>6683766</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2782,69 +2728,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128356319</v>
+        <v>128354540</v>
       </c>
       <c r="B23" t="n">
-        <v>92834</v>
+        <v>93215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565206</v>
+        <v>565071</v>
       </c>
       <c r="R23" t="n">
-        <v>6683808</v>
+        <v>6683539</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2888,66 +2825,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128356333</v>
+        <v>128356336</v>
       </c>
       <c r="B24" t="n">
-        <v>92834</v>
+        <v>93215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565281</v>
+        <v>565294</v>
       </c>
       <c r="R24" t="n">
-        <v>6683884</v>
+        <v>6683885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,6 +2908,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3006,54 +2939,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128356332</v>
+        <v>128356337</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>93215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565289</v>
+        <v>565149</v>
       </c>
       <c r="R25" t="n">
-        <v>6683895</v>
+        <v>6683707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,6 +3010,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3112,54 +3041,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128356323</v>
+        <v>128356338</v>
       </c>
       <c r="B26" t="n">
-        <v>92834</v>
+        <v>93215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565127</v>
+        <v>565124</v>
       </c>
       <c r="R26" t="n">
-        <v>6683598</v>
+        <v>6683659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,6 +3112,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,10 +3143,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128356346</v>
+        <v>128356342</v>
       </c>
       <c r="B27" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3253,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565165</v>
+        <v>565338</v>
       </c>
       <c r="R27" t="n">
-        <v>6683730</v>
+        <v>6683896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3240,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128356287</v>
+        <v>128356343</v>
       </c>
       <c r="B28" t="n">
-        <v>86764</v>
+        <v>93215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565133</v>
+        <v>565300</v>
       </c>
       <c r="R28" t="n">
-        <v>6683665</v>
+        <v>6683931</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,10 +3337,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128356337</v>
+        <v>128356344</v>
       </c>
       <c r="B29" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3447,10 +3372,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565149</v>
+        <v>565307</v>
       </c>
       <c r="R29" t="n">
-        <v>6683707</v>
+        <v>6683918</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,11 +3408,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3514,54 +3434,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128356248</v>
+        <v>128356345</v>
       </c>
       <c r="B30" t="n">
-        <v>92443</v>
+        <v>93215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565207</v>
+        <v>565282</v>
       </c>
       <c r="R30" t="n">
-        <v>6683770</v>
+        <v>6683847</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,10 +3531,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128356309</v>
+        <v>128356346</v>
       </c>
       <c r="B31" t="n">
-        <v>92800</v>
+        <v>93215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,21 +3542,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3655,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565184</v>
+        <v>565165</v>
       </c>
       <c r="R31" t="n">
-        <v>6683739</v>
+        <v>6683730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3717,48 +3628,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128354204</v>
+        <v>128356348</v>
       </c>
       <c r="B32" t="n">
-        <v>86926</v>
+        <v>93215</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565325</v>
+        <v>565149</v>
       </c>
       <c r="R32" t="n">
-        <v>6683920</v>
+        <v>6683699</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3802,60 +3713,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128354354</v>
+        <v>128356349</v>
       </c>
       <c r="B33" t="n">
-        <v>92834</v>
+        <v>93215</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565289</v>
+        <v>565147</v>
       </c>
       <c r="R33" t="n">
-        <v>6683828</v>
+        <v>6683691</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3899,56 +3810,47 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128356255</v>
+        <v>128356350</v>
       </c>
       <c r="B34" t="n">
-        <v>92443</v>
+        <v>93215</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
@@ -3958,7 +3860,7 @@
         <v>565128</v>
       </c>
       <c r="R34" t="n">
-        <v>6683585</v>
+        <v>6683651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128353904</v>
+        <v>128356351</v>
       </c>
       <c r="B35" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,17 +3950,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565224</v>
+        <v>565125</v>
       </c>
       <c r="R35" t="n">
-        <v>6683766</v>
+        <v>6683620</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4102,22 +4004,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128356343</v>
+        <v>128356352</v>
       </c>
       <c r="B36" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4149,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565300</v>
+        <v>565124</v>
       </c>
       <c r="R36" t="n">
-        <v>6683931</v>
+        <v>6683563</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,54 +4113,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128356250</v>
+        <v>128356353</v>
       </c>
       <c r="B37" t="n">
-        <v>92443</v>
+        <v>93215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565136</v>
+        <v>565118</v>
       </c>
       <c r="R37" t="n">
-        <v>6683681</v>
+        <v>6683561</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128356336</v>
+        <v>128356356</v>
       </c>
       <c r="B38" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565294</v>
+        <v>565307</v>
       </c>
       <c r="R38" t="n">
-        <v>6683885</v>
+        <v>6683932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,11 +4281,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4419,48 +4307,59 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128356276</v>
+        <v>128379692</v>
       </c>
       <c r="B39" t="n">
-        <v>97507</v>
+        <v>93215</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565383</v>
+        <v>565156</v>
       </c>
       <c r="R39" t="n">
-        <v>6683939</v>
+        <v>6683686</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4498,28 +4397,39 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128356326</v>
+        <v>128354183</v>
       </c>
       <c r="B40" t="n">
-        <v>92834</v>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,46 +4437,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565306</v>
+        <v>565320</v>
       </c>
       <c r="R40" t="n">
-        <v>6683915</v>
+        <v>6683918</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4610,22 +4511,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128356252</v>
+        <v>128356231</v>
       </c>
       <c r="B41" t="n">
-        <v>92443</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,7 +4553,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4666,10 +4567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565313</v>
+        <v>565261</v>
       </c>
       <c r="R41" t="n">
-        <v>6683875</v>
+        <v>6683777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,10 +4629,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128356240</v>
+        <v>128356234</v>
       </c>
       <c r="B42" t="n">
-        <v>92443</v>
+        <v>92869</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,7 +4659,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4772,10 +4673,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565298</v>
+        <v>565304</v>
       </c>
       <c r="R42" t="n">
-        <v>6683931</v>
+        <v>6683798</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4834,10 +4735,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128356234</v>
+        <v>128356235</v>
       </c>
       <c r="B43" t="n">
-        <v>92443</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4878,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565304</v>
+        <v>565149</v>
       </c>
       <c r="R43" t="n">
-        <v>6683798</v>
+        <v>6683718</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4940,37 +4841,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128356219</v>
+        <v>128356236</v>
       </c>
       <c r="B44" t="n">
-        <v>91028</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256335</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4984,10 +4885,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>565287</v>
+        <v>565136</v>
       </c>
       <c r="R44" t="n">
-        <v>6683892</v>
+        <v>6683697</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,7 +4929,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5047,10 +4947,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128356317</v>
+        <v>128356237</v>
       </c>
       <c r="B45" t="n">
-        <v>92834</v>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5058,26 +4958,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5091,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565188</v>
+        <v>565304</v>
       </c>
       <c r="R45" t="n">
-        <v>6683735</v>
+        <v>6683884</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128356262</v>
+        <v>128356240</v>
       </c>
       <c r="B46" t="n">
-        <v>92443</v>
+        <v>92869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5183,7 +5083,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5197,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565306</v>
+        <v>565298</v>
       </c>
       <c r="R46" t="n">
-        <v>6683913</v>
+        <v>6683931</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5259,45 +5159,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128356351</v>
+        <v>128356245</v>
       </c>
       <c r="B47" t="n">
-        <v>92816</v>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565125</v>
+        <v>565330</v>
       </c>
       <c r="R47" t="n">
-        <v>6683620</v>
+        <v>6683935</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5356,45 +5265,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128356307</v>
+        <v>128356246</v>
       </c>
       <c r="B48" t="n">
-        <v>92800</v>
+        <v>92869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565193</v>
+        <v>565122</v>
       </c>
       <c r="R48" t="n">
-        <v>6683755</v>
+        <v>6683547</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,48 +5371,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128353808</v>
+        <v>128356248</v>
       </c>
       <c r="B49" t="n">
-        <v>92800</v>
+        <v>92869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565189</v>
+        <v>565207</v>
       </c>
       <c r="R49" t="n">
-        <v>6683740</v>
+        <v>6683770</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5538,57 +5465,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128356310</v>
+        <v>128356250</v>
       </c>
       <c r="B50" t="n">
-        <v>92800</v>
+        <v>92869</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565306</v>
+        <v>565136</v>
       </c>
       <c r="R50" t="n">
-        <v>6683913</v>
+        <v>6683681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128356374</v>
+        <v>128356252</v>
       </c>
       <c r="B51" t="n">
-        <v>86926</v>
+        <v>92869</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,26 +5594,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5691,10 +5627,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565325</v>
+        <v>565313</v>
       </c>
       <c r="R51" t="n">
-        <v>6683931</v>
+        <v>6683875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5753,10 +5689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128353745</v>
+        <v>128356255</v>
       </c>
       <c r="B52" t="n">
-        <v>92834</v>
+        <v>92869</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5764,37 +5700,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>565166</v>
+        <v>565128</v>
       </c>
       <c r="R52" t="n">
-        <v>6683711</v>
+        <v>6683585</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5838,57 +5783,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128356350</v>
+        <v>128356257</v>
       </c>
       <c r="B53" t="n">
-        <v>92816</v>
+        <v>92869</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565128</v>
+        <v>565243</v>
       </c>
       <c r="R53" t="n">
-        <v>6683651</v>
+        <v>6683765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5947,37 +5901,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128356294</v>
+        <v>128356259</v>
       </c>
       <c r="B54" t="n">
-        <v>91043</v>
+        <v>92869</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5991,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565290</v>
+        <v>565167</v>
       </c>
       <c r="R54" t="n">
-        <v>6683893</v>
+        <v>6683728</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6053,10 +6007,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128356236</v>
+        <v>128356260</v>
       </c>
       <c r="B55" t="n">
-        <v>92443</v>
+        <v>92869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6083,7 +6037,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6097,10 +6051,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565136</v>
+        <v>565139</v>
       </c>
       <c r="R55" t="n">
-        <v>6683697</v>
+        <v>6683696</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,45 +6113,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128356356</v>
+        <v>128356261</v>
       </c>
       <c r="B56" t="n">
-        <v>92816</v>
+        <v>92869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565307</v>
+        <v>565331</v>
       </c>
       <c r="R56" t="n">
-        <v>6683932</v>
+        <v>6683832</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,45 +6219,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128356352</v>
+        <v>128356262</v>
       </c>
       <c r="B57" t="n">
-        <v>92816</v>
+        <v>92869</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565124</v>
+        <v>565306</v>
       </c>
       <c r="R57" t="n">
-        <v>6683563</v>
+        <v>6683913</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,37 +6325,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128356257</v>
+        <v>128356294</v>
       </c>
       <c r="B58" t="n">
-        <v>92443</v>
+        <v>91435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6397,10 +6369,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565243</v>
+        <v>565290</v>
       </c>
       <c r="R58" t="n">
-        <v>6683765</v>
+        <v>6683893</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6459,48 +6431,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128356360</v>
+        <v>128353570</v>
       </c>
       <c r="B59" t="n">
-        <v>100824</v>
+        <v>93233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565329</v>
+        <v>565129</v>
       </c>
       <c r="R59" t="n">
-        <v>6683831</v>
+        <v>6683660</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6544,44 +6516,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128353737</v>
+        <v>128353672</v>
       </c>
       <c r="B60" t="n">
-        <v>86764</v>
+        <v>93233</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6591,10 +6563,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565164</v>
+        <v>565163</v>
       </c>
       <c r="R60" t="n">
-        <v>6683706</v>
+        <v>6683698</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6653,14 +6625,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128356316</v>
+        <v>128353745</v>
       </c>
       <c r="B61" t="n">
-        <v>92834</v>
+        <v>93233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6681,29 +6653,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>565125</v>
+        <v>565166</v>
       </c>
       <c r="R61" t="n">
-        <v>6683662</v>
+        <v>6683711</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6747,26 +6710,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128356320</v>
+        <v>128354354</v>
       </c>
       <c r="B62" t="n">
-        <v>92834</v>
+        <v>93233</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6787,29 +6750,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565213</v>
+        <v>565289</v>
       </c>
       <c r="R62" t="n">
-        <v>6683796</v>
+        <v>6683828</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6853,26 +6807,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128356322</v>
+        <v>128356315</v>
       </c>
       <c r="B63" t="n">
-        <v>92834</v>
+        <v>93233</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6895,7 +6849,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6909,10 +6863,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>565121</v>
+        <v>565123</v>
       </c>
       <c r="R63" t="n">
-        <v>6683569</v>
+        <v>6683582</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6971,48 +6925,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128353797</v>
+        <v>128356316</v>
       </c>
       <c r="B64" t="n">
-        <v>86764</v>
+        <v>93233</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>565197</v>
+        <v>565125</v>
       </c>
       <c r="R64" t="n">
-        <v>6683732</v>
+        <v>6683662</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7056,49 +7019,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128356259</v>
+        <v>128356317</v>
       </c>
       <c r="B65" t="n">
-        <v>92443</v>
+        <v>93233</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7112,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565167</v>
+        <v>565188</v>
       </c>
       <c r="R65" t="n">
-        <v>6683728</v>
+        <v>6683735</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,45 +7137,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128356270</v>
+        <v>128356318</v>
       </c>
       <c r="B66" t="n">
-        <v>92810</v>
+        <v>93233</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565281</v>
+        <v>565133</v>
       </c>
       <c r="R66" t="n">
-        <v>6683884</v>
+        <v>6683665</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,37 +7243,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128356261</v>
+        <v>128356319</v>
       </c>
       <c r="B67" t="n">
-        <v>92443</v>
+        <v>93233</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7315,10 +7287,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565331</v>
+        <v>565206</v>
       </c>
       <c r="R67" t="n">
-        <v>6683832</v>
+        <v>6683808</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7377,45 +7349,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128356361</v>
+        <v>128356320</v>
       </c>
       <c r="B68" t="n">
-        <v>100824</v>
+        <v>93233</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565330</v>
+        <v>565213</v>
       </c>
       <c r="R68" t="n">
-        <v>6683934</v>
+        <v>6683796</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,14 +7455,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128356331</v>
+        <v>128356321</v>
       </c>
       <c r="B69" t="n">
-        <v>92834</v>
+        <v>93233</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7504,7 +7485,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7518,10 +7499,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565298</v>
+        <v>565225</v>
       </c>
       <c r="R69" t="n">
-        <v>6683926</v>
+        <v>6683834</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7580,37 +7561,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128356231</v>
+        <v>128356322</v>
       </c>
       <c r="B70" t="n">
-        <v>92443</v>
+        <v>93233</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7624,10 +7605,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565261</v>
+        <v>565121</v>
       </c>
       <c r="R70" t="n">
-        <v>6683777</v>
+        <v>6683569</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7686,48 +7667,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128354308</v>
+        <v>128356323</v>
       </c>
       <c r="B71" t="n">
-        <v>100824</v>
+        <v>93233</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>565341</v>
+        <v>565127</v>
       </c>
       <c r="R71" t="n">
-        <v>6683943</v>
+        <v>6683598</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7771,22 +7761,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128354290</v>
+        <v>128356324</v>
       </c>
       <c r="B72" t="n">
-        <v>86963</v>
+        <v>93233</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7794,37 +7784,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>565327</v>
+        <v>565185</v>
       </c>
       <c r="R72" t="n">
-        <v>6683939</v>
+        <v>6683745</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7868,22 +7867,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128354079</v>
+        <v>128356325</v>
       </c>
       <c r="B73" t="n">
-        <v>92800</v>
+        <v>93233</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,37 +7890,46 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565281</v>
+        <v>565139</v>
       </c>
       <c r="R73" t="n">
-        <v>6683847</v>
+        <v>6683679</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7965,57 +7973,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128356288</v>
+        <v>128356326</v>
       </c>
       <c r="B74" t="n">
-        <v>86764</v>
+        <v>93233</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565128</v>
+        <v>565306</v>
       </c>
       <c r="R74" t="n">
-        <v>6683644</v>
+        <v>6683915</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8074,45 +8091,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128356286</v>
+        <v>128356327</v>
       </c>
       <c r="B75" t="n">
-        <v>86764</v>
+        <v>93233</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565257</v>
+        <v>565292</v>
       </c>
       <c r="R75" t="n">
-        <v>6683775</v>
+        <v>6683907</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8171,14 +8197,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128356315</v>
+        <v>128356330</v>
       </c>
       <c r="B76" t="n">
-        <v>92834</v>
+        <v>93233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8201,7 +8227,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8215,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565123</v>
+        <v>565306</v>
       </c>
       <c r="R76" t="n">
-        <v>6683582</v>
+        <v>6683912</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8277,35 +8303,44 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128356363</v>
+        <v>128356331</v>
       </c>
       <c r="B77" t="n">
-        <v>100824</v>
+        <v>93233</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
@@ -8315,7 +8350,7 @@
         <v>565298</v>
       </c>
       <c r="R77" t="n">
-        <v>6683884</v>
+        <v>6683926</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8374,48 +8409,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128353641</v>
+        <v>128356332</v>
       </c>
       <c r="B78" t="n">
-        <v>86764</v>
+        <v>93233</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565149</v>
+        <v>565289</v>
       </c>
       <c r="R78" t="n">
-        <v>6683686</v>
+        <v>6683895</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8459,22 +8503,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128356344</v>
+        <v>128356333</v>
       </c>
       <c r="B79" t="n">
-        <v>92816</v>
+        <v>93233</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8482,34 +8526,43 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565307</v>
+        <v>565281</v>
       </c>
       <c r="R79" t="n">
-        <v>6683918</v>
+        <v>6683884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8568,48 +8621,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128354183</v>
+        <v>128356334</v>
       </c>
       <c r="B80" t="n">
-        <v>92443</v>
+        <v>93233</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565320</v>
+        <v>565315</v>
       </c>
       <c r="R80" t="n">
-        <v>6683918</v>
+        <v>6683935</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8653,22 +8715,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128354266</v>
+        <v>128356335</v>
       </c>
       <c r="B81" t="n">
-        <v>86963</v>
+        <v>93233</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8676,37 +8738,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skommarboberget, Skommarboberget, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565313</v>
+        <v>565323</v>
       </c>
       <c r="R81" t="n">
-        <v>6683939</v>
+        <v>6683839</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8736,6 +8798,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i stor häxring</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8750,54 +8817,59 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128356330</v>
+        <v>128356218</v>
       </c>
       <c r="B82" t="n">
-        <v>92834</v>
+        <v>58114</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8806,10 +8878,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>565306</v>
+        <v>565169</v>
       </c>
       <c r="R82" t="n">
-        <v>6683912</v>
+        <v>6683577</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8868,10 +8940,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128356334</v>
+        <v>128356276</v>
       </c>
       <c r="B83" t="n">
-        <v>92834</v>
+        <v>97983</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8879,43 +8951,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>565315</v>
+        <v>565383</v>
       </c>
       <c r="R83" t="n">
-        <v>6683935</v>
+        <v>6683939</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8974,10 +9037,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128356318</v>
+        <v>128354308</v>
       </c>
       <c r="B84" t="n">
-        <v>92834</v>
+        <v>101326</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8985,46 +9048,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>565133</v>
+        <v>565341</v>
       </c>
       <c r="R84" t="n">
-        <v>6683665</v>
+        <v>6683943</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9068,71 +9122,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128379692</v>
+        <v>128356360</v>
       </c>
       <c r="B85" t="n">
-        <v>92821</v>
+        <v>101326</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>565156</v>
+        <v>565329</v>
       </c>
       <c r="R85" t="n">
-        <v>6683686</v>
+        <v>6683831</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9170,80 +9213,66 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>kalkmark</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128379701</v>
+        <v>128356361</v>
       </c>
       <c r="B86" t="n">
-        <v>92805</v>
+        <v>101326</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>565183</v>
+        <v>565330</v>
       </c>
       <c r="R86" t="n">
-        <v>6683738</v>
+        <v>6683934</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9275,43 +9304,522 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>6 m långt mycel</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>kalkmark</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128356362</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>565302</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6683928</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128356363</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>565298</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6683884</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128356219</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>565287</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6683892</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128354266</v>
+      </c>
+      <c r="B90" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>565313</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6683939</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128354290</v>
+      </c>
+      <c r="B91" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skommarboberget, Skommarboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>565327</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6683939</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34930-2024 artfynd.xlsx
+++ b/artfynd/A 34930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356310</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356311</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128379701</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120161061</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354204</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353641</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353737</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353797</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356285</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356286</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356287</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356288</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353720</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356270</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2737,6 +2842,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353904</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354540</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2936,6 +3051,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356336</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3038,6 +3158,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356337</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3140,6 +3265,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356338</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3237,6 +3367,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356342</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3334,6 +3469,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356343</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3431,6 +3571,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356344</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3528,6 +3673,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356345</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3625,6 +3775,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356346</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3722,6 +3877,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356348</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3819,6 +3979,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356349</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3916,6 +4081,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356350</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356351</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4110,6 +4285,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356352</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4207,6 +4387,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356353</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4304,6 +4489,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356356</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4423,6 +4613,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128379692</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4520,6 +4715,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354183</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4626,6 +4826,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356231</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4732,6 +4937,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356234</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4838,6 +5048,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356235</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4944,6 +5159,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356236</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5050,6 +5270,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356237</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5156,6 +5381,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356240</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5262,6 +5492,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356245</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5368,6 +5603,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356246</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5474,6 +5714,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356248</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5580,6 +5825,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356250</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5686,6 +5936,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356252</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5792,6 +6047,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356255</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,6 +6158,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356257</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6004,6 +6269,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356259</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6110,6 +6380,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356260</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6216,6 +6491,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356261</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6322,6 +6602,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356262</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6428,6 +6713,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356294</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6525,6 +6815,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353570</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6622,6 +6917,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353672</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6719,6 +7019,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353745</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6816,6 +7121,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354354</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6922,6 +7232,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356315</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7028,6 +7343,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356316</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7134,6 +7454,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356317</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7240,6 +7565,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356318</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7346,6 +7676,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356319</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7452,6 +7787,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356320</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7558,6 +7898,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356321</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7664,6 +8009,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356322</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7770,6 +8120,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356323</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7876,6 +8231,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356324</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7982,6 +8342,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356325</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8088,6 +8453,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356326</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8194,6 +8564,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356327</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8300,6 +8675,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356330</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8406,6 +8786,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356331</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8512,6 +8897,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356332</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8618,6 +9008,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356333</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8724,6 +9119,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356334</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8826,6 +9226,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356335</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8937,6 +9342,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356218</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9034,6 +9444,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356276</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9131,6 +9546,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354308</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9228,6 +9648,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356360</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9325,6 +9750,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356361</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9422,6 +9852,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356362</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9519,6 +9954,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356363</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9626,6 +10066,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356219</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9723,6 +10168,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354266</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9820,8 +10270,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>